--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -16,7 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_TARGET_DEV" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_BUDGET" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_GA_BEHAVIOR" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_부록_DIM_FACT" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_TARGET_BIZ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_부록_DIM_FACT" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,6 +498,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>⚙️ 생성기: scripts/gen_column_mapping.py — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_column_mapping.py 수정 후 재실행하세요.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -692,12 +700,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>(FACT_TARGET_BIZ)</t>
+          <t>WIDE_TARGET_BIZ</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>⛔ 원천 대기(E-6)</t>
+          <t>⛔ 구조준비·원천 대기(E-6)</t>
         </is>
       </c>
     </row>
@@ -719,6 +727,323 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WIDE_TARGET_BIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>GOLD 컬럼</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>업무 의미</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>SILVER 원천(테이블.컬럼)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>BRONZE 원천(테이블.컬럼)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>변환 규칙</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MONTH_KEY</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>목표 월(YYYYMM)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ERP_BIZ_TARGET.MONTH_KEY</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>(원천 부재·E-6)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>월키 클램프(무효→0)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ORG_NM(계층)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>조직/부서</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>DIM_ORG(이름 크로스워크)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO.DEPT_NM</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ORG_NM 이름매칭(본부/지부 vs 부서 grain 불일치 가능)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>후원사업명</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO.SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>SPONSOR_BIZ_NM 이름매칭</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>캠페인명</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>TM_CM_CMPGN_MNG.CMPGN_NM</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_NM 이름매칭(선택 grain·nullable)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ANNUAL_GOAL_CNT</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>연사업목표(#152)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ERP_BIZ_TARGET.TARGET_AMT(금액)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>(원천 부재)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>⚠️단위충돌: 금액≠건→오귀속 방지 NULL(GOLD DDL 금액 measure 신설 or 건 원천확보 시 배선)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SUPP_GOAL_CNT</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>추경목표(#153)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>(원천 부재)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>(원천 부재)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>원천부재→NULL</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ANNUAL_CUM_GOAL_CNT</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>연사업누계목표(#154)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>(원천 부재)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>(원천 부재)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>원천부재→NULL</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SUPP_CUM_GOAL_CNT</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>추경누계목표(#155)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>(원천 부재)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>(원천 부재)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>원천부재→NULL</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -845,12 +1170,12 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>user_id 매칭(0행·비활성)</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+          <t>exact 매칭 1,274명·활성(2026-07-15)·XREF dedup·⚠️G-5 재검증</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1863,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>GA4_EVENT + IDENTITY</t>
+          <t>GA4_EVENT + IDENTITY_MEMBER_XREF</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1548,7 +1873,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>샤드 통합</t>
+          <t>샤드 통합·IDENTITY_SK 실조인(2026-07-15)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1649,7 +1974,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>(원천 부재)</t>
+          <t>ERP_BIZ_TARGET(스키마-only 0행)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1659,7 +1984,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>별도 입고 대기(E-6)</t>
+          <t>dbt 스켈레톤 저작(0행)·이름 크로스워크 조인·단위충돌(금액vs건)→측정치 NULL·입고 시 자동화(E-6)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -4547,12 +4872,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>user_id→session_fill(브리지, S)</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+          <t>IDENTITY_SK→DIM_MEMBER_IDENTITY 실조인(2026-07-15)·⚠️G-5 재검증</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
     </row>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -732,15 +732,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,25 +759,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>지표#</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>업무 의미</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SILVER 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BRONZE 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>변환 규칙</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -788,27 +794,28 @@
           <t>MONTH_KEY</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>목표 월(YYYYMM)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>ERP_BIZ_TARGET.MONTH_KEY</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>(원천 부재·E-6)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>월키 클램프(무효→0)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -822,25 +829,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>공114·115·116</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>조직/부서</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>DIM_ORG(이름 크로스워크)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>TM_CM_DEPT_INFO.DEPT_NM</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>ORG_NM 이름매칭(본부/지부 vs 부서 grain 불일치 가능)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -854,25 +866,30 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>공123·124</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>후원사업명</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>TM_CM_SPNSR_BSNS_INFO.SPNSR_BSNS_NM</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>SPONSOR_BIZ_NM 이름매칭</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -886,25 +903,30 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>공18·120</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>캠페인명</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>TM_CM_CMPGN_MNG.CMPGN_NM</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>CAMPAIGN_NM 이름매칭(선택 grain·nullable)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -918,25 +940,30 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>공152</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>연사업목표(#152)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ERP_BIZ_TARGET.TARGET_AMT(금액)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>(원천 부재)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>⚠️단위충돌: 금액≠건→오귀속 방지 NULL(GOLD DDL 금액 measure 신설 or 건 원천확보 시 배선)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -950,25 +977,30 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>공153</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>추경목표(#153)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>(원천 부재)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>(원천 부재)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>원천부재→NULL</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -982,25 +1014,30 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>공154</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>연사업누계목표(#154)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>(원천 부재)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>(원천 부재)</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>원천부재→NULL</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -1014,25 +1051,30 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>공155</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>추경누계목표(#155)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>(원천 부재)</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>(원천 부재)</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>원천부재→NULL</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -2004,15 +2046,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2030,25 +2073,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>지표#</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>업무 의미</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SILVER 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BRONZE 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>변환 규칙</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -2060,27 +2108,28 @@
           <t>MONTH_KEY</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>실적 월(YYYYMM)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DEV.OCCRRNC_DE 등 거래일</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_DVLP_AMT.OCCRRNC_DE</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>거래일→월 롤업(YYYYMM)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2094,25 +2143,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>공110</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>회원 식별키</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_INFO.MBER_NO / TM_MM_ONCE_MBER_INFO.ONCE_MBER_NO</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>정기∪일시 회원번호 통합키</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2126,25 +2180,30 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>공148</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>개발(명)</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DEV(MBER_NO distinct)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_DVLP_AMT.MBER_NO</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>월×회원 COUNT(DISTINCT)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2158,25 +2217,30 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>공4·5·149</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>개발(건)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_DVLP_AMT.SPNSR_AMT</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>SUM(금액)/10000 basis</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2190,25 +2254,30 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>공150</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>증액(명)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_AMT_CHANGE(RDCAMT_YN='N')</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_IRSD.SPNSR_AMT·RDCAMT_YN</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>증액분 회원 COUNT</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2222,25 +2291,30 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>공38</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>감액(건)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_AMT_CHANGE(RDCAMT_YN='Y')</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_IRSD.SPNSR_AMT·RDCAMT_YN</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>SUM(감액금액)/10000</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2254,25 +2328,30 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>신20</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>이탈(건)=취소+감액</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DISCONTINUE + CRM_MEMBER_AMT_CHANGE</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC + TM_MM_FDRM_MBER_IRSD</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>SUM(취소+감액)/10000 (신규 표준지표)</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2286,25 +2365,30 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>공156</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>활동회원(명)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_STATUS_HIST + CRM_MEMBER_SPONSOR_BIZ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>TH_MM_FDRM_MBER_STNG_DTLS + TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>월말 시점 스냅샷 COUNT</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2318,25 +2402,30 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>공36</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
           <t>미납(건)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>CRM_PAYMENT_BILLING(PAY_STAT_CD=F∪NULL)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>TM_PM_MBRFEE_ACMSLT.PAY_STAT_CD</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>미납 상태 건수(C-3 정의)</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2350,25 +2439,30 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>공35</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
           <t>중단(건)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DISCONTINUE</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC.SPNSR_DSCNTC_DE</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>월 중단 건수</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2382,25 +2476,30 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>공66</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t>정기회비(원)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>정기 납입액 SUM(원단위)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2414,25 +2513,30 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>공69·70</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
           <t>납입회비(원)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>TM_PM_MBRFEE_ACMSLT.PAY_AMT + TM_PM_DNTN_DTLS.PAY_AMT</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>회비∪기부금 납입 SUM</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2446,25 +2550,30 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>공71</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
           <t>청구(원)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>TM_PM_MBRFEE_ACMSLT.RQEST_AMT</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>청구액 SUM(행기준)</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2478,25 +2587,30 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>공34</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
           <t>재후원 여부</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_RESPONSOR</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_RE_SPNSR</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>재후원 이력 존재 플래그</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2508,27 +2622,28 @@
           <t>INBOUND_CALL_CNT</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>인바운드콜수</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>(CRM 부재)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>(원천 없음)</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>현업 수기입력(비-CRM, C-8)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -2540,27 +2655,28 @@
           <t>TS_CALL_CNT</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>TS콜수</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>(CRM 부재)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>(원천 없음)</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>현업 수기입력(비-CRM, C-8)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -2574,25 +2690,30 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>공130</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
           <t>성별</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_INFO.SEX</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>1/3→M, 2/4→F, NULL→NULL 정규화</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2606,25 +2727,30 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>공131</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
           <t>지역</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DEV.AREA_CD(스냅샷)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_DVLP_AMT.AREA_CD</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>CM018 코드→라벨(개발시점 스냅샷)</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2636,27 +2762,28 @@
           <t>MEMBER_AGE_BAND</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>연령대</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DEV.AGE(스냅샷)</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_DVLP_AMT.AGE</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>연령 코드화(생년 raw 미적재)</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2670,25 +2797,30 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>공132</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
           <t>회원상태</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER.MBER_STAT_CD + STATUS_HIST</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_INFO.MBER_STAT_CD</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>MM010 코드→라벨 + SCD2 이력</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2700,27 +2832,28 @@
           <t>MEMBER_TYPE</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>회원구분(정기/일시)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER.MEMBER_TYPE(파생)</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_INFO / TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>FDRM/ONCE 크로스워크(테이블 출처 기반)</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2734,25 +2867,30 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>공117</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>TM_CM_BRND_MNG.BRND_NM</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>캠페인→브랜드 LEFT JOIN</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2766,25 +2904,30 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>공18·120</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
           <t>캠페인명</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>TM_CM_CMPGN_MNG.CMPGN_NM</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2798,25 +2941,30 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>공123·124</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
           <t>후원사업명</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>TM_CM_SPNSR_BSNS_INFO.SPNSR_BSNS_NM</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2830,25 +2978,30 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>공125</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
           <t>결제수단</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>CRM_PAYMENT_METHOD.CARD_DIV_CD</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>TM_PM_SETLE_INFO.CARD_DIV_CD</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>코드→라벨</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2865,15 +3018,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2891,25 +3045,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>지표#</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>업무 의미</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SILVER 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BRONZE 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>변환 규칙</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -2921,27 +3080,28 @@
           <t>DATE_SK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>발송일(YYYYMMDD)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>CRM_SEND_REQUEST 발송일</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>TM_MS_EMAIL_SNDNG / TM_MS_MSG_AT_SNDNG / TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>채널별 발송일 통합</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2955,25 +3115,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>공110</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>발송 대상 회원</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>CRM_SEND_MEMBER.MBER_NO</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>TD_MS_EMAIL_SNDNG_DTLS / TD_MS_MSG_AT_SNDNG_DTLS / TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>발송상세 회원키</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2987,25 +3152,30 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>공85</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>발송수(명)</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>CRM_SEND_MEMBER(MBER_NO distinct)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>TD_MS_*_SNDNG_DTLS</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>COUNT(DISTINCT 회원)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3019,25 +3189,30 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>공86</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>성공수(명)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>CRM_SEND_RESULT(성공)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>TD_MS_EMAIL_LQY_SNDNG / TD_MS_MSG_AT_LQY_SNDNG / TD_MS_PSTMTR_LQY_SNDNG</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>성과 성공건 회원 COUNT</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3051,25 +3226,30 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>공87</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>실패수(명)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>CRM_SEND_RESULT(실패)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>TD_MS_*_LQY_SNDNG</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>성과 실패건 회원 COUNT</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3083,25 +3263,30 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>공88</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>서신참여(명)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>CRM_RELATION_ACTIVITY(LETTER)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>발송×서신 매칭</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3115,25 +3300,30 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>공91</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>선물금참여(원)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>CRM_RELATION_ACTIVITY.GFTMNEY</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>TM_RM_RELATNSP_GFTMNEY_INFO.GFTMNEY</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>선물금 SUM(원단위)</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3147,25 +3337,30 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>공139</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>+5일 서신참여(명)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>CRM_RELATION_ACTIVITY × CRM_SEND_*</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>발송일+5일 윈도우 매칭</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3179,25 +3374,30 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>공143</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
           <t>+5일 증액참여(명)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_AMT_CHANGE × CRM_SEND_*</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_IRSD</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>발송일+5일 윈도우 매칭</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3211,25 +3411,30 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>공136</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
           <t>발송 제목</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>SND_REQ_MST.SEND_TITLE / TM_MS_*_SNDNG</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3243,25 +3448,30 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>공138</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t>발송상태</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>TD_MS_*_SNDNG_DTLS</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>코드→라벨</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3273,27 +3483,28 @@
           <t>APP_PUSH_SEND_CNT</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>앱푸시 발송수</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>(ADMIN 제외)</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>(원천 미채택)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>어드민 제외 확정(2026-07-09)→미채움</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3305,27 +3516,28 @@
           <t>SERVICE_CHANNEL</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>발송 채널</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>CRM_SEND_REQUEST.SEND_CHANNEL</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>SND_REQ_MST / TM_MS_*_SNDNG</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>이메일/문자/우편 채널</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3342,15 +3554,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3368,25 +3581,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>지표#</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>업무 의미</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SILVER 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BRONZE 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>변환 규칙</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -3398,27 +3616,28 @@
           <t>PERF_DATE_SK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>광고 실적일</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>AGENCY_AD_PERFORMANCE 실적일</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>유형별 실적일 통합</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3432,25 +3651,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>공6</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>광고비(원)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>AGENCY_AD_PERFORMANCE 광고비</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS(광고비 컬럼 3종)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>유형별 비용 정제→UNION</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3464,25 +3688,30 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>공23</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>노출수</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>AGENCY_AD_PERFORMANCE</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>DGT_AD_CMPGN_DTLS(노출)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>디지털(DGT)만 존재</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3496,25 +3725,30 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>공24</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>클릭수</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>AGENCY_AD_PERFORMANCE</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>DGT_AD_CMPGN_DTLS(클릭)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>디지털(DGT)만 존재</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3528,25 +3762,30 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>공25</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>인입콜수</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>AGENCY_AD_PERFORMANCE</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>REBRDC/VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>TRY_TO_NUMBER 캐스팅</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3558,27 +3797,28 @@
           <t>GA_CONV_MEMBERS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>GA전환수(명)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>GA4_EVENT(전환 이벤트)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>BRONZE_GA4.events_YYYYMMDD</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>전환정의(O5) 회신 대기</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3592,25 +3832,30 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>공117</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>TM_CM_BRND_MNG.BRND_NM</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>캠페인 이름매칭(Q10) 대기</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3622,27 +3867,28 @@
           <t>AD_MEDIA_NAME</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>매체명</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>AGENCY_AD_CREATIVE.MEDIA_NAME</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>DGT_AD_CMPGN_DTLS.MEDIA_NM 등</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>유형별 산재→UNION</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3654,27 +3900,28 @@
           <t>AD_PLATFORM</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>플랫폼</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>AGENCY_AD_CREATIVE.PLATFORM</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3688,25 +3935,30 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>공14</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
           <t>디바이스</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>GA4_DEVICE.DEVICE_TYPE</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>BRONZE_GA4.events(device)</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>PC/M/APP</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3723,15 +3975,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3749,25 +4002,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>지표#</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>업무 의미</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SILVER 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BRONZE 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>변환 규칙</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -3779,27 +4037,28 @@
           <t>DATE_SK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>거래일</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DEV.OCCRRNC_DE</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_DVLP_AMT.OCCRRNC_DE</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3813,25 +4072,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>공110</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>회원 식별키</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_INFO.MBER_NO</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3845,25 +4109,30 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>공149·35</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>개발/중단 건·명</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DEV + CRM_MEMBER_DISCONTINUE</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_DVLP_AMT + TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>개발·중단 이벤트 건수</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3877,25 +4146,30 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>공162</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>중단 사유</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DISCONTINUE.DSCNTC_RSN_CD</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC.DSCNTC_RSN_CD</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>사유코드→라벨</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3907,27 +4181,28 @@
           <t>STOP_CHANNEL</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>중단 경로</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>CRM_MEMBER_DISCONTINUE.DSCNTC_PATH</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>TM_MM_FDRM_MBER_SPNSR_DSCNTC.DSCNTC_PATH</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3944,15 +4219,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3970,25 +4246,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>지표#</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>업무 의미</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SILVER 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BRONZE 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>변환 규칙</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -4000,27 +4281,28 @@
           <t>DATE_SK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>행사일</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>CRM_EVENT.STRT_DE</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>TM_MS_EVENT.STRT_DE / TM_MS_CRMN</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>행사∪캠페인행사</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4034,25 +4316,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>공110</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>참여 회원</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>CRM_EVENT_PARTICIPATION.MBER_NO</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>TD_MS_EVENT_PRTCPNT_DTL / TD_MS_CRMN_PRTCPNT</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4064,27 +4351,28 @@
           <t>EVENT_NAME</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>행사명</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>CRM_EVENT.EVENT_NM</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>TM_MS_EVENT.EVENT_NM</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4096,27 +4384,28 @@
           <t>PARTICIPATION_STATUS</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>참여상태</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_CD</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>TD_MS_EVENT_PRTCPNT_DTL.PARTCPT_STAT_CD</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>모집/참여/취소/당첨</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4128,27 +4417,28 @@
           <t>RECEIPT_AMT</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>참여 납입액</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>CRM_EVENT_PARTICIPATION.RCPMNY_AMT</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>TD_MS_EVENT_PRTCPNT_DTL.RCPMNY_AMT</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>원단위</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4160,27 +4450,28 @@
           <t>VIEW_CNT</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>행사 조회수</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>(ADMIN 제외)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>(원천 미채택)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>어드민 제외 확정→미채움</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4197,15 +4488,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4223,25 +4515,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>지표#</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>업무 의미</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SILVER 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BRONZE 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>변환 규칙</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -4253,27 +4550,28 @@
           <t>MONTH_KEY</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>목표 월(YYYYMM)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>CRM_DEV_TARGET(STDYY+STDR_MT)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>TM_CM_MBER_DVLP_GOAL.STDYY·STDR_MT</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>연+월→YYYYMM</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4287,25 +4585,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>공114·115·116</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>조직/부서</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>CRM_ORG.DEPT_NM(←DEPT_ID)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>TM_CM_DEPT_INFO.DEPT_NM</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>부서 계층 전개</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4319,25 +4622,30 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>공121</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>개발구분</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>CRM_DEV_TARGET.MBER_DVLP_DIV_CD</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>TM_CM_MBER_DVLP_GOAL.MBER_DVLP_DIV_CD</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>코드→라벨</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4349,27 +4657,28 @@
           <t>GOAL_CNT</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>목표 건수</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>CRM_DEV_TARGET.GOAL_CNT</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>TM_CM_MBER_DVLP_GOAL.GOAL_CNT</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4386,15 +4695,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4412,25 +4722,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>지표#</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>업무 의미</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SILVER 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BRONZE 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>변환 규칙</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -4442,27 +4757,28 @@
           <t>MONTH_KEY</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>예산 월(YYYYMM)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>ERP_BUDGET.MONTH_KEY</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>BDGT_ACMSLT_LEDGER(YEAR + 월컬럼)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>wide→long 언피벗(12개월)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4474,27 +4790,28 @@
           <t>BUDGET_ITEM(계층)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>예산과목(장~세세목)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ERP_BUDGET_ITEM(JANG~SUBDTL)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>BDGT_ACMSLT_LEDGER.JANG_NM~SUBDTL_ITEM_NM</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>6단계 계층 보존·MD5 키</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4506,27 +4823,28 @@
           <t>YEAR_BUDGET_AMT</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>편성예산(원)</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>ERP_BUDGET.YEAR_BUDGET_AMT</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>BDGT_ACMSLT_LEDGER.YEAR_BDGT_AMT_n</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>월별 언피벗</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4538,27 +4856,28 @@
           <t>EXEC_AMT</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>집행예산(원)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>ERP_BUDGET.EXEC_AMT</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>BDGT_ACMSLT_LEDGER.EXEC_AMT_n</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>월별 언피벗</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4572,25 +4891,30 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>공114·115·116</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>조직/부서</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ERP_BUDGET_ITEM.BDGT_UNIT_NM</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>BDGT_ACMSLT_LEDGER.BDGT_UNIT_NM</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>예산단위명(이름)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4602,27 +4926,28 @@
           <t>FUNDRAISING_COST</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>모금성비용(원)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>(원천 부재)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>(ERP 원장에 없음)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>원천 부재(E-1)→미채움</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4636,25 +4961,30 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>공6</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>광고비(원)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>AGENCY 보강 대기</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>DGT/REBRDC/VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>AGENCY_COST 보강(E-4)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4671,15 +5001,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4697,25 +5028,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>지표#</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>업무 의미</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SILVER 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>BRONZE 원천(테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>변환 규칙</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -4727,27 +5063,28 @@
           <t>DATE_SK</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>행동 일자</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>GA4_EVENT.event_date</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>BRONZE_GA4.events_YYYYMMDD.event_date</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>샤드 UNION</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4761,25 +5098,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>공97</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>세션수</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>GA4_EVENT.ga_session_id</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>BRONZE_GA4.events(event_params: ga_session_id)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>param 승격·비가산 주의</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4793,25 +5135,30 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>공107</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>스크롤 깊이</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>GA4_EVENT.percent_scrolled</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>BRONZE_GA4.events(event_params: percent_scrolled)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>param 승격</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4825,25 +5172,30 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>공105·106</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>페이지 경로</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>GA4_EVENT.page_location</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>BRONZE_GA4.events(event_params: page_location)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>degenerate</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4857,25 +5209,30 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>공112</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>GA↔회원 연결</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>GA4_IDENTITY.member_id</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>BRONZE_GA4.events(user_id / user_pseudo_id)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>IDENTITY_SK→DIM_MEMBER_IDENTITY 실조인(2026-07-15)·⚠️G-5 재검증</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4889,25 +5246,30 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>공109</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>유입 소스/매체</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>GA4_TRAFFIC_SOURCE.UTM_*</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>BRONZE_GA4.events(traffic_source)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -16,10 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_EVENT_PARTICIPATION" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_GA_BEHAVIOR" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_MEMBER_EVENT" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_MEMBER_MONTHLY" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_SERVICE_EVENT" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_TARGET_BIZ" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_TARGET_DEV" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_MEMBER_FEE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_MEMBER_MONTHLY" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_SERVICE_EVENT" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_TARGET_BIZ" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_TARGET_DEV" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2243,6 +2244,1920 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WIDE_마트</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>WIDE_컬럼</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>GOLD_원천(테이블.컬럼)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SILVER_원천(테이블.컬럼)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BRONZE_원천(테이블)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>업무_의미(배포 COMMENT)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>WIDE→GOLD_확정도</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>계보_확정도</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>상태_근거(실측)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MONTH_KEY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.MONTH_KEY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>회비월 YYYYMM (무효/NULL 이면 납입월 폴백, 둘 다 무효면 0=Unknown월 — FMM 과 동일 규칙)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>비영 40,262,023/40,262,076 (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAL_YEAR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.MONTH_KEY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FLOOR(MONTH_KEY/100) — 연도</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>비영 40,262,023/40,262,076 (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAL_MONTH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.MONTH_KEY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MOD(MONTH_KEY,100) — 월</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>비영 40,262,023/40,262,076 (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MEMBER_DK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.MEMBER_DK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.MBER_NO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>비영 40,262,076/40,262,076 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_SK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.SPONSORSHIP_SK</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.MBER_NO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>비영 40,187,961/40,262,076 (99.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>🔴**납입 대상** 후원사업 — 회비 행에 붙은 값이다(원천 SPNSR_BSNS_ID 채움 99.83%·36종). 획득 후원사업(ACQ_SPONSORSHIP_NAME)과 다르다: 한 회원이 여러 후원사업에 낸다(회원-월 조합 37,148,615 → 회원-월-후원사업 39,563,730 = 6.5% 증가). 이것이 이 팩트를 FMM 과 분리한 이유다</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FEE_DIV_CD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.FEE_DIV_CD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.MBRFEE_DIV_CD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>비영 39,615,365/40,262,076 (98.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FEE_DIV_NAME</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.FEE_DIV_NAME</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>회비구분(PM010 실측 확정): 정기·선물금·일시·긴급구호. 🔴기부금 행은 원천이 NULL 이다 — 결측이 아니라 해당없음(P21)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>비영 39,615,365/40,262,076 (98.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PAYMENT_TYPE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.PAYMENT_TYPE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAYMENT_TYPE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>납입유형 = 회비/기부금. 🔴납부율·미납 분석은 회비만으로 스코프할 것 — 기부금은 원천에 청구(RQEST_AMT)가 전건 NULL 이라 분모에 들어갈 수 없다(O40)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>비영 40,262,076/40,262,076 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PAYMENT_SK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.PAYMENT_SK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.MBER_NO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>비영 40,069,970/40,262,076 (99.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PAYMENT_METHOD_NAME</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DIM_PAYMENT.SETTLE_METHOD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>결제수단 라벨. ⚠️커버리지 99.3%(6종=자동이체·신용카드·네이버페이·회비통장·OCR·휴대폰) — 원천 11종 중 5종(3·10·6·13·7, 225,855행=0.48%)은 **코드그룹 미특정**으로 (미매핑)이다. CRM_CODE 에서 11종을 덮는 그룹이 6개 나왔으나 전부 의미 무관(간사/질병/취미…)이라 추측하지 않았다 — 숫자 코드 우연 일치(P36). 원본 코드는 SETLE_CD 로 보존</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>비영 6/7 (85.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SETLE_CD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.SETLE_CD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.SETLE_CD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>결제수단 원본 코드(degen). 라벨 없는 5종을 잃지 않기 위해 보존한다 — 현업 코드그룹 확인 대상(O45-B)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>비영 40,242,656/40,262,076 (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LAST_PAY_DATE_SK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.LAST_PAY_DATE_SK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>해당 조합의 **최종 납입일** (FK→DIM_DATE). 🔴합계가 아니라 시점 축이다. FMM 은 월 팩트라 일자 분해가 불가하므로 「기준일(납입일)」 요구는 이 뷰에서만 답한다</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>비영 38,392,804/40,262,076 (95.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LAST_PAY_DATE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DIM_DATE.FULL_DATE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>비영 16,436/16,437 (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LAST_BILL_DATE_SK</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.LAST_BILL_DATE_SK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.RQEST_DE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>비영 39,615,364/40,262,076 (98.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>비영 7,749,993/7,925,716 (97.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MEMBER_STATUS_NAME</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>비영 7,925,715/7,925,716 (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MBER_DIV_CD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER.MBER_DIV_CD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MEMBER_TYPE_NAME</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER.SEX</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.SEX</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GENDER_NAME</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER.GENDER_NAME</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ACQ_CAMPAIGN_SK</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_SK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ACQ_BRAND</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_BRAND</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ACQ_CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ACQ_PARENT_CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_PARENT_CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ACQ_PROMO_METHOD_NAME</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_PROMO_METHOD_NAME</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ACQ_MARKETING_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_MARKETING_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>획득 캠페인의 마케팅캠페인(O45 conformed 축). 광고비와 결합할 때 이 축을 쓴다 — 개발캠페인 단위로 내리면 광고비가 복제된다(팬아웃)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ACQ_ORG_SK</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_ORG_SK</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ACQ_DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>🔴**획득(최초개발) 시점 부서**다. 개발실적보고의 「부서」(=사건 부서)와 다르다 — 사건 부서는 WIDE_MEMBER_EVENT.ORG_DEPARTMENT 를 쓴다(O34 _AT_PLEDGE/_AT_EVENT 규약의 재적용)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ACQ_SPONSORSHIP_SK</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_SK</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ACQ_SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ACQ_AGE_BAND</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_AGE_BAND</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ACQ_REGION</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_REGION</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>원천무관(ETL 생성)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BILLED_AMT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.BILLED_AMT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>청구액(원) = SUM(RQEST_AMT). FMM 과 동일 식이므로 전체 합계가 일치해야 한다(기준값 891,959,790,888)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>비영 39,615,189/40,262,076 (98.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PAID_FEE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.PAID_FEE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>납입 총액(원) = 회비 + 기부금. 🔴납부율 분자로 쓰지 말 것(O40) — PAID_FEE_BILLABLE 을 쓴다</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>비영 38,383,610/40,262,076 (95.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PAID_FEE_BILLABLE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.PAID_FEE_BILLABLE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>회비 납입액(원) — 납부율 분자 정본(O40)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>비영 37,739,730/40,262,076 (93.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>UNPAID_BILLED_AMT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.UNPAID_BILLED_AMT</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>미납 청구액(원) — DEC-3 정본 = PAY_STAT_CD IN (F, NULL) 인 청구액. 🔴차감식(청구−납입) 아님. ⚠️조회 시점 스냅샷 — 과거 미납이 이후 납입되면 값이 바뀐다</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>비영 3,489,362/40,262,076 (8.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BILLING_ROWS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.BILLING_ROWS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>집계된 원천 회비행 수. 🔴금액이 아니다 — 「건수」로 쓰지 말 것(정본 (건) 정의는 CONF-2 미결)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>비영 40,262,076/40,262,076 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>UNPAID_FLAG</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.UNPAID_FLAG</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_STAT_CD</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>해당 조합에 미납 청구행이 하나라도 있는가(BOOLOR_AGG). 회원 단위 미납 여부는 WIDE_MEMBER_MONTHLY 의 UNPAID_FLAG_EOM 을 쓴다</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>비영 3,489,366/40,262,076 (8.7%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6423,7 +8338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9365,7 +11280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10247,7 +12162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_AD_BROADCAST" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_AD_BROADCAST_CASE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_AD_DIGITAL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_AD_PERFORMANCE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_BUDGET" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_DEV_ACHIEVEMENT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_AD_COMBINED" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_AD_DIGITAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_AD_PERFORMANCE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_BUDGET" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_EVENT_PARTICIPATION" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_GA_BEHAVIOR" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIDE_MEMBER_EVENT" sheetId="9" state="visible" r:id="rId9"/>
@@ -531,11 +531,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>광고성과 행 식별자(grain) — 코어 WIDE_AD_PERFORMANCE 조인키</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -583,11 +579,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>광고 원천유형 VIDEO/REBROADCAST (본 뷰는 방송 2종만)</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -635,11 +627,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>광고 실적일 YYYYMMDD</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -687,11 +675,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[코어] 광고비(원) — VIDEO=실집행·REBRDC=편성비용</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -739,11 +723,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[코어] 인입콜수</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -791,11 +771,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>시간대</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -843,11 +819,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CM위치 (VIDEO 전용)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -895,11 +867,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>RT(재방송)유형 (REBRDC 전용)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -947,11 +915,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>광고시작시간 (VIDEO 전용)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -999,11 +963,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>광고종료시간 (VIDEO 전용)</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1051,11 +1011,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>송출일 — 실적일(PERF_DATE_SK)과 다를 수 있음</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1103,11 +1059,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>프로그램/편성명</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1155,11 +1107,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>채널사</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1207,11 +1155,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>채널사유형 (VIDEO 전용)</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1259,11 +1203,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SPOT유형 (VIDEO 전용)</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1311,11 +1251,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>🔴 광고 초수 (VIDEO 전용) — **현재 값을 신뢰하지 말 것**(O29). 적재값이 30,000,000/60,000,000/90,000,000 이라 「초」로 읽으면 오답이다(µs 해석 유력하나 미확정·현업 확인 대기). 또한 원천 HH:MM:SS 표기 **32,739행(96.6%)이 TRY_TO_NUMBER 캐스팅에서 무성 소실**됐다 → 유효 커버리지 1,151/36,416=3.2%(파싱 시 93.1% 회복). REBRDC 의 NULL 은 결손이 아니라 원천 부재</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1363,11 +1299,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>요일구분 평일/주말 (VIDEO 전용)</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1415,11 +1347,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>프로그램 시작시간 (VIDEO 전용)</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1467,11 +1395,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>CTV구분 (VIDEO 전용)</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1519,11 +1443,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>방송구분 (REBRDC 전용)</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1571,11 +1491,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>광고횟수</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1623,11 +1539,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>전환콜 (VIDEO 전용) — 인입콜과 별개</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1675,11 +1587,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>개발회원수 (REBRDC 전용) — ⚠️GA 전환이 아님(O16 분리)</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1727,11 +1635,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>개발건수 (REBRDC 전용) — ⚠️GA 전환이 아님(O16 분리)</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1779,11 +1683,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>광고시청률(대행사 산정) — 비가산 N, 재합산 금지</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1831,11 +1731,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>CPC(대행사 산정) — 비가산 N, 재합산 금지</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1875,11 +1771,7 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>DIM_DATE.FULL_DATE — 실적일 일자</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1919,11 +1811,7 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DIM_DATE.YEAR — 실적일 년</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -1963,11 +1851,7 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DIM_DATE.MONTH — 실적일 월</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2007,11 +1891,7 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>DIM_DATE.QUARTER — 실적일 분기</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2051,11 +1931,7 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DIM_DATE.IS_HOLIDAY — 실적일 휴일여부</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2103,11 +1979,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2155,11 +2027,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.MEDIA_NAME — 매체명</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2207,11 +2075,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.CREATIVE — 소재</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2337,11 +2201,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>회비월 YYYYMM (무효/NULL 이면 납입월 폴백, 둘 다 무효면 0=Unknown월 — FMM 과 동일 규칙)</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2389,11 +2249,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FLOOR(MONTH_KEY/100) — 연도</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2441,11 +2297,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MOD(MONTH_KEY,100) — 월</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2589,11 +2441,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>🔴**납입 대상** 후원사업 — 회비 행에 붙은 값이다(원천 SPNSR_BSNS_ID 채움 99.83%·36종). 획득 후원사업(ACQ_SPONSORSHIP_NAME)과 다르다: 한 회원이 여러 후원사업에 낸다(회원-월 조합 37,148,615 → 회원-월-후원사업 39,563,730 = 6.5% 증가). 이것이 이 팩트를 FMM 과 분리한 이유다</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2689,11 +2537,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>회비구분(PM010 실측 확정): 정기·선물금·일시·긴급구호. 🔴기부금 행은 원천이 NULL 이다 — 결측이 아니라 해당없음(P21)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2741,11 +2585,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>납입유형 = 회비/기부금. 🔴납부율·미납 분석은 회비만으로 스코프할 것 — 기부금은 원천에 청구(RQEST_AMT)가 전건 NULL 이라 분모에 들어갈 수 없다(O40)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2841,11 +2681,7 @@
           <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>결제수단 라벨. ⚠️커버리지 99.3%(6종=자동이체·신용카드·네이버페이·회비통장·OCR·휴대폰) — 원천 11종 중 5종(3·10·6·13·7, 225,855행=0.48%)은 **코드그룹 미특정**으로 (미매핑)이다. CRM_CODE 에서 11종을 덮는 그룹이 6개 나왔으나 전부 의미 무관(간사/질병/취미…)이라 추측하지 않았다 — 숫자 코드 우연 일치(P36). 원본 코드는 SETLE_CD 로 보존</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2893,11 +2729,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>결제수단 원본 코드(degen). 라벨 없는 5종을 잃지 않기 위해 보존한다 — 현업 코드그룹 확인 대상(O45-B)</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -2945,11 +2777,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>해당 조합의 **최종 납입일** (FK→DIM_DATE). 🔴합계가 아니라 시점 축이다. FMM 은 월 팩트라 일자 분해가 불가하므로 「기준일(납입일)」 요구는 이 뷰에서만 답한다</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -3378,12 +3206,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3246,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3286,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3326,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3538,12 +3366,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3565,11 +3393,7 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>획득 캠페인의 마케팅캠페인(O45 conformed 축). 광고비와 결합할 때 이 축을 쓴다 — 개발캠페인 단위로 내리면 광고비가 복제된다(팬아웃)</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -3582,12 +3406,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,575,011/1,585,949 (99.3%)</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3446,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,948/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3649,11 +3473,7 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>🔴**획득(최초개발) 시점 부서**다. 개발실적보고의 「부서」(=사건 부서)와 다르다 — 사건 부서는 WIDE_MEMBER_EVENT.ORG_DEPARTMENT 를 쓴다(O34 _AT_PLEDGE/_AT_EVENT 규약의 재적용)</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -3666,12 +3486,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3526,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3566,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3786,12 +3606,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3826,12 +3646,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,574,536/1,585,949 (99.3%)</t>
         </is>
       </c>
     </row>
@@ -3861,11 +3681,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>청구액(원) = SUM(RQEST_AMT). FMM 과 동일 식이므로 전체 합계가 일치해야 한다(기준값 891,959,790,888)</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -3913,11 +3729,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>납입 총액(원) = 회비 + 기부금. 🔴납부율 분자로 쓰지 말 것(O40) — PAID_FEE_BILLABLE 을 쓴다</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -3965,11 +3777,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>회비 납입액(원) — 납부율 분자 정본(O40)</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4017,11 +3825,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>미납 청구액(원) — DEC-3 정본 = PAY_STAT_CD IN (F, NULL) 인 청구액. 🔴차감식(청구−납입) 아님. ⚠️조회 시점 스냅샷 — 과거 미납이 이후 납입되면 값이 바뀐다</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4069,11 +3873,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>집계된 원천 회비행 수. 🔴금액이 아니다 — 「건수」로 쓰지 말 것(정본 (건) 정의는 CONF-2 미결)</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4121,11 +3921,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>해당 조합에 미납 청구행이 하나라도 있는가(BOOLOR_AGG). 회원 단위 미납 여부는 WIDE_MEMBER_MONTHLY 의 UNPAID_FLAG_EOM 을 쓴다</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4251,11 +4047,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>YYYYMM</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4303,11 +4095,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FLOOR(MONTH_KEY/100) — 연도</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4355,11 +4143,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MOD(MONTH_KEY,100) — 월</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4407,11 +4191,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_IRSD</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>불변 회원키(조인용)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4459,11 +4239,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>개발(건) SUM(금액)/10000 (#4·5·149)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4511,11 +4287,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>개발(명) COUNT (#148)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4563,11 +4335,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>중단(건) (#35, FME 롤업)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4615,11 +4383,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>미납(건) (#36)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4667,11 +4431,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>활동(건) (#37·157)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4719,11 +4479,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>활동(명) (#156)</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4771,11 +4527,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>활동누계(건) (#159)</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4823,11 +4575,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>활동누계(명) (#158)</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4875,11 +4623,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>증액(건) (#151)</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4927,11 +4671,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>증액(명) (#150)</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -4979,11 +4719,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>감액(건) SUM(감액금액)/10000 (#38)</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5031,11 +4767,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>이탈(건) SUM(취소+감액)/10000 (신규#20)</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5083,11 +4815,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>연도초 활동회원(건) (#49)</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5135,11 +4863,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>연도말 활동회원(건) (#50)</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5187,11 +4911,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>월말활동회원(건) (#52)</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5239,11 +4959,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>전월말 활동회원(건) (#53)</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5291,11 +5007,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>캠페인별 미납(건) (#83)</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5343,11 +5055,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>회원상태별 미납(건) (#84)</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5395,11 +5103,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>정기회비(원) (#66)</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5447,11 +5151,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>정기회원 일시회비(원) (#67)</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5499,11 +5199,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>일시회원 일시회비(원) (#68)</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5551,11 +5247,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>납입회비(원) (#69·70 단일화)</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5603,11 +5295,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>청구(원) (#71)</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5655,11 +5343,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>인바운드콜수 (overview)</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5707,11 +5391,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>TS콜수 (overview)</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5759,11 +5439,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>개발구분 (#121)</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5811,11 +5487,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>신규여부 (#32)</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5863,11 +5535,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>증액여부 (#33)</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5915,11 +5583,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>재후원여부 (#34)</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -5967,11 +5631,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>캠페인 가입일 (#27)</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6019,11 +5679,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>가입캠페인 중단일 (#26)</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6071,11 +5727,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>후원금액대1 5만 (#72)</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6123,11 +5775,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>후원금액대2 1만 (#73)</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6175,11 +5823,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>후원기간대1 5년 (#74)</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6227,11 +5871,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>후원기간대2 1년 (#75)</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6279,11 +5919,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>후원기간(개월) (#127)</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6331,11 +5967,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>후원기간(년) (#128)</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6383,11 +6015,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>납입개월수 (#129)</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6435,11 +6063,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>신규/기존(시점귀속, #113)</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6487,11 +6111,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>월초 미납회원 여부(=전월말 상태, #80)</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6539,11 +6159,7 @@
           <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>월말 미납회원 여부 (#80)</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6591,11 +6207,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.SEX — 성별 코드 raw(CM013 0~8). 라벨=SEX_NM(원천)·MEMBER_GENDER_NAME(분석)</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6643,11 +6255,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.SEX_NM — CM013 원천 라벨(국내/외국인 축 보존)</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6695,11 +6303,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.GENDER_NAME — 성별 (#130) CM017 분석 라벨: 남자/여자/기타/단체/기업</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6747,11 +6351,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AREA_CD — 지역 코드 raw(CM018 18종 + sentinel '0'). 라벨=MEMBER_REGION</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6799,11 +6399,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.REGION — 지역 (#131) CM018 약칭 라벨(서울/경기/인천…). ⚠️개발약정 **시점 스냅샷**이라 SCD2 버전별로 다를 수 있다(O27). ONCE(일시회원)는 개발약정 부재로 NULL</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6851,11 +6447,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AGE — 연령대 코드 raw(CM014 1~12). 🔴연속형 나이가 아니다(1=10대미만…9=70대이상·10=단체·11=기업·12=기타). 라벨=MEMBER_AGE_BAND</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6903,11 +6495,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AGE_BAND — 연령대 CM014 라벨. ⚠️개발약정 **시점 스냅샷**(O27). ONCE 는 NULL</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -6955,11 +6543,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MBER_STAT_CD — 회원상태 코드 raw(MM010)</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7007,11 +6591,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME — 회원상태 (#132) MM010 라벨: 1활동회원·2~11미납·12후원중단</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7059,11 +6639,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.PREV_MBER_STAT_CD — 상태전이 **이전상태** 코드(MM010). 원천 STATUS_HIST.BF_STAT_CD 100%·12/12 일치. 이력 미보유행은 NULL</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7111,11 +6687,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.PREV_MEMBER_STATUS_NAME — 이전상태 라벨(MM010). 현재상태와 짝지어 전이 분석에 쓴다</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7163,11 +6735,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MBER_DIV_CD — 회원구분 코드 raw(MM018)</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7215,11 +6783,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME — 회원구분 MM018 라벨(개인/기업/단체)</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7267,11 +6831,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.FIRST_JOIN_DATE — 최초가입일 (#28)</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7319,11 +6879,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.FIRST_CAMPAIGN — 최초캠페인 (#29)</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7371,11 +6927,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.JOIN_PATH_CD — 가입경로 코드 raw(MM014)</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7423,11 +6975,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.ENROLL_PATH_NAME — 가입경로 MM014 라벨</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7475,11 +7023,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.FIRST_SPONSORSHIP — 최초후원사업(최소 발생일의 SPNSR_BSNS_ID). ONCE 는 NULL</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7527,11 +7071,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.LAST_STOP_DATE — 최종중단일. 🔴그 버전 시점까지의 as-of max 다(단순 max 는 미래정보 누설). 적중 19.73%</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7579,11 +7119,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK — 캠페인 업무키</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7631,11 +7167,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.BRAND — 공통브랜드 (#117)</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7683,11 +7215,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.PARENT_CAMPAIGN — 공통상위캠페인 (#119)</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7735,11 +7263,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명 (#120)</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7787,11 +7311,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.PROMO_METHOD — 홍보방법 (#118)</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7839,11 +7359,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_TYPE — 캠페인 유형 (#17)</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7891,11 +7407,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK — 후원사업 업무키</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7943,11 +7455,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME — 후원사업 전체 (#123)</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -7995,11 +7503,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_ABBR — 약칭 (#124)</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8047,11 +7551,7 @@
           <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>DIM_PAYMENT.PAYMENT_METHOD — 납입방식 (#125)</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8099,11 +7599,7 @@
           <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>DIM_PAYMENT.SETTLE_METHOD — 결제방식</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8151,11 +7647,7 @@
           <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>DIM_PAYMENT.FEE_TYPE — 회비유형(정기/일시)</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8203,11 +7695,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>DIM_REASON.REASON_CODE — 사유코드</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8255,11 +7743,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>DIM_REASON.REASON_NAME — 중단사유·미납사유 (#162·#82)</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8307,11 +7791,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>DIM_REASON.REASON_TYPE — 중단/미납 구분</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8437,11 +7917,7 @@
           <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>발송일 YYYYMMDD</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8489,11 +7965,7 @@
           <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>발송 대상 회원 (불변키)</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8541,11 +8013,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔴「명」이 아니다 — 발송 플래그(전 행 1). SUM 은 행수=발송 건수이며 실측 38,470,780 로 실제 고유회원 1,031,971 대비 37.3배 과대다(O39). 발송(명)(#85)은 COUNT(DISTINCT MEMBER_DK).</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8593,11 +8061,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>성공수(명) (#86)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8645,11 +8109,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>실패수(명) (#87)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8697,11 +8157,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>오픈(명) (overview)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8749,11 +8205,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>서신참여(명) (#88)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8801,11 +8253,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>서신참여(건) (#89)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8853,11 +8301,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>선물금참여(명) (#90)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8905,11 +8349,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>선물금참여(원) (#91)</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -8957,11 +8397,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>+5일차 서신참여(명) (#139)</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9009,11 +8445,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>+5일차 서신참여(건) (#140)</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9061,11 +8493,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>+5일차 선물금참여(명) (#141)</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9113,11 +8541,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>+5일차 선물금참여(건) (#142)</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9165,11 +8589,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>+5일차 증액참여(명) (#143)</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9217,11 +8637,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>+5일차 증액참여(건) (#144)</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9269,11 +8685,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>+5일차 중단(명) (#145)</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9321,11 +8733,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>+5일차 중단(건) (#146)</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9373,11 +8781,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>서비스(명) (#160)</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9425,11 +8829,7 @@
           <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>서비스(건) (#161)</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9477,11 +8877,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>제목 (#136)</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9529,11 +8925,7 @@
           <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>발송상태 (#138)</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9581,11 +8973,7 @@
           <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>발송상태2</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9633,11 +9021,7 @@
           <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>발송유형</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9685,11 +9069,7 @@
           <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>메일수신여부</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9737,11 +9117,7 @@
           <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>결연회원 중단여부</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9781,11 +9157,7 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>DIM_DATE.FULL_DATE — 실제 일자</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9825,11 +9197,7 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DIM_DATE.YEAR — 년</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9869,11 +9237,7 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DIM_DATE.MONTH — 월</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9913,11 +9277,7 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>DIM_DATE.DAY_OF_WEEK — 요일</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -9957,11 +9317,7 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DIM_DATE.WEEK_OF_YEAR — 주차</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10001,11 +9357,7 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>DIM_DATE.IS_HOLIDAY — 휴일여부</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10053,11 +9405,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.SEX — 성별 코드 raw(CM013 0~8). 라벨=SEX_NM(원천)·MEMBER_GENDER_NAME(분석)</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10105,11 +9453,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.SEX_NM — CM013 원천 라벨(국내/외국인 축 보존)</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10157,11 +9501,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.GENDER_NAME — 성별 (#130) CM017 분석 라벨: 남자/여자/기타/단체/기업</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10209,11 +9549,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AREA_CD — 지역 코드 raw(CM018 18종 + sentinel '0'). 라벨=MEMBER_REGION</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10261,11 +9597,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.REGION — 지역 (#131) CM018 약칭 라벨(서울/경기/인천…). ⚠️개발약정 **시점 스냅샷**이라 SCD2 버전별로 다를 수 있다(O27). ONCE(일시회원)는 개발약정 부재로 NULL</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10313,11 +9645,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AGE — 연령대 코드 raw(CM014 1~12). 🔴연속형 나이가 아니다(1=10대미만…9=70대이상·10=단체·11=기업·12=기타). 라벨=MEMBER_AGE_BAND</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10365,11 +9693,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AGE_BAND — 연령대 CM014 라벨. ⚠️개발약정 **시점 스냅샷**(O27). ONCE 는 NULL</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10417,11 +9741,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MBER_STAT_CD — 회원상태 코드 raw(MM010)</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10469,11 +9789,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME — 회원상태 (#132) MM010 라벨: 1활동회원·2~11미납·12후원중단</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10521,11 +9837,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MBER_DIV_CD — 회원구분 코드 raw(MM018)</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10573,11 +9885,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME — 회원구분 MM018 라벨(개인/기업/단체)</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10625,11 +9933,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>DIM_SEND_TYPE.SEND_GBN_TOP — 발송구분 대 코드 raw. ⚠️이 값은 CRM_CODE.CD_ID(코드그룹 ID) 자체다(MS046 결연·MS047 회원·MS048 회비·MS049 서비스·MS050 사업보고 등 12종). 라벨=SEND_TYPE_L</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10677,11 +9981,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>DIM_SEND_TYPE.SEND_TYPE_L — 발송구분(대) (#133) 라벨: 결연/회비/서비스/사업보고/참여/기타. 커버리지 21.58% · 미매칭은 '(미매핑)'</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10729,11 +10029,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>DIM_SEND_TYPE.SEND_GBN_MID — 발송구분 중 코드 raw. 🔴코드 단독 사용 금지 — 코드 16종에 라벨 26종이 대응한다(부모 대분류에 따라 의미가 달라짐). (대,중) 쌍으로 해석할 것</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10781,11 +10077,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>DIM_SEND_TYPE.SEND_TYPE_M — 발송구분(중) (#134) 라벨: 선물금/신규결연회원발송/회원서신/만18세아동종결/일반퇴소 등</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10833,11 +10125,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>DIM_SEND_TYPE.SEND_GBN_BOT — 발송구분 소 코드 raw. 🔴코드 42종 vs 라벨 56종 → (대,중,소) 경로로만 해석</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10885,11 +10173,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>DIM_SEND_TYPE.SEND_TYPE_S — 발송구분(소) (#135) 라벨: 선물금접수확인/신규결연우편물(PF)/결연100일/서신접수확인/첫출금안내(사단) 등</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10937,11 +10221,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>DIM_SERVICE.SUBTYPE — 발송/참여 subtype</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -10989,11 +10269,7 @@
           <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>DIM_SERVICE.CHANNEL — CRM_UMS / ADMIN</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11041,11 +10317,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK — 캠페인 업무키</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11093,11 +10365,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.BRAND — 공통브랜드 (#117)</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11145,11 +10413,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.PARENT_CAMPAIGN — 공통상위캠페인 (#119)</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11197,11 +10461,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명 (#120)</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11249,11 +10509,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.PROMO_METHOD — 홍보방법 (#118)</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11375,11 +10631,7 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>목표월 YYYYMM</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11423,11 +10675,7 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FLOOR(MONTH_KEY/100) — 연도</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11471,11 +10719,7 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MOD(MONTH_KEY,100) — 월</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11519,11 +10763,7 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>연사업목표(건) (#152)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11567,11 +10807,7 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>추경목표(건) (#153)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11615,11 +10851,7 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>연사업누계목표(건) (#154)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11663,11 +10895,7 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>추경누계목표(건) (#155)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11715,11 +10943,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>DIM_ORG.CORP — 법인 (#114)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11767,11 +10991,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>DIM_ORG.DIVISION — 본부/지부 (#115)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11819,11 +11039,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>DIM_ORG.DEPARTMENT — 부서 (#116)</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11871,11 +11087,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>DIM_ORG.TEAM — 팀</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11923,11 +11135,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK — 후원사업 업무키</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -11975,11 +11183,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME — 후원사업 전체 (#123)</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12027,11 +11231,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK — 캠페인 업무키</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12079,11 +11279,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.BRAND — 공통브랜드 (#117)</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12131,11 +11327,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명 (#120)</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12261,11 +11453,7 @@
           <t>TM_CM_MBER_DVLP_GOAL</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>목표월 YYYYMM</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12313,11 +11501,7 @@
           <t>TM_CM_MBER_DVLP_GOAL</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FLOOR(MONTH_KEY/100) — 연도</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12365,11 +11549,7 @@
           <t>TM_CM_MBER_DVLP_GOAL</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MOD(MONTH_KEY,100) — 월</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12417,11 +11597,7 @@
           <t>TM_CM_MBER_DVLP_GOAL</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>개발구분 (#121 conform)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12469,11 +11645,7 @@
           <t>TM_CM_MBER_DVLP_GOAL</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>회원개발목표(건) (CRM TM_CM_MBER_DVLP_GOAL)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12521,11 +11693,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DIM_ORG.CORP — 법인 (as-was #114)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12573,11 +11741,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>DIM_ORG.DIVISION — 본부/지부 (as-was #115)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12625,11 +11789,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>DIM_ORG.DEPARTMENT — 부서 (as-was #116)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12677,11 +11837,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>DIM_ORG.TEAM — 팀 (as-was)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12807,11 +11963,7 @@
           <t>REBRDC_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>grain 1/2 · 광고성과 행 식별자 — 코어 WIDE_AD_PERFORMANCE 조인키(1:N)</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12859,11 +12011,7 @@
           <t>REBRDC_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>grain 2/2 · 사례 순번 1~3 (원천 CASE1~CASE3 언피벗축)</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12911,11 +12059,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>광고 원천유형 — 본 뷰는 REBROADCAST 만</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -12963,11 +12107,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>광고 실적일 YYYYMMDD</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13015,11 +12155,7 @@
           <t>REBRDC_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>사례 사업구분</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13067,11 +12203,7 @@
           <t>REBRDC_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>사례 가족유형</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13119,11 +12251,7 @@
           <t>REBRDC_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>사례 어필포인트</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13171,11 +12299,7 @@
           <t>REBRDC_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>사례구분</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13223,11 +12347,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>RT(재방송)유형 — 위성 FAD_B 에서 동반</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13275,11 +12395,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>프로그램/편성명 — 위성 FAD_B 에서 동반</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13327,11 +12443,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>채널사 — 위성 FAD_B 에서 동반</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13379,11 +12491,7 @@
           <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>송출일 — 위성 FAD_B 에서 동반</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13423,11 +12531,7 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>DIM_DATE.FULL_DATE — 실적일 일자</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13467,11 +12571,7 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>DIM_DATE.YEAR — 실적일 년</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13511,11 +12611,7 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>DIM_DATE.MONTH — 실적일 월</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13555,11 +12651,7 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>DIM_DATE.QUARTER — 실적일 분기</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13607,11 +12699,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13639,6 +12727,2528 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WIDE_마트</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>WIDE_컬럼</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>GOLD_원천(테이블.컬럼)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SILVER_원천(테이블.컬럼)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BRONZE_원천(테이블)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>업무_의미(배포 COMMENT)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>WIDE→GOLD_확정도</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>계보_확정도</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>상태_근거(실측)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AD_PERF_DK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_PERF_DK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.AD_PERF_DK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>비영 243,545/243,545 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PERF_DATE_SK</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.PERF_DATE_SK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.AD_DATE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>비영 243,545/243,545 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_SK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.CAMPAIGN_SK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.AD_DATE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>전건 0 (비영 0/243,545) — 설계O·값 미주입</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MKTG_CAMPAIGN_SK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.MKTG_CAMPAIGN_SK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.AD_SOURCE_TYPE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>비영 218,402/243,545 (89.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AD_CREATIVE_SK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_CREATIVE_SK</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.AD_DATE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>전건 0 (비영 0/243,545) — 설계O·값 미주입</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DEVICE_SK</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.DEVICE_SK</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GA4_DEVICE.DEVICE_TYPE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>컬럼확정(2단)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>비영 243,545/243,545 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AD_COST</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_COST</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.AD_COST</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>비영 231,012/243,545 (94.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.IMPRESSION_CNT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>비영 196,572/243,545 (80.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CLICKS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.CLICKS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.CLICK_CNT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>비영 173,825/243,545 (71.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INBOUND_CALL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.INBOUND_CALL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.INBOUND_CALL_CNT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>비영 21,455/243,545 (8.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GA_CONV_MEMBERS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.GA_CONV_MEMBERS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.CONV_MEMBER_CNT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>비영 45,823/243,545 (18.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GA_CONV_CNT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.GA_CONV_CNT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.CONV_UNIT_CNT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>비영 12,753/243,545 (5.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DAY_OF_WEEK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.DAY_OF_WEEK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.AD_DATE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>비영 243,545/243,545 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WEEK_OF_YEAR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.WEEK_OF_YEAR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.AD_DATE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>비영 243,545/243,545 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AD_SOURCE_TYPE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_SOURCE_TYPE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.AD_SOURCE_TYPE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>비영 243,545/243,545 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PAGE_TYPE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.PAGE_TYPE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.PAGE_TYPE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>비영 541/205,059 (0.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AD_GROUP_NM</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.AD_GROUP_NM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.AD_GROUP_NM</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>비영 893/205,059 (0.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GROUP_DIV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.GROUP_DIV</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.GROUP_DIV</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>비영 782/205,059 (0.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CREATIVE_TYPE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.CREATIVE_TYPE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.CREATIVE_TYPE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>비영 84,326/205,059 (41.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AD_TYPE_NM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.AD_TYPE_NM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.AD_TYPE_NM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>비영 205,059/205,059 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>READ_CNT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.READ_CNT</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.READ_CNT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>비영 5,260/205,059 (2.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MEDIA_POTENTIAL_CUST_CNT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.MEDIA_POTENTIAL_CUST_CNT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.MEDIA_POTENTIAL_CUST_CNT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>전건 NULL (0/205,059)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CRM_DEV_CNT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.CRM_DEV_CNT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.CRM_DEV_CNT</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>비영 42,034/205,059 (20.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CTR_SRC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.CTR_SRC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.CTR_SRC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>비영 10,978/205,059 (5.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CVR_SRC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.CVR_SRC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.CVR_SRC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>비영 2,900/205,059 (1.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CPC_SRC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.CPC_SRC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.CPC_SRC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>비영 11,510/205,059 (5.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CPM_SRC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.CPM_SRC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.CPM_SRC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>비영 12,569/205,059 (6.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CPA_SRC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.CPA_SRC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.CPA_SRC</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>비영 3,319/205,059 (1.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DEV_UNIT_PRICE_SRC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.DEV_UNIT_PRICE_SRC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.DEV_UNIT_PRICE_SRC</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>비영 3,319/205,059 (1.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>VTR_SRC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FACT_AD_DIGITAL.VTR_SRC</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_DIGITAL.VTR_SRC</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>비영 5,260/205,059 (2.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TIME_BAND</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.TIME_BAND</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.TIME_BAND</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>비영 37,218/38,486 (96.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CM_POSITION</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.CM_POSITION</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.CM_POSITION</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>비영 32,840/38,486 (85.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RT_TYPE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.RT_TYPE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.RT_TYPE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>비영 2,070/38,486 (5.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AD_START_TIME</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.AD_START_TIME</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.AD_START_TIME</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>비영 33,843/38,486 (87.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AD_END_TIME</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.AD_END_TIME</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.AD_END_TIME</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>비영 15,203/38,486 (39.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BROADCAST_DATE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.BROADCAST_DATE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.BROADCAST_DATE</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>비영 38,486/38,486 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PROGRAM_NM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.PROGRAM_NM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.PROGRAM_NM</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>비영 36,097/38,486 (93.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CHANNEL_COMPANY</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.CHANNEL_COMPANY</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.CHANNEL_COMPANY</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>비영 38,486/38,486 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CHANNEL_COMPANY_TYPE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.CHANNEL_COMPANY_TYPE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.CHANNEL_COMPANY_TYPE</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>비영 36,384/38,486 (94.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SPOT_TYPE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.SPOT_TYPE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.SPOT_TYPE</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>비영 14,199/38,486 (36.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DURATION_SEC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.DURATION_SEC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.DURATION_SEC</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>비영 32,739/38,486 (85.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DAY_DIV</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.DAY_DIV</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.DAY_DIV</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>비영 35,148/38,486 (91.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PRG_START_TIME</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.PRG_START_TIME</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.PRG_START_TIME</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>비영 33,024/38,486 (85.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CTV_DIV</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.CTV_DIV</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.CTV_DIV</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>비영 2,170/38,486 (5.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BRDC_DIV</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.BRDC_DIV</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.BRDC_DIV</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>비영 237/38,486 (0.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AD_CNT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.AD_CNT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.AD_CNT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>비영 37,295/38,486 (96.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CONV_CALL_CNT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.CONV_CALL_CNT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.CONV_CALL_CNT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>전건 NULL (0/38,486)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DVLP_MEMBER_CNT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.DVLP_MEMBER_CNT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.DVLP_MEMBER_CNT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>비영 2,025/38,486 (5.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DVLP_CNT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.DVLP_CNT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.DVLP_CNT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>비영 2,026/38,486 (5.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BRDC_AD_VIEW_RT_SRC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.AD_VIEW_RT_SRC</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.AD_VIEW_RT_SRC</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>비영 13,988/38,486 (36.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BRDC_CPC_SRC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FACT_AD_BROADCAST.CPC_SRC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_BROADCAST.CPC_SRC</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>비영 17,834/38,486 (46.3%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13737,11 +15347,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>광고성과 행 식별자(grain) — 코어 WIDE_AD_PERFORMANCE 조인키</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13789,11 +15395,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>광고 원천유형 — 본 뷰는 DIGITAL 만</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13841,11 +15443,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>광고 실적일 YYYYMMDD</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13893,11 +15491,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>[코어] GA 광고비(원)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13945,11 +15539,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>[코어] 노출수 — CTR 분모</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -13997,11 +15587,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>[코어] 클릭수 — CTR 분자</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14049,11 +15635,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[코어] GA전환수(명) — CVR 분자(O16 교정 후 디지털 전용)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14101,11 +15683,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>[코어] GA전환수(건/VU) — CPA 분모(O16 교정 후 디지털 전용)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14153,11 +15731,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>페이지유형</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14205,11 +15779,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>광고그룹명</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14257,11 +15827,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>그룹구분</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14309,11 +15875,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>소재유형(원천 표기)</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14361,11 +15923,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>광고유형명(대행사 표기) — ⚠️AD_SOURCE_TYPE 과 다른 개념</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14413,11 +15971,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>읽음수</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14465,11 +16019,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>매체 잠재고객수</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14517,11 +16067,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CRM 개발건수</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14569,11 +16115,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>CTR(대행사 산정) — 비가산 N. DW 재계산=SUM(CLICKS)/SUM(IMPRESSIONS)</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14621,11 +16163,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>CVR(대행사 산정) — 비가산 N. DW 재계산=SUM(GA_CONV_MEMBERS)/SUM(CLICKS)</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14673,11 +16211,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>CPC(대행사 산정) — 비가산 N. DW 재계산=SUM(AD_COST)/SUM(CLICKS)</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14725,11 +16259,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>CPM(대행사 산정) — 비가산 N. DW 재계산=SUM(AD_COST)/SUM(IMPRESSIONS)*1000</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14777,11 +16307,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>CPA(대행사 산정) — 비가산 N. DW 재계산=SUM(AD_COST)/SUM(GA_CONV_CNT)</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14829,11 +16355,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>개발단가(대행사 산정) — 비가산 N</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14881,11 +16403,7 @@
           <t>DGT_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VTR(대행사 산정) — 비가산 N, base 부재로 재계산 불가</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14925,11 +16443,7 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>DIM_DATE.FULL_DATE — 실적일 일자</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -14969,11 +16483,7 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>DIM_DATE.YEAR — 실적일 년</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15013,11 +16523,7 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>DIM_DATE.MONTH — 실적일 월</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15057,11 +16563,7 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>DIM_DATE.QUARTER — 실적일 분기</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15101,11 +16603,7 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DIM_DATE.IS_HOLIDAY — 실적일 휴일여부</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15153,11 +16651,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15205,11 +16699,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.MEDIA_NAME — 매체명</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15257,11 +16747,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.CREATIVE — 소재</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15305,11 +16791,7 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>DIM_DEVICE.DEVICE_TYPE — M / PC (디지털은 기기 실존)</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15336,7 +16818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15435,11 +16917,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>광고성과 행 식별자(grain) — 위성 뷰 조인키</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15487,11 +16965,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>광고 실적일 YYYYMMDD</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15539,11 +17013,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>광고비(원)</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15591,11 +17061,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>노출수(디지털 전용)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15643,11 +17109,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>클릭수(디지털 전용)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15695,11 +17157,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>인입콜수</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15747,11 +17205,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>GA전환수(명) — 디지털 전용(O16 교정: 재방송 개발실적 제외)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15799,11 +17253,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>GA전환수(건/VU) — 디지털 전용(O16 교정: 재방송 개발실적 제외)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15851,11 +17301,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>요일(팩트 degen)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15903,11 +17349,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>주차(팩트 degen)</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15955,11 +17397,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>광고 원천유형 DIGITAL/VIDEO/REBROADCAST — 출처 명시축(팩트 degen, DEC-8)</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -15999,11 +17437,7 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>DIM_DATE.FULL_DATE — 실적일 일자</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16043,11 +17477,7 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>DIM_DATE.YEAR — 실적일 년</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16087,11 +17517,7 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>DIM_DATE.MONTH — 실적일 월</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16131,11 +17557,7 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>DIM_DATE.QUARTER — 실적일 분기</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16175,11 +17597,7 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>DIM_DATE.IS_HOLIDAY — 실적일 휴일여부</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16227,11 +17645,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK — 캠페인 업무키</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16279,11 +17693,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.BRAND — 공통브랜드 (#117)</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16331,11 +17741,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.PARENT_CAMPAIGN — 공통상위캠페인 (#119)</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16383,11 +17789,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명 (#120)</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16435,11 +17837,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.PROMO_METHOD — 홍보방법 (#118)</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16487,11 +17885,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_TYPE — 캠페인 유형 (#17)</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16539,11 +17933,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.AD_CREATIVE_BK — 광고소재 업무키</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16591,11 +17981,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.MEDIA_NAME — 매체명 (#11)</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16643,11 +18029,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.PLATFORM — 플랫폼 (#12)</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16695,11 +18077,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.PLATFORM_TYPE — 플랫폼/매체유형 (#13)</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16747,11 +18125,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.CREATIVE — 소재 (#20)</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16799,11 +18173,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.AD_TYPE — 소재 광고유형 (⚠️AD_SOURCE_TYPE 과 다른 개념)</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16851,11 +18221,7 @@
           <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DIM_AD_CREATIVE.TARGET_GROUP — 타겟그룹</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16899,11 +18265,7 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>DIM_DEVICE.DEVICE_TYPE — PC / M / (해당없음)방송 / (unknown)</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16947,11 +18309,7 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DIM_DEVICE.DEVICE_SCOPE_DESC — 기기 멤버 의미 자기설명(DEC-10)</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -16978,7 +18336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17077,11 +18435,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>예산월 YYYYMM</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17129,11 +18483,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FLOOR(MONTH_KEY/100) — 연도</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17181,11 +18531,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MOD(MONTH_KEY,100) — 월</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17233,11 +18579,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>편성예산(월, 원)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17285,11 +18627,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>편성예산(연, 원)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17337,11 +18675,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>집행예산(ERP 월, 원)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17389,11 +18723,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>집행예산(추정, 원)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17441,11 +18771,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>모금성비용(원)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17493,11 +18819,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>광고비(원)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17545,11 +18867,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>DIM_ORG.CORP — 법인 (as-was #114)</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17597,11 +18915,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>DIM_ORG.DIVISION — 본부/지부 (as-was #115)</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17649,11 +18963,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>DIM_ORG.DEPARTMENT — 부서 (as-was #116)</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17701,11 +19011,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>DIM_ORG.TEAM — 팀 (as-was)</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17753,11 +19059,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>DIM_BUDGET_ITEM.BUDGET_ITEM_NAME — 세세목명</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17805,11 +19107,7 @@
           <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>DIM_BUDGET_ITEM.BUDGET_CATEGORY — 예산구분</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17857,11 +19155,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK — 캠페인 업무키</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17909,11 +19203,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.BRAND — 공통브랜드 (#117)</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -17961,11 +19251,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명 (#120)</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -18013,11 +19299,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK — 후원사업 업무키</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -18065,11 +19347,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME — 후원사업 전체 (#123)</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -18088,892 +19366,6 @@
       <c r="J21" t="inlineStr">
         <is>
           <t>비영 51/51 (100%)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>WIDE_마트</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>WIDE_컬럼</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>GOLD_원천(테이블.컬럼)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SILVER_원천(테이블.컬럼)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>BRONZE_원천(테이블)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>업무_의미(배포 COMMENT)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>WIDE→GOLD_확정도</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>계보_확정도</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>상태_근거(실측)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MONTH_KEY</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>FACT_TARGET_DEV.MONTH_KEY</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CRM_DEV_TARGET.STDR_MT</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TM_CM_MBER_DVLP_GOAL</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>목표·실적 공통 월키 YYYYMM (월 conform 축)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CTE경유·동명대조</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>컬럼확정</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>비영 25,344/25,344 (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CAL_YEAR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FLOOR(MONTH_KEY/100) — 연도</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CAL_MONTH</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MOD(MONTH_KEY,100) — 월</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ORG_SK</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DIM_ORG.ORG_SK</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CRM_ORG.DEPT_ID</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TM_CM_DEPT_INFO</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>조직 대리키 (FK→DIM_ORG). 실적측은 실적부서(ACMSLT_DEPT_CD) 기준</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CTE경유·다중후보(DIM_ORG,FACT_MEMBER_EVENT,FACT_TARGET_DEV)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>컬럼확정</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>비영 1,314/1,315 (99.9%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ORG_DEPARTMENT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>부서명 (정본 #116) — 장표 첫 축. DIM_ORG.DEPARTMENT</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ORG_DIVISION</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DIM_ORG.DIVISION — 실적지부. ⚠️산출규칙 미확정으로 전건 NULL (CONF-4)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ORG_TEAM</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>DIM_ORG.TEAM — 팀. ⚠️보류로 전건 NULL (CONF-4)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ORG_CORP</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>DIM_ORG.CORP — 법인. ⚠️부서 차원에서 산출 불가로 전건 NULL (CONF-4)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DEV_TYPE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FACT_TARGET_DEV.DEV_TYPE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CRM_DEV_TARGET.MBER_DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TM_CM_MBER_DVLP_GOAL</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>개발구분 코드 (MM015 중 1신규·2증액·4재후원). 정본 공#121 개발 정의와 일치하는 축 — 목표·실적 공통</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>CTE경유·동명대조</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>컬럼확정</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>비영 25,344/25,344 (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DEV_TYPE_NAME</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>개발구분명 (MM015 라벨). 코드는 DEV_TYPE</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GOAL_CNT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>FACT_TARGET_DEV.GOAL_CNT</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CRM_DEV_TARGET.GOAL_CNT</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TM_CM_MBER_DVLP_GOAL</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>월 회원개발목표(건) — 장표 「월 목표」. 원천 CRM TM_CM_MBER_DVLP_GOAL</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>CTE경유·동명대조</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>컬럼확정</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>비영 10,677/25,344 (42.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ACTUAL_CNT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>월 개발실적(건) — 장표 「월 실적」. FME.DEV_CNT 월 롤업(코드 1·2·4 한정)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GOAL_CNT_YTD</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>(누계)월 목표(건) — 당해년 1월~당월 누적. 🔴월 비가산 — 월을 가로질러 합산 금지</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ACTUAL_CNT_YTD</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>(누계)월 실적(건) — 당해년 1월~당월 누적. 🔴월 비가산</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>GOAL_CNT_YEAR</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>연 목표(건) — 당해년 12개월 합. 별도 저장 지표가 아니라 월 목표의 연 합계다. 🔴월 비가산</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ACTUAL_CNT_YEAR</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>연 실적(건) — 당해년 12개월 합. 🔴월 비가산</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HAS_GOAL_ROW</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>목표 **행**의 존재 여부 — 값이 0 이거나 NULL 이어도 TRUE 다. 🔴**달성율 스코프로 쓰지 말 것**: 원천이 2020년부터 부서×월×개발구분 조합을 전량 행 생성하고 미편성분을 0 으로 채우므로 목표 행의 과반이 0 이다. 이 플래그로 분자를 스코프하면 목표 0 행의 실적이 분모 없이 분자에 들어가 달성율이 폭증한다(실측 확인 후 교정). 달성율은 HAS_POSITIVE_GOAL 을 쓴다. 이 컬럼의 용도는 「목표 행 자체가 없는 조합」(=FALSE)을 찾는 것이다</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>HAS_POSITIVE_GOAL</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>🟢**목표가 실제로 편성됐는지**(GOAL_CNT&gt;0) — 달성율 분모·분자 스코프의 **정본**이다. 목표 미편성 부서·월의 실적이 분자에 섞이면 달성율이 조용히 과대해진다(P18·P63). SV_DEV_ACHIEVEMENT.ACHIEVEMENT_RATE 는 이 조건을 식에 못박아 두었으므로 소비 시 별도 필터가 불필요하다. ⚠️FALSE 는 「목표 0 건으로 명시」와 「목표 미입력(원천 NULL)」을 함께 담는다 — 구분이 필요하면 FACT_TARGET_DEV.GOAL_CNT IS NULL 로 팩트에서 본다</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>WIDE_DEV_ACHIEVEMENT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>HAS_ACTUAL</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>실적 발생 여부. FALSE 는 목표만 편성된 월(미래월 포함)이다 — 실적 0 으로 읽되 「미달」로 단정하지 말 것</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>미해석</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19081,11 +19473,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>참여일 YYYYMMDD</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19133,11 +19521,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>참여 회원 (불변키)</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19185,11 +19569,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>총인원 — 🔴 전건 0(미배선). 원인=O28 코드체계 미확정. 0 을 실측값으로 읽지 말 것</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19237,11 +19617,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>대기인원 — 🔴 전건 0(미배선). 원인=O28 코드체계 미확정. 0 을 실측값으로 읽지 말 것</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19289,11 +19665,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>취소인원 — 🔴 전건 0(미배선). 원인=O28 코드체계 미확정. 0 을 실측값으로 읽지 말 것</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19341,11 +19713,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>신청확정인원 — 🔴 전건 0(미배선). 원인=O28 코드체계 미확정. 0 을 실측값으로 읽지 말 것</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19393,11 +19761,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>참여인원 — ⚠️ 행당 상수 1 하드코딩(집계 아님). 취소·불참 행도 1 이므로 상태별 분해 불가</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19445,11 +19809,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>불참인원 — 🔴 전건 0(미배선). 원인=O28 코드체계 미확정. 0 을 실측값으로 읽지 말 것</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19497,11 +19857,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>참여자수 — ⚠️ 행당 상수 1(=행수). 회원 중복 미제거 → 「몇 명」은 COUNT(DISTINCT MEMBER_DK) 사용((행사,회원) 802,298 &lt; 행수 1,134,126)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19549,11 +19905,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>참여횟수 — 🔴 전건 0(미배선). 🟢 원천 `PARTCPT_SEQ` 100% 채움이고 O28 과 무관하게 산출 가능</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19601,11 +19953,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>대기횟수 — 🔴 전건 0(미배선). O28 확정 후 산출</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19653,11 +20001,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>불참횟수 — 🔴 전건 0(미배선). O28 확정 후 산출</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19705,11 +20049,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>누적신청횟수 — 🔴 전건 0(미배선). `PARTCPT_SEQ` 기반 산출 가능(O28 무관)</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19757,11 +20097,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>정기후원금(원)</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19809,11 +20145,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>당첨여부</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19861,11 +20193,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>본인참여여부 — 🔴 전건 NULL(미배선). 원천 대응 미확정</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19913,11 +20241,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>🔴 참여상태 — **코드체계 2개 혼입**(O28). 일반행사=MS304(110=Success·120=Fail·130~220=N_step_right/fail) 707,476행 / 캠페인행사=소정수 1~6 152,046행(의미 미확정·문서20 §I). 판별자=`EVENT_KIND`(단 고아 23.2% 는 `(미매핑)`). **두 체계 합산·GROUP BY 금지** · 한글 비교는 0행 반환</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -19965,11 +20289,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>참여경로</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20017,11 +20337,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>참여채널</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20069,11 +20385,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>증액여부 — 🔴 전건 NULL(미배선). 증액 정소재지는 `FACT_MEMBER_EVENT.DVLP_DIV_CD`(MM015 코드2)</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20121,11 +20433,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>원천 행사키(degenerate key) — 🔴고아 행사 식별자 보존용. 행사 마스터에 없는 53개 행사·263,611행(23.2%)은 EVENT_SK 가 0 으로 뭉개져 서로 구별되지 않았다. ⚠️차원측 EVENT_BK 와 다르다(그쪽은 고아가 '(미매핑)'). 접두 EVENT_/CRMN_ 가 PART_STATUS 코드체계 판별자</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20173,11 +20481,7 @@
           <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>참여 일련번호(degenerate key) — 🔷(PART_EVENT_BK,MEMBER_DK,PARTCPT_SEQ) 가 행을 유일 식별한다. EVENT_SK 로 대체하면 고아 31,831키·63,783행이 충돌. ⚠️전역 순번 아님 · 원천에 음수 20,844행·INT_MIN 1행 → 식별자 전용, 정렬·범위조건 금지</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20217,11 +20521,7 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>DIM_DATE.FULL_DATE — 실제 일자</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20261,11 +20561,7 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>DIM_DATE.YEAR — 년</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20305,11 +20601,7 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>DIM_DATE.MONTH — 월</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20349,11 +20641,7 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>DIM_DATE.DAY_OF_WEEK — 요일</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20393,11 +20681,7 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>DIM_DATE.WEEK_OF_YEAR — 주차</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20437,11 +20721,7 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DIM_DATE.IS_HOLIDAY — 휴일여부</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20489,11 +20769,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.SEX — 성별 코드 raw(CM013 0~8). 라벨=SEX_NM(원천)·MEMBER_GENDER_NAME(분석)</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20541,11 +20817,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.SEX_NM — CM013 원천 라벨(국내/외국인 축 보존)</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20593,11 +20865,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.GENDER_NAME — 성별 (#130) CM017 분석 라벨: 남자/여자/기타/단체/기업</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20645,11 +20913,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AREA_CD — 지역 코드 raw(CM018 18종 + sentinel '0'). 라벨=MEMBER_REGION</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20697,11 +20961,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.REGION — 지역 (#131) CM018 약칭 라벨(서울/경기/인천…). ⚠️개발약정 **시점 스냅샷**이라 SCD2 버전별로 다를 수 있다(O27). ONCE(일시회원)는 개발약정 부재로 NULL</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20749,11 +21009,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AGE — 연령대 코드 raw(CM014 1~12). 🔴연속형 나이가 아니다(1=10대미만…9=70대이상·10=단체·11=기업·12=기타). 라벨=MEMBER_AGE_BAND</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20801,11 +21057,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AGE_BAND — 연령대 CM014 라벨. ⚠️개발약정 **시점 스냅샷**(O27). ONCE 는 NULL</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20853,11 +21105,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MBER_STAT_CD — 회원상태 코드 raw(MM010)</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20905,11 +21153,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME — 회원상태 (#132) MM010 라벨: 1활동회원·2~11미납·12후원중단</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -20957,11 +21201,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MBER_DIV_CD — 회원구분 코드 raw(MM018)</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21009,11 +21249,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME — 회원구분 MM018 라벨(개인/기업/단체)</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21061,11 +21297,7 @@
           <t>TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>DIM_EVENT.EVENT_BK — 행사 업무키</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21113,11 +21345,7 @@
           <t>TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>DIM_EVENT.EVENT_KIND — 🔴 행사종류 코드 raw(`EVENT`=일반행사 / `CRMN`=캠페인행사). ⚠️종전 COMMENT 「온라인/오프라인」 은 **거짓**이었다(실측 도메인 EVENT 376·CRMN 3,410·NULL 1) → 그 값으로 필터하면 0행 반환. 라벨=`EVENT_KIND_NAME`. 🔷 이 컬럼이 `PART_STATUS` 코드체계 판별자다</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21165,11 +21393,7 @@
           <t>TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>DIM_EVENT.EVENT_CATEGORY — 행사구분</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21217,11 +21441,7 @@
           <t>TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>DIM_EVENT.EVENT_NAME — 행사명</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21269,11 +21489,7 @@
           <t>TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>DIM_EVENT.EVENT_START_DATE — 행사기간 시작</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21321,11 +21537,7 @@
           <t>TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>DIM_EVENT.EVENT_END_DATE — 행사기간 종료</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21373,11 +21585,7 @@
           <t>TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>DIM_EVENT.APPLY_CHANNEL — 신청경로</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21425,11 +21633,7 @@
           <t>TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>DIM_EVENT.RECRUIT_HEADCOUNT — 행사 모집인원(정원). 채움 88.8%. 🔴**행사 grain 값이다** — 참여행마다 반복되므로 이 뷰에서 SUM 하면 101.0배 과대계상된다(행사 참값 4,513,184). 행사 단위로 MAX/평균 또는 DISTINCT 행사 기준으로만 집계할 것</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21477,11 +21681,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK — 캠페인 업무키</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21529,11 +21729,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.BRAND — 공통브랜드 (#117)</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21581,11 +21777,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명 (#120)</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21633,11 +21825,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK — 후원사업 업무키</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21685,11 +21873,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME — 후원사업 전체 (#123)</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21811,11 +21995,7 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>행동 발생일 YYYYMMDD</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21859,11 +22039,7 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>페이지경로 — 🔴 쿼리문자열 제외됨(산식 = SPLIT_PART(PAGE_LOCATION,「?」,1) · 실측 「?」 포함 0행). 정본 #105「페이지경로+쿼리문자열」 미충족이며 정본 #122 결연아동코드(childnum=) 파생 불가</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21907,11 +22083,7 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>페이지위치 (#106) — 🔴 grain 내 MAX() 대표값(URL 전체 아님). 원천 distinct 75,474종 → GOLD 8,408종만 생존(67,066종·88.9% 소실). childnum 594→352종 · memnum 1,589→680종. 특정 URL 유무 판정 금지</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -21955,11 +22127,7 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>방문수 — 가산(실측 배수 1.0000)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22003,11 +22171,7 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>이벤트수 — 가산(실측 배수 1.0000)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22051,11 +22215,7 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>조회수 — 가산(실측 배수 1.0000)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22099,11 +22259,7 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>세션수 (#97) — 🔴 비가산(non-additive). 산식 = COUNT(DISTINCT USER_PSEUDO_ID||GA_SESSION_ID) 이며 집계 grain 에서 같은 세션이 여러 행에 반복된다. SUM 시 3.15배 과대계상(실측 원천 77,172 → 합계 243,156). 재합산 금지</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22147,11 +22303,7 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>참여세션수 — 🔴 비가산(non-additive). 산식 = COUNT(DISTINCT …) 이며 SUM 시 4.30배 과대계상(실측 원천 37,505 → 합계 161,117). 재합산 금지</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22195,11 +22347,7 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>[비가산] 스크롤깊이 — 재합산 금지</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22243,11 +22391,7 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[비가산] 활성사용자 — 재합산 금지</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22291,11 +22435,7 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[비가산] 총사용자 — 재합산 금지</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22339,11 +22479,7 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[비가산] 평균세션시간 — 재합산 금지 (#98)</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22391,11 +22527,7 @@
           <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[비가산] 이탈율 — 재합산 금지 (#108)</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22439,11 +22571,7 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[비가산] 참여율 — 재합산 금지</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22487,11 +22615,7 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[비가산] 세션당 평균참여시간 — 재합산 금지</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22531,11 +22655,7 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>DIM_DATE.FULL_DATE — 실제 일자</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22575,11 +22695,7 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>DIM_DATE.YEAR — 년</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22619,11 +22735,7 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>DIM_DATE.MONTH — 월</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22663,11 +22775,7 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>DIM_DATE.DAY_OF_WEEK — 요일</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22707,11 +22815,7 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>DIM_DATE.WEEK_OF_YEAR — 주차</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22751,11 +22855,7 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>DIM_DATE.IS_HOLIDAY — 휴일여부</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22803,11 +22903,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER_IDENTITY.MEMBER_DK — 불변 회원키 (매칭분·미매칭 NULL, ⚠️G-5 재검증)</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22855,11 +22951,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER_IDENTITY.MEMBER_NO — 회원번호 (#110)</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22907,11 +22999,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER_IDENTITY.MEMNUM — 🔴 전건 NULL(미배선). 정본 #111. 원천 실재 = SILVER.GA4_EVENT.PAGE_LOCATION 의 memnum=(17,795행·1,589종) — 조회 시 항상 0행</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -22959,11 +23047,7 @@
           <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER_IDENTITY.GA_MEMBER_ID — GA member_id (#112)</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23007,11 +23091,7 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>DIM_GA_EVENT.EVENT_CATEGORY — 이벤트 카테고리 (#99)</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23055,11 +23135,7 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>DIM_GA_EVENT.EVENT_LABEL — 이벤트 라벨 (#100)</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23103,11 +23179,7 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DIM_GA_EVENT.EVENT_ACTION — 이벤트 액션 (#101)</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23151,11 +23223,7 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DIM_GA_SOURCE.UTM_SOURCE — source</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23199,11 +23267,7 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>DIM_GA_SOURCE.UTM_MEDIUM — medium</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23247,11 +23311,7 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DIM_GA_SOURCE.UTM_CONTENT — 세션 수동 광고 콘텐츠 (#103)</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23295,11 +23355,7 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>DIM_GA_SOURCE.UTM_TERM — 세션 수동 검색어 (#104)</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23343,11 +23399,7 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>DIM_GA_SOURCE.SOURCE_MEDIUM — 세션 소스/매체 (#109)</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23391,11 +23443,7 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>DIM_DEVICE.DEVICE_TYPE — PC / M / APP</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23443,11 +23491,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK — 🔴 전건 「(미매핑)」. FACT_GA_BEHAVIOR.CAMPAIGN_SK 가 상수 0 하드코딩이라 캠페인축이 도달 불가하다(실측 distinct 1). GA 캠페인은 SILVER.GA4_EVENT.UTM_CAMPAIGN(244종·채움 88.0%)에 있고 미배선 — 조회 금지</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23495,11 +23539,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.BRAND — 🔴 전건 NULL(센티넬 행). CAMPAIGN_BK 참조 — 조회 금지</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23547,11 +23587,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 🔴 전건 「(미매핑)」. CAMPAIGN_BK 참조 — 조회 금지</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23677,11 +23713,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>사건일 YYYYMMDD</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23729,11 +23761,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>상태전이 대상 회원 (불변키)</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23781,11 +23809,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>원천 계통 구분: DEV=개발원천 / STOP=중단원천. 상태는 DVLP_DIV_NM 참조 (O24)</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23833,11 +23857,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>개발구분코드 raw (정본 MM015: 1신규 2증액 3감액 4재후원 5후원중단). 중단원천 행은 NULL</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23885,11 +23905,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>개발구분명 (신규/증액/감액/재후원/후원중단). ⚠️ '후원중단'은 EVENT_TYPE='STOP'과 동일 사건 중복 → 합산 금지 (O24)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23937,11 +23953,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>후원금액(원) raw — 감액·후원중단은 음수. (건) 지표는 금액÷10,000 (정본 공#38·#151)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -23989,11 +24001,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>개발(건) (#149) — 정본 공#121 = 신규·증액·재후원 한정 (O24 교정)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24041,11 +24049,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>🔴「명」이 아니다 — 개발 사건 플래그(0/1). SUM 은 개발(건)이며 실측 2,291,878 로 실제 고유회원 1,585,923 대비 44.5% 과대다(O39). 개발(명)(#148)은 COUNT(DISTINCT MEMBER_DK). 월 단위는 FACT_MEMBER_MONTHLY.DEV_MEMBERS 사용.</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24093,11 +24097,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>중단(건) (#35)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24145,11 +24145,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>🔴「명」이 아니다 — 중단 사건 플래그(0/1). SUM 은 중단(건)이며 실측 1,038,262 로 실제 고유회원 903,064 대비 15.0% 과대다(O39). 중단(명)은 COUNT(DISTINCT MEMBER_DK).</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24197,11 +24193,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>미납중단(건)</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24249,11 +24241,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>미납중단(명)</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24301,11 +24289,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>가입일</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24353,11 +24337,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>중단일</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24405,11 +24385,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>중단사유</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24457,11 +24433,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>중단채널</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24509,11 +24481,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>중단사유명 (정본 공#162) — MM005 라벨. 코드는 STOP_REASON. 개발원천 행은 개념 부재로 NULL (O25)</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24561,11 +24529,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>중단경로명 — MM287 라벨(SYSTEM/CRM/홈페이지). 코드는 STOP_CHANNEL. 개발원천 행은 NULL (O25)</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24613,11 +24577,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>신규기존</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24665,11 +24625,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>🔴**사건(개발약정) 시점** 연령대 코드 raw(CM014 1~12). 연속형 나이 아님 — 평균 금지. 라벨=AGE_BAND_AT_EVENT. **MEMBER_AGE_CD 와 다른 축**(그쪽은 최근 약정 스냅샷) — 값이 다를 수 있고 이 컬럼이 사건 당시 정확값이다. 중단(STOP)행은 원천 컬럼 부재로 NULL (O35)</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24717,11 +24673,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>🔴**사건 시점** 연령대 라벨(CM014 사전 조인). ✅'10대 미만'이 상위인 것은 오류가 아니다 — 편지쓰기대회 계열 캠페인(희망편지·가족그림편지·세계시민교육편지)이 아동 본인 명의 약정을 맺기 때문이며, 같은 뷰의 캠페인 축과 교차하면 재현된다. 결측·기본값 오염으로 설명 금지(O34-B). MEMBER_AGE_BAND(스냅샷)와 값이 다를 수 있다. STOP 행 NULL (O35)</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24769,11 +24721,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>🔴**사건 시점** 지역 코드 raw(CM018 + 라벨 없는 센티넬 '0'). 라벨=REGION_AT_EVENT. **MEMBER_AREA_CD 와 다른 축**(그쪽은 최근 약정 스냅샷). ⚠️현재 거주지가 아니다 — 원천에 현주소 축이 없다(O34). STOP 행 NULL (O35)</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24821,11 +24769,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>🔴**사건 시점** 지역 라벨(CM018 약칭·지표 공#131). 코드는 AREA_CD_AT_EVENT. 센티넬 '0' 은 사전 라벨이 없어 NULL — '미상'으로 창작하지 않는다. ⚠️현재 거주지 아님(O34) · MEMBER_REGION(스냅샷)과 값이 다를 수 있다. STOP 행 NULL (O35)</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24865,11 +24809,7 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>DIM_DATE.FULL_DATE — 실제 일자</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24909,11 +24849,7 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>DIM_DATE.YEAR — 년</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24953,11 +24889,7 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>DIM_DATE.MONTH — 월</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -24997,11 +24929,7 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>DIM_DATE.DAY_OF_WEEK — 요일</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25041,11 +24969,7 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DIM_DATE.WEEK_OF_YEAR — 주차</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25085,11 +25009,7 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DIM_DATE.QUARTER — 분기</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25129,11 +25049,7 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>DIM_DATE.IS_HOLIDAY — 휴일여부</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25181,11 +25097,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.SEX — 성별 코드 raw(CM013 0~8: 1국내남·2국내여·3외국남·4외국여·5외국기타·6단체·7기업·8기타). 라벨=SEX_NM(원천)·MEMBER_GENDER_NAME(분석)</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25233,11 +25145,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.SEX_NM — CM013 원천 라벨. 국내/외국인 축 보존</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25285,11 +25193,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.GENDER_NAME — 성별 (#130) CM017 분석 라벨: 남자/여자/기타/단체/기업</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25337,11 +25241,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AREA_CD — 지역 코드 raw(CM018 18종 + sentinel '0'). 라벨=MEMBER_REGION</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25389,11 +25289,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.REGION — 지역 (#131) CM018 약칭 라벨(서울/경기/인천…). ⚠️개발약정 **시점 스냅샷**이라 SCD2 버전별로 다를 수 있다(O27). ONCE(일시회원)는 개발약정 부재로 NULL. 🔴 **이 행의 사건 시점 지역이 아니다** — 사건 시점 값은 REGION_AT_EVENT 를 쓸 것(O35)</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25441,11 +25337,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AGE — 연령대 코드 raw(CM014 1~12). 🔴연속형 나이가 아니다(1=10대미만…9=70대이상·10=단체·11=기업·12=기타). 라벨=MEMBER_AGE_BAND</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25493,11 +25385,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.AGE_BAND — 연령대 CM014 라벨. ⚠️개발약정 **시점 스냅샷**(O27). ONCE 는 NULL. 🔴 **이 행의 사건 시점 연령대가 아니다** — 사건 시점 값은 AGE_BAND_AT_EVENT 를 쓸 것(O35)</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25545,11 +25433,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MBER_STAT_CD — 회원상태 코드 raw(MM010). 라벨=MEMBER_STATUS_NAME</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25597,11 +25481,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME — 회원상태 (#132) MM010 라벨</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25649,11 +25529,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.PREV_MBER_STAT_CD — 상태전이 **이전상태** 코드(MM010). 원천 STATUS_HIST.BF_STAT_CD 100%·12/12 일치. 이력 미보유행은 NULL</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25701,11 +25577,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.PREV_MEMBER_STATUS_NAME — 이전상태 라벨(MM010). 현재상태와 짝지어 전이 분석에 쓴다</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25753,11 +25625,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MBER_DIV_CD — 회원구분 코드 raw(MM018). 라벨=MEMBER_TYPE_NAME</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25805,11 +25673,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME — 회원구분 MM018 라벨(개인/기업/단체)</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25857,11 +25721,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.JOIN_PATH_CD — 가입경로 코드 raw(MM014). 라벨=MEMBER_ENROLL_PATH_NAME</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25909,11 +25769,7 @@
           <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>DIM_MEMBER.ENROLL_PATH_NAME — 가입경로 MM014 라벨</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -25961,11 +25817,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK — 캠페인 업무키</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26013,11 +25865,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.BRAND — 공통브랜드 (#117)</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26065,11 +25913,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.PARENT_CAMPAIGN — 공통상위캠페인 (#119)</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26117,11 +25961,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME — 캠페인명 (#120)</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26169,11 +26009,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.PROMO_METHOD — 홍보방법 (#118)</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26221,11 +26057,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_TYPE — 캠페인카테고리 (MM294)</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26273,11 +26105,7 @@
           <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>DIM_CAMPAIGN.INFLOW_PATH — 주요캠페인/개발인입경로 (MM293)</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26325,11 +26153,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK — 후원사업 업무키</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26377,11 +26201,7 @@
           <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME — 후원사업 전체 (#123)</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26429,11 +26249,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>DIM_ORG.CORP — 법인 (as-was #114)</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26481,11 +26297,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>DIM_ORG.DIVISION — 본부/지부 (as-was #115)</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26533,11 +26345,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>DIM_ORG.DEPARTMENT — 부서 (as-was #116). 🔴 **개발(DEV) 사건 전용**(O38): 실적부서(ACMSLT_DEPT_CD) 기준으로 배선됐다. 중단(STOP) 행은 원천이 등록부서만 보유해 역할이 달라 '(미매핑)'으로 나온다 — 「부서별 중단건」으로 읽지 말 것</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26585,11 +26393,7 @@
           <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>DIM_ORG.TEAM — 팀 (as-was)</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26637,11 +26441,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>DIM_REASON.REASON_CODE — 사유코드</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26689,11 +26489,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>DIM_REASON.REASON_NAME — 중단/미납사유</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>직접참조</t>
@@ -26741,11 +26537,7 @@
           <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>DIM_REASON.REASON_TYPE — 사유 코드그룹 ID. ⚠️'중단/미납 구분' 아님 — 실제값은 CRM 코드그룹 ID 336종(O21 교정, 2026-08-03 재확증: 336/336 전건 CRM_CODE.CD_ID 매칭)</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>직접참조</t>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_STAT_CD</t>
+          <t>DIM_MEMBER_CURRENT.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 7,749,993/7,925,716 (97.8%)</t>
+          <t>비영 1,587,342/1,763,065 (90.0%)</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
+          <t>DIM_MEMBER_CURRENT.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 7,925,715/7,925,716 (100.0%)</t>
+          <t>비영 1,763,064/1,763,065 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_DIV_CD</t>
+          <t>DIM_MEMBER_CURRENT.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 1,763,065/1,763,065 (100%)</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
+          <t>DIM_MEMBER_CURRENT.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 1,763,065/1,763,065 (100%)</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX</t>
+          <t>DIM_MEMBER_CURRENT.SEX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 1,762,644/1,763,065 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER_NAME</t>
+          <t>DIM_MEMBER_CURRENT.GENDER_NAME</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 1,762,644/1,763,065 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -9051,22 +9051,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MAIL_RECEIVE_FLAG</t>
+          <t>SEND_STATUS_GROUP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.MAIL_RECEIVE_FLAG</t>
+          <t>FACT_SERVICE_EVENT.SEND_STATUS_GROUP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SEND_CHANNEL</t>
+          <t>CRM_SEND_MEMBER.SEND_STATUS_GROUP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,470,780)</t>
+          <t>비영 20,284,338/38,470,780 (52.7%)</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MEMBER_STOP_FLAG</t>
+          <t>SEND_STATUS_NAME</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.MEMBER_STOP_FLAG</t>
+          <t>FACT_SERVICE_EVENT.SEND_STATUS_NAME</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SEND_CHANNEL</t>
+          <t>CRM_SEND_MEMBER.SEND_STATUS_NAME</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -9130,12 +9130,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,470,780)</t>
+          <t>비영 20,284,338/38,470,780 (52.7%)</t>
         </is>
       </c>
     </row>
@@ -9147,16 +9147,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FULL_DATE</t>
+          <t>SEND_RESULT_CD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIM_DATE.FULL_DATE</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>FACT_SERVICE_EVENT.SEND_RESULT_CD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SEND_RESULT_CD</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
@@ -9165,7 +9173,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9175,7 +9183,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 26,255,375/38,470,780 (68.2%)</t>
         </is>
       </c>
     </row>
@@ -9187,16 +9195,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YEAR</t>
+          <t>SEND_RESULT_GROUP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DIM_DATE.YEAR</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>FACT_SERVICE_EVENT.SEND_RESULT_GROUP</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SEND_RESULT_GROUP</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
@@ -9205,7 +9221,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9215,7 +9231,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 24,853,956/38,470,780 (64.6%)</t>
         </is>
       </c>
     </row>
@@ -9227,16 +9243,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MONTH</t>
+          <t>SEND_RESULT_NAME</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIM_DATE.MONTH</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+          <t>FACT_SERVICE_EVENT.SEND_RESULT_NAME</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SEND_RESULT_NAME</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
@@ -9245,7 +9269,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9255,7 +9279,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 24,853,956/38,470,780 (64.6%)</t>
         </is>
       </c>
     </row>
@@ -9267,16 +9291,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DAY_OF_WEEK</t>
+          <t>MAIL_RECEIVE_FLAG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIM_DATE.DAY_OF_WEEK</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+          <t>FACT_SERVICE_EVENT.MAIL_RECEIVE_FLAG</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SEND_CHANNEL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -9285,17 +9317,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>전건 NULL (0/38,470,780)</t>
         </is>
       </c>
     </row>
@@ -9307,16 +9339,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WEEK_OF_YEAR</t>
+          <t>MEMBER_STOP_FLAG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIM_DATE.WEEK_OF_YEAR</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+          <t>FACT_SERVICE_EVENT.MEMBER_STOP_FLAG</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SEND_CHANNEL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
@@ -9325,17 +9365,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>전건 NULL (0/38,470,780)</t>
         </is>
       </c>
     </row>
@@ -9347,12 +9387,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IS_HOLIDAY</t>
+          <t>FULL_DATE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIM_DATE.IS_HOLIDAY</t>
+          <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -9370,12 +9410,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9387,24 +9427,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>YEAR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.YEAR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
@@ -9413,7 +9445,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -9423,7 +9455,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9435,24 +9467,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SEX_NM</t>
+          <t>MONTH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX_NM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX_NM</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.MONTH</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
@@ -9461,7 +9485,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -9471,7 +9495,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9483,24 +9507,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MEMBER_GENDER_NAME</t>
+          <t>DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER_NAME</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD</t>
-        </is>
-      </c>
+          <t>DIM_DATE.DAY_OF_WEEK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
@@ -9509,7 +9525,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -9519,7 +9535,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9531,24 +9547,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MEMBER_AREA_CD</t>
+          <t>WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AREA_CD</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.AREA_CD</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+          <t>DIM_DATE.WEEK_OF_YEAR</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
@@ -9557,7 +9565,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -9567,7 +9575,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 7,738,245/7,925,716 (97.6%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9579,24 +9587,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MEMBER_REGION</t>
+          <t>IS_HOLIDAY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.REGION</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD</t>
-        </is>
-      </c>
+          <t>DIM_DATE.IS_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
@@ -9605,17 +9605,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 7,681,020/7,925,716 (96.9%)</t>
+          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9627,22 +9627,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_CD</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE</t>
+          <t>DIM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AGE</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 7,738,250/7,925,716 (97.6%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9675,22 +9675,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_BAND</t>
+          <t>SEX_NM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE_BAND</t>
+          <t>DIM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 7,738,250/7,925,716 (97.6%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9723,22 +9723,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MBER_STAT_CD</t>
+          <t>MEMBER_GENDER_NAME</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_STAT_CD</t>
+          <t>DIM_MEMBER.GENDER_NAME</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,749,993/7,925,716 (97.8%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9771,22 +9771,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MEMBER_STATUS_NAME</t>
+          <t>MEMBER_AREA_CD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
+          <t>DIM_MEMBER.AREA_CD</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_MEMBER_DEV.AREA_CD</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,925,715/7,925,716 (100.0%)</t>
+          <t>비영 7,738,245/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -9819,22 +9819,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MBER_DIV_CD</t>
+          <t>MEMBER_REGION</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_DIV_CD</t>
+          <t>DIM_MEMBER.REGION</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_DIV_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 7,681,020/7,925,716 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -9867,22 +9867,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MEMBER_TYPE_NAME</t>
+          <t>MEMBER_AGE_CD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
+          <t>DIM_MEMBER.AGE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER_DEV.AGE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -9898,12 +9898,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 7,738,250/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -9915,22 +9915,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SEND_TYPE_L_CD</t>
+          <t>MEMBER_AGE_BAND</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIM_SEND_TYPE.SEND_GBN_TOP</t>
+          <t>DIM_MEMBER.AGE_BAND</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SEND_GBN_TOP</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 65/66 (98.5%)</t>
+          <t>비영 7,738,250/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -9963,22 +9963,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SEND_TYPE_L</t>
+          <t>MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIM_SEND_TYPE.SEND_TYPE_L</t>
+          <t>DIM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SEND_GBN_TOP_NM</t>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -9994,12 +9994,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 66/66 (100%)</t>
+          <t>비영 7,749,993/7,925,716 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -10011,22 +10011,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SEND_TYPE_M_CD</t>
+          <t>MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIM_SEND_TYPE.SEND_GBN_MID</t>
+          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SEND_GBN_MID</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 65/66 (98.5%)</t>
+          <t>비영 7,925,715/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -10059,22 +10059,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SEND_TYPE_M</t>
+          <t>MBER_DIV_CD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIM_SEND_TYPE.SEND_TYPE_M</t>
+          <t>DIM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SEND_GBN_MID_NM</t>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 66/66 (100%)</t>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
         </is>
       </c>
     </row>
@@ -10107,22 +10107,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SEND_TYPE_S_CD</t>
+          <t>MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIM_SEND_TYPE.SEND_GBN_BOT</t>
+          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SEND_GBN_BOT</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -10138,12 +10138,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 65/66 (98.5%)</t>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
         </is>
       </c>
     </row>
@@ -10155,17 +10155,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SEND_TYPE_S</t>
+          <t>SEND_TYPE_L_CD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIM_SEND_TYPE.SEND_TYPE_S</t>
+          <t>DIM_SEND_TYPE.SEND_GBN_TOP</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SEND_GBN_BOT_NM</t>
+          <t>CRM_SEND_REQUEST.SEND_GBN_TOP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 66/66 (100%)</t>
+          <t>비영 65/66 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -10203,17 +10203,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SERVICE_SUBTYPE</t>
+          <t>SEND_TYPE_L</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIM_SERVICE.SUBTYPE</t>
+          <t>DIM_SEND_TYPE.SEND_TYPE_L</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+          <t>CRM_SEND_REQUEST.SEND_GBN_TOP_NM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 9/11 (81.8%)</t>
+          <t>비영 66/66 (100%)</t>
         </is>
       </c>
     </row>
@@ -10251,17 +10251,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SERVICE_CHANNEL</t>
+          <t>SEND_TYPE_M_CD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIM_SERVICE.CHANNEL</t>
+          <t>DIM_SEND_TYPE.SEND_GBN_MID</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SEND_CHANNEL</t>
+          <t>CRM_SEND_REQUEST.SEND_GBN_MID</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 11/11 (100%)</t>
+          <t>비영 65/66 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -10299,22 +10299,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>SEND_TYPE_M</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_SEND_TYPE.SEND_TYPE_M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>CRM_SEND_REQUEST.SEND_GBN_MID_NM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 66/66 (100%)</t>
         </is>
       </c>
     </row>
@@ -10347,22 +10347,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>SEND_TYPE_S_CD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_SEND_TYPE.SEND_GBN_BOT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_SEND_REQUEST.SEND_GBN_BOT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 65/66 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -10395,22 +10395,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CAMPAIGN_PARENT</t>
+          <t>SEND_TYPE_S</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.PARENT_CAMPAIGN</t>
+          <t>DIM_SEND_TYPE.SEND_TYPE_S</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.UPPER_CMPGN_CD</t>
+          <t>CRM_SEND_REQUEST.SEND_GBN_BOT_NM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -10426,12 +10426,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 66/66 (100%)</t>
         </is>
       </c>
     </row>
@@ -10443,22 +10443,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>SERVICE_SUBTYPE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_SERVICE.SUBTYPE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 9/11 (81.8%)</t>
         </is>
       </c>
     </row>
@@ -10491,22 +10491,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CAMPAIGN_PROMO_METHOD</t>
+          <t>SERVICE_CHANNEL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.PROMO_METHOD</t>
+          <t>DIM_SERVICE.CHANNEL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.PR_MTH_CD</t>
+          <t>CRM_SEND_REQUEST.SEND_CHANNEL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -10522,10 +10522,250 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>비영 11/11 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WIDE_SERVICE_EVENT</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_BK</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>비영 36,144/36,144 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WIDE_SERVICE_EVENT</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_BRAND</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DIM_CAMPAIGN.BRAND</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>비영 34,686/36,144 (96.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WIDE_SERVICE_EVENT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_PARENT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DIM_CAMPAIGN.PARENT_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.UPPER_CMPGN_CD</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>비영 34,686/36,144 (96.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WIDE_SERVICE_EVENT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>비영 36,144/36,144 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WIDE_SERVICE_EVENT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_PROMO_METHOD</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DIM_CAMPAIGN.PROMO_METHOD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.PR_MTH_CD</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>비영 34,686/36,144 (96.0%)</t>
         </is>
@@ -19380,7 +19620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19470,7 +19710,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -19518,7 +19758,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -19566,7 +19806,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -19614,7 +19854,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -19662,7 +19902,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -19710,7 +19950,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -19758,7 +19998,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -19806,7 +20046,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -19854,7 +20094,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -19902,7 +20142,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -19950,7 +20190,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -19998,7 +20238,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -20046,7 +20286,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -20094,7 +20334,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -20142,7 +20382,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -20190,7 +20430,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -20238,7 +20478,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -20286,7 +20526,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -20334,7 +20574,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -20382,7 +20622,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -20415,22 +20655,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PART_EVENT_BK</t>
+          <t>PART_STATUS_GROUP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.EVENT_BK</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_GROUP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.EVENT_KEY</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_GROUP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -20446,12 +20686,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,134,126/1,134,126 (100%)</t>
+          <t>비영 1,122,886/1,134,126 (99.0%)</t>
         </is>
       </c>
     </row>
@@ -20463,22 +20703,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PARTCPT_SEQ</t>
+          <t>PART_STATUS_NAME</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_NAME</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -20494,12 +20734,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,134,126/1,134,126 (100%)</t>
+          <t>비영 1,122,884/1,134,126 (99.0%)</t>
         </is>
       </c>
     </row>
@@ -20511,16 +20751,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FULL_DATE</t>
+          <t>PART_PATH_GROUP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DIM_DATE.FULL_DATE</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.PART_PATH_GROUP</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_GROUP</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
@@ -20529,7 +20777,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -20539,7 +20787,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 1,124,441/1,134,126 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -20551,16 +20799,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YEAR</t>
+          <t>PART_PATH_NAME</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DIM_DATE.YEAR</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.PART_PATH_NAME</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_NM</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
@@ -20569,7 +20825,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -20579,7 +20835,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 1,124,439/1,134,126 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -20591,16 +20847,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MONTH</t>
+          <t>PART_CHANNEL_GROUP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DIM_DATE.MONTH</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_GROUP</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_GROUP</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
@@ -20609,7 +20873,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -20619,7 +20883,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 981,922/1,134,126 (86.6%)</t>
         </is>
       </c>
     </row>
@@ -20631,16 +20895,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DAY_OF_WEEK</t>
+          <t>PART_CHANNEL_NAME</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DIM_DATE.DAY_OF_WEEK</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_NAME</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_NM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
@@ -20649,7 +20921,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -20659,7 +20931,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 981,920/1,134,126 (86.6%)</t>
         </is>
       </c>
     </row>
@@ -20671,16 +20943,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WEEK_OF_YEAR</t>
+          <t>PART_EVENT_BK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIM_DATE.WEEK_OF_YEAR</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_BK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.EVENT_KEY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
@@ -20689,17 +20969,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -20711,16 +20991,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IS_HOLIDAY</t>
+          <t>PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DIM_DATE.IS_HOLIDAY</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
@@ -20729,17 +21017,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -20751,24 +21039,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>FULL_DATE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.FULL_DATE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
@@ -20777,7 +21057,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -20787,7 +21067,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20799,24 +21079,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SEX_NM</t>
+          <t>YEAR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX_NM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX_NM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.YEAR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -20825,7 +21097,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -20835,7 +21107,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20847,24 +21119,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MEMBER_GENDER_NAME</t>
+          <t>MONTH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER_NAME</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD</t>
-        </is>
-      </c>
+          <t>DIM_DATE.MONTH</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
@@ -20873,7 +21137,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -20883,7 +21147,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20895,24 +21159,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MEMBER_AREA_CD</t>
+          <t>DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AREA_CD</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.AREA_CD</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+          <t>DIM_DATE.DAY_OF_WEEK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
@@ -20921,7 +21177,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -20931,7 +21187,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 7,738,245/7,925,716 (97.6%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20943,24 +21199,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MEMBER_REGION</t>
+          <t>WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.REGION</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD</t>
-        </is>
-      </c>
+          <t>DIM_DATE.WEEK_OF_YEAR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
@@ -20969,7 +21217,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -20979,7 +21227,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 7,681,020/7,925,716 (96.9%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20991,24 +21239,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_CD</t>
+          <t>IS_HOLIDAY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.AGE</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+          <t>DIM_DATE.IS_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
@@ -21017,17 +21257,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 7,738,250/7,925,716 (97.6%)</t>
+          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -21039,22 +21279,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_BAND</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE_BAND</t>
+          <t>DIM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -21075,7 +21315,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 7,738,250/7,925,716 (97.6%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21087,17 +21327,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MBER_STAT_CD</t>
+          <t>SEX_NM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_STAT_CD</t>
+          <t>DIM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
+          <t>CRM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -21123,7 +21363,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 7,749,993/7,925,716 (97.8%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21135,22 +21375,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MEMBER_STATUS_NAME</t>
+          <t>MEMBER_GENDER_NAME</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
+          <t>DIM_MEMBER.GENDER_NAME</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -21171,7 +21411,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 7,925,715/7,925,716 (100.0%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21183,22 +21423,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MBER_DIV_CD</t>
+          <t>MEMBER_AREA_CD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_DIV_CD</t>
+          <t>DIM_MEMBER.AREA_CD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_DIV_CD</t>
+          <t>CRM_MEMBER_DEV.AREA_CD</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -21214,12 +21454,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 7,738,245/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21231,12 +21471,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MEMBER_TYPE_NAME</t>
+          <t>MEMBER_REGION</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
+          <t>DIM_MEMBER.REGION</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -21262,12 +21502,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 7,681,020/7,925,716 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -21279,22 +21519,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EVENT_BK</t>
+          <t>MEMBER_AGE_CD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_BK</t>
+          <t>DIM_MEMBER.AGE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_KEY</t>
+          <t>CRM_MEMBER_DEV.AGE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -21310,12 +21550,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 3,787/3,787 (100%)</t>
+          <t>비영 7,738,250/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21327,22 +21567,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EVENT_KIND</t>
+          <t>MEMBER_AGE_BAND</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_KIND</t>
+          <t>DIM_MEMBER.AGE_BAND</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_SOURCE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -21363,7 +21603,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 7,738,250/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21375,22 +21615,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY</t>
+          <t>MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY</t>
+          <t>DIM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_CD</t>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -21411,7 +21651,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 7,749,993/7,925,716 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -21423,22 +21663,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EVENT_NAME</t>
+          <t>MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_NAME</t>
+          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_NM</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -21459,7 +21699,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 7,925,715/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21471,22 +21711,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EVENT_START_DATE</t>
+          <t>MBER_DIV_CD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_START_DATE</t>
+          <t>DIM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CRM_EVENT.STRT_DE</t>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -21502,12 +21742,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 3,785/3,787 (99.9%)</t>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
         </is>
       </c>
     </row>
@@ -21519,22 +21759,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EVENT_END_DATE</t>
+          <t>MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_END_DATE</t>
+          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CRM_EVENT.END_DE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -21550,12 +21790,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 3,785/3,787 (99.9%)</t>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
         </is>
       </c>
     </row>
@@ -21567,22 +21807,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EVENT_APPLY_CHANNEL</t>
+          <t>EVENT_BK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIM_EVENT.APPLY_CHANNEL</t>
+          <t>DIM_EVENT.EVENT_BK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRM_EVENT.END_DE</t>
+          <t>CRM_EVENT.EVENT_KEY</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -21598,12 +21838,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>전건 NULL (0/3,787)</t>
+          <t>비영 3,787/3,787 (100%)</t>
         </is>
       </c>
     </row>
@@ -21615,22 +21855,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EVENT_RECRUIT_HEADCOUNT</t>
+          <t>EVENT_KIND</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
+          <t>DIM_EVENT.EVENT_KIND</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
+          <t>CRM_EVENT.EVENT_SOURCE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -21651,7 +21891,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 3,348/3,787 (88.4%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21663,22 +21903,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_EVENT.EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>CRM_EVENT.EVENT_SOURCE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -21699,7 +21939,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 3,787/3,787 (100%)</t>
         </is>
       </c>
     </row>
@@ -21711,22 +21951,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_EVENT.EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_EVENT.EVENT_DIV_CD</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -21747,7 +21987,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21759,22 +21999,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_EVENT.EVENT_DIV_GROUP</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -21790,12 +22030,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21807,22 +22047,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_EVENT.EVENT_DIV_NM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -21838,12 +22078,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21855,22 +22095,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_NAME</t>
+          <t>EVENT_NAME</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+          <t>DIM_EVENT.EVENT_NAME</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+          <t>CRM_EVENT.EVENT_NM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -21886,10 +22126,442 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>비영 3,786/3,787 (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>EVENT_START_DATE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DIM_EVENT.EVENT_START_DATE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CRM_EVENT.STRT_DE</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>비영 3,785/3,787 (99.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>EVENT_END_DATE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DIM_EVENT.EVENT_END_DATE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CRM_EVENT.END_DE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>비영 3,785/3,787 (99.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>EVENT_APPLY_CHANNEL</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DIM_EVENT.APPLY_CHANNEL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CRM_EVENT.END_DE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>전건 NULL (0/3,787)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>EVENT_RECRUIT_HEADCOUNT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>비영 3,348/3,787 (88.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_BK</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>비영 36,144/36,144 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_BRAND</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DIM_CAMPAIGN.BRAND</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>비영 34,686/36,144 (96.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>비영 36,144/36,144 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_BK</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>비영 51/51 (100%)</t>
         </is>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 231,012/243,545 (94.9%)</t>
+          <t>비영 240,487/255,417 (94.2%)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 21,455/243,545 (8.8%)</t>
+          <t>비영 22,070/255,417 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 37,218/38,486 (96.7%)</t>
+          <t>비영 38,064/39,332 (96.8%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 32,840/38,486 (85.3%)</t>
+          <t>비영 33,621/39,332 (85.5%)</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 2,070/38,486 (5.4%)</t>
+          <t>비영 2,113/39,332 (5.4%)</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 33,843/38,486 (87.9%)</t>
+          <t>비영 34,624/39,332 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 15,203/38,486 (39.5%)</t>
+          <t>비영 15,984/39,332 (40.6%)</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 36,097/38,486 (93.8%)</t>
+          <t>비영 36,921/39,332 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 36,384/38,486 (94.5%)</t>
+          <t>비영 37,172/39,332 (94.5%)</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 14,199/38,486 (36.9%)</t>
+          <t>비영 14,980/39,332 (38.1%)</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 32,739/38,486 (85.1%)</t>
+          <t>비영 32,739/39,332 (83.2%)</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 35,148/38,486 (91.3%)</t>
+          <t>비영 35,951/39,332 (91.4%)</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 33,024/38,486 (85.8%)</t>
+          <t>비영 33,805/39,332 (85.9%)</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 2,170/38,486 (5.6%)</t>
+          <t>비영 2,170/39,332 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 237/38,486 (0.6%)</t>
+          <t>비영 239/39,332 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 37,295/38,486 (96.9%)</t>
+          <t>비영 38,120/39,332 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,486)</t>
+          <t>전건 NULL (0/39,332)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 2,025/38,486 (5.3%)</t>
+          <t>비영 2,071/39,332 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 2,026/38,486 (5.3%)</t>
+          <t>비영 2,072/39,332 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 13,988/38,486 (36.3%)</t>
+          <t>비영 14,410/39,332 (36.6%)</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 17,834/38,486 (46.3%)</t>
+          <t>비영 18,345/39,332 (46.6%)</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 8,715/8,716 (100.0%)</t>
+          <t>비영 9,164/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 8,712/8,716 (100.0%)</t>
+          <t>비영 9,161/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2471,22 +2471,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FEE_DIV_CD</t>
+          <t>SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.FEE_DIV_CD</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.MBRFEE_DIV_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 39,615,365/40,262,076 (98.4%)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FEE_DIV_NAME</t>
+          <t>SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.FEE_DIV_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 39,615,365/40,262,076 (98.4%)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -2567,17 +2567,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PAYMENT_TYPE</t>
+          <t>FEE_DIV_CD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.PAYMENT_TYPE</t>
+          <t>FACT_MEMBER_FEE.FEE_DIV_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAYMENT_TYPE</t>
+          <t>CRM_PAYMENT_BILLING.MBRFEE_DIV_CD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 40,262,076/40,262,076 (100%)</t>
+          <t>비영 39,615,365/40,262,076 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -2615,22 +2615,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PAYMENT_SK</t>
+          <t>FEE_DIV_NAME</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.PAYMENT_SK</t>
+          <t>FACT_MEMBER_FEE.FEE_DIV_NAME</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.MBER_NO</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 40,069,970/40,262,076 (99.5%)</t>
+          <t>비영 39,615,365/40,262,076 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -2663,22 +2663,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PAYMENT_METHOD_NAME</t>
+          <t>PAYMENT_TYPE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.SETTLE_METHOD</t>
+          <t>FACT_MEMBER_FEE.PAYMENT_TYPE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+          <t>CRM_PAYMENT_BILLING.PAYMENT_TYPE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 6/7 (85.7%)</t>
+          <t>비영 40,262,076/40,262,076 (100%)</t>
         </is>
       </c>
     </row>
@@ -2711,17 +2711,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SETLE_CD</t>
+          <t>PAYMENT_SK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.SETLE_CD</t>
+          <t>FACT_MEMBER_FEE.PAYMENT_SK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.SETLE_CD</t>
+          <t>CRM_PAYMENT_BILLING.MBER_NO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 40,242,656/40,262,076 (100.0%)</t>
+          <t>비영 40,069,970/40,262,076 (99.5%)</t>
         </is>
       </c>
     </row>
@@ -2759,22 +2759,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAST_PAY_DATE_SK</t>
+          <t>PAYMENT_METHOD_NAME</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.LAST_PAY_DATE_SK</t>
+          <t>DIM_PAYMENT.SETTLE_METHOD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 38,392,804/40,262,076 (95.4%)</t>
+          <t>비영 6/7 (85.7%)</t>
         </is>
       </c>
     </row>
@@ -2807,16 +2807,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAST_PAY_DATE</t>
+          <t>SETLE_CD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DIM_DATE.FULL_DATE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>FACT_MEMBER_FEE.SETLE_CD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.SETLE_CD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
@@ -2825,7 +2833,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2835,7 +2843,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 40,242,656/40,262,076 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2847,17 +2855,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAST_BILL_DATE_SK</t>
+          <t>LAST_PAY_DATE_SK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.LAST_BILL_DATE_SK</t>
+          <t>FACT_MEMBER_FEE.LAST_PAY_DATE_SK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_DE</t>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2883,7 +2891,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 39,615,364/40,262,076 (98.4%)</t>
+          <t>비영 38,392,804/40,262,076 (95.4%)</t>
         </is>
       </c>
     </row>
@@ -2895,24 +2903,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MBER_STAT_CD</t>
+          <t>LAST_PAY_DATE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.FULL_DATE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 1,587,342/1,763,065 (90.0%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2943,22 +2943,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEMBER_STATUS_NAME</t>
+          <t>LAST_BILL_DATE_SK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.MEMBER_STATUS_NAME</t>
+          <t>FACT_MEMBER_FEE.LAST_BILL_DATE_SK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_PAYMENT_BILLING.RQEST_DE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 1,763,064/1,763,065 (100.0%)</t>
+          <t>비영 39,615,364/40,262,076 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MBER_DIV_CD</t>
+          <t>MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.MBER_DIV_CD</t>
+          <t>DIM_MEMBER_CURRENT.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_DIV_CD</t>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,763,065/1,763,065 (100%)</t>
+          <t>비영 1,587,342/1,763,065 (90.0%)</t>
         </is>
       </c>
     </row>
@@ -3039,22 +3039,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEMBER_TYPE_NAME</t>
+          <t>MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.MEMBER_TYPE_NAME</t>
+          <t>DIM_MEMBER_CURRENT.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3070,12 +3070,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 1,763,065/1,763,065 (100%)</t>
+          <t>비영 1,763,064/1,763,065 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3087,17 +3087,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>MBER_DIV_CD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.SEX</t>
+          <t>DIM_MEMBER_CURRENT.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.SEX</t>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 1,762,644/1,763,065 (100.0%)</t>
+          <t>비영 1,763,065/1,763,065 (100%)</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GENDER_NAME</t>
+          <t>MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.GENDER_NAME</t>
+          <t>DIM_MEMBER_CURRENT.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,762,644/1,763,065 (100.0%)</t>
+          <t>비영 1,763,065/1,763,065 (100%)</t>
         </is>
       </c>
     </row>
@@ -3183,16 +3183,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ACQ_CAMPAIGN_SK</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_SK</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>DIM_MEMBER_CURRENT.SEX</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.SEX</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
@@ -3201,7 +3209,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3211,7 +3219,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,585,945/1,585,949 (100.0%)</t>
+          <t>비영 1,762,644/1,763,065 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3223,16 +3231,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ACQ_BRAND</t>
+          <t>GENDER_NAME</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_BRAND</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>DIM_MEMBER_CURRENT.GENDER_NAME</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
@@ -3241,7 +3257,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3251,7 +3267,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,585,945/1,585,949 (100.0%)</t>
+          <t>비영 1,762,644/1,763,065 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ACQ_CAMPAIGN_NAME</t>
+          <t>ACQ_CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_NAME</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -3286,12 +3302,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 1,585,949/1,585,949 (100%)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3303,12 +3319,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ACQ_PARENT_CAMPAIGN_NAME</t>
+          <t>ACQ_BRAND</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_PARENT_CAMPAIGN_NAME</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_BRAND</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -3343,12 +3359,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ACQ_PROMO_METHOD_NAME</t>
+          <t>ACQ_CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_PROMO_METHOD_NAME</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -3366,12 +3382,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 1,585,945/1,585,949 (100.0%)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3399,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ACQ_MARKETING_CAMPAIGN</t>
+          <t>ACQ_PARENT_CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_MARKETING_CAMPAIGN</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_PARENT_CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -3411,7 +3427,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 1,575,011/1,585,949 (99.3%)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3423,12 +3439,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ACQ_ORG_SK</t>
+          <t>ACQ_PROMO_METHOD_NAME</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_ORG_SK</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_PROMO_METHOD_NAME</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3451,7 +3467,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 1,585,948/1,585,949 (100.0%)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3479,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ACQ_DEPARTMENT</t>
+          <t>ACQ_MARKETING_CAMPAIGN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_DEPARTMENT</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_MARKETING_CAMPAIGN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -3486,12 +3502,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 1,585,949/1,585,949 (100%)</t>
+          <t>비영 1,010,927/1,585,949 (63.7%)</t>
         </is>
       </c>
     </row>
@@ -3503,12 +3519,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ACQ_SPONSORSHIP_SK</t>
+          <t>ACQ_ORG_SK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_SK</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_ORG_SK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -3526,12 +3542,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 1,585,949/1,585,949 (100%)</t>
+          <t>비영 1,585,948/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3559,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ACQ_SPONSORSHIP_NAME</t>
+          <t>ACQ_DEPARTMENT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_NAME</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_DEPARTMENT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -3583,12 +3599,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ACQ_AGE_BAND</t>
+          <t>ACQ_SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_AGE_BAND</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -3623,12 +3639,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ACQ_REGION</t>
+          <t>ACQ_SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_REGION</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -3646,12 +3662,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 1,574,536/1,585,949 (99.3%)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3663,24 +3679,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BILLED_AMT</t>
+          <t>ACQ_AGE_BAND</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.BILLED_AMT</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_AGE_BAND</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
@@ -3689,17 +3697,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 39,615,189/40,262,076 (98.4%)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3711,24 +3719,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PAID_FEE</t>
+          <t>ACQ_REGION</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.PAID_FEE</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_REGION</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 38,383,610/40,262,076 (95.3%)</t>
+          <t>비영 1,574,536/1,585,949 (99.3%)</t>
         </is>
       </c>
     </row>
@@ -3759,17 +3759,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PAID_FEE_BILLABLE</t>
+          <t>BILLED_AMT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.PAID_FEE_BILLABLE</t>
+          <t>FACT_MEMBER_FEE.BILLED_AMT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 37,739,730/40,262,076 (93.7%)</t>
+          <t>비영 39,615,189/40,262,076 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -3807,17 +3807,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UNPAID_BILLED_AMT</t>
+          <t>PAID_FEE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.UNPAID_BILLED_AMT</t>
+          <t>FACT_MEMBER_FEE.PAID_FEE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 3,489,362/40,262,076 (8.7%)</t>
+          <t>비영 38,383,610/40,262,076 (95.3%)</t>
         </is>
       </c>
     </row>
@@ -3855,17 +3855,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BILLING_ROWS</t>
+          <t>PAID_FEE_BILLABLE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.BILLING_ROWS</t>
+          <t>FACT_MEMBER_FEE.PAID_FEE_BILLABLE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 40,262,076/40,262,076 (100%)</t>
+          <t>비영 37,739,730/40,262,076 (93.7%)</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UNPAID_FLAG</t>
+          <t>UNPAID_BILLED_AMT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.UNPAID_FLAG</t>
+          <t>FACT_MEMBER_FEE.UNPAID_BILLED_AMT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_STAT_CD</t>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3938,6 +3938,102 @@
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>비영 3,489,362/40,262,076 (8.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BILLING_ROWS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.BILLING_ROWS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>비영 40,262,076/40,262,076 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>UNPAID_FLAG</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.UNPAID_FLAG</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_STAT_CD</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>비영 3,489,366/40,262,076 (8.7%)</t>
         </is>
@@ -3954,7 +4050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4332,7 +4428,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -4375,12 +4471,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -4423,12 +4519,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -4444,12 +4540,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4567,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -4492,12 +4588,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 38,423,125/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -4519,12 +4615,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -4545,7 +4641,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>전건 NULL (0/40,054,883)</t>
         </is>
       </c>
     </row>
@@ -4567,12 +4663,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -4593,7 +4689,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>전건 NULL (0/40,054,883)</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4711,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -4663,12 +4759,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -4711,12 +4807,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -4759,12 +4855,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -4807,12 +4903,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -4828,12 +4924,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 35,527,740/40,054,883 (88.7%)</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4951,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4876,12 +4972,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 36,348,044/40,054,883 (90.7%)</t>
         </is>
       </c>
     </row>
@@ -4903,12 +4999,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4924,12 +5020,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -4951,12 +5047,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4972,12 +5068,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 37,695,311/40,054,883 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -4999,12 +5095,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -5047,12 +5143,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -5335,12 +5431,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -5383,12 +5479,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -5431,12 +5527,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -5479,12 +5575,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -5527,12 +5623,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -5575,12 +5671,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -5628,7 +5724,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -5719,12 +5815,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -5767,12 +5863,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -5815,12 +5911,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -5863,12 +5959,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -5911,12 +6007,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -5959,12 +6055,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -6007,12 +6103,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -6348,7 +6444,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -6444,7 +6540,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -7020,7 +7116,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -7068,7 +7164,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -7116,7 +7212,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -7137,7 +7233,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7260,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -7185,7 +7281,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7308,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -7233,7 +7329,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7356,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -7281,7 +7377,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7404,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -7329,7 +7425,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7452,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -7377,7 +7473,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>비영 33,892/36,144 (93.8%)</t>
+          <t>비영 33,918/36,164 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -7533,22 +7629,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PAYMENT_METHOD</t>
+          <t>SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.PAYMENT_METHOD</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -7564,12 +7660,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>비영 7/7 (100%)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -7581,22 +7677,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PAYMENT_SETTLE_METHOD</t>
+          <t>SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.SETTLE_METHOD</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -7617,7 +7713,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>비영 6/7 (85.7%)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -7629,17 +7725,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PAYMENT_FEE_TYPE</t>
+          <t>PAYMENT_METHOD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.FEE_TYPE</t>
+          <t>DIM_PAYMENT.PAYMENT_METHOD</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_CD</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7660,12 +7756,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>전건 NULL (0/7)</t>
+          <t>비영 7/7 (100%)</t>
         </is>
       </c>
     </row>
@@ -7677,22 +7773,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REASON_CODE</t>
+          <t>PAYMENT_SETTLE_METHOD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_CODE</t>
+          <t>DIM_PAYMENT.SETTLE_METHOD</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_ID</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -7708,12 +7804,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>비영 5,839/5,839 (100%)</t>
+          <t>비영 6/7 (85.7%)</t>
         </is>
       </c>
     </row>
@@ -7725,22 +7821,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>REASON_NAME</t>
+          <t>PAYMENT_FEE_TYPE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_NAME</t>
+          <t>DIM_PAYMENT.FEE_TYPE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -7756,12 +7852,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>비영 5,839/5,839 (100%)</t>
+          <t>전건 NULL (0/7)</t>
         </is>
       </c>
     </row>
@@ -7773,17 +7869,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>REASON_TYPE</t>
+          <t>REASON_CODE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_TYPE</t>
+          <t>DIM_REASON.REASON_CODE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CRM_CODE.CD_ID</t>
+          <t>CRM_CODE.DTL_CD_ID</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7804,12 +7900,108 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>비영 5,838/5,839 (100.0%)</t>
+          <t>비영 5,854/5,854 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>REASON_NAME</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_NAME</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>비영 5,854/5,854 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CRM_CODE.CD_ID</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>비영 5,853/5,854 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7935,7 +8127,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 38,470,780/38,470,780 (100%)</t>
+          <t>비영 38,467,142/38,467,142 (100%)</t>
         </is>
       </c>
     </row>
@@ -7983,7 +8175,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 38,470,780/38,470,780 (100%)</t>
+          <t>비영 38,467,142/38,467,142 (100%)</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8223,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 38,470,780/38,470,780 (100%)</t>
+          <t>비영 38,467,142/38,467,142 (100%)</t>
         </is>
       </c>
     </row>
@@ -8053,12 +8245,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -8074,12 +8266,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>비영 24,263,968/38,467,142 (63.1%)</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8293,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -8117,17 +8309,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>비영 1,986,871/38,467,142 (5.2%)</t>
         </is>
       </c>
     </row>
@@ -8149,12 +8341,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -8165,17 +8357,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>비영 411,290/38,467,142 (1.1%)</t>
         </is>
       </c>
     </row>
@@ -8197,12 +8389,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -8213,7 +8405,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8223,7 +8415,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8245,12 +8437,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -8261,7 +8453,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8271,7 +8463,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8511,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8559,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8607,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8655,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8703,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8751,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8607,7 +8799,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8847,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8895,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8943,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8991,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8847,7 +9039,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8895,7 +9087,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 36,635,286/38,470,780 (95.2%)</t>
+          <t>비영 36,631,648/38,467,142 (95.2%)</t>
         </is>
       </c>
     </row>
@@ -8943,7 +9135,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 35,751,014/38,470,780 (92.9%)</t>
+          <t>비영 35,747,376/38,467,142 (92.9%)</t>
         </is>
       </c>
     </row>
@@ -8991,7 +9183,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,470,780)</t>
+          <t>전건 NULL (0/38,467,142)</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9231,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 38,470,780/38,470,780 (100%)</t>
+          <t>비영 38,467,142/38,467,142 (100%)</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9279,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 20,284,338/38,470,780 (52.7%)</t>
+          <t>비영 20,284,338/38,467,142 (52.7%)</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9327,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 20,284,338/38,470,780 (52.7%)</t>
+          <t>비영 20,284,338/38,467,142 (52.7%)</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9375,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 26,255,375/38,470,780 (68.2%)</t>
+          <t>비영 26,251,737/38,467,142 (68.2%)</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9423,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 24,853,956/38,470,780 (64.6%)</t>
+          <t>비영 24,850,318/38,467,142 (64.6%)</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9471,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 24,853,956/38,470,780 (64.6%)</t>
+          <t>비영 24,850,318/38,467,142 (64.6%)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9519,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,470,780)</t>
+          <t>전건 NULL (0/38,467,142)</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9567,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,470,780)</t>
+          <t>전건 NULL (0/38,467,142)</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9978,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -9882,7 +10074,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -10554,7 +10746,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -10575,7 +10767,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10794,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -10623,7 +10815,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10842,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -10671,7 +10863,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10890,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -10719,7 +10911,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10938,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -10767,7 +10959,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11660,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -11489,7 +11681,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -11516,7 +11708,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -11537,7 +11729,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11756,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -11585,7 +11777,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12413,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 5,340/5,340 (100%)</t>
+          <t>비영 5,442/5,442 (100%)</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12461,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 5,340/5,340 (100%)</t>
+          <t>비영 5,442/5,442 (100%)</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12509,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12557,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12605,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 5,335/5,340 (99.9%)</t>
+          <t>비영 5,433/5,442 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12653,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 5,260/5,340 (98.5%)</t>
+          <t>비영 5,359/5,442 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12701,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 5,314/5,340 (99.5%)</t>
+          <t>비영 5,413/5,442 (99.5%)</t>
         </is>
       </c>
     </row>
@@ -12557,7 +12749,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 5,302/5,340 (99.3%)</t>
+          <t>비영 5,401/5,442 (99.2%)</t>
         </is>
       </c>
     </row>
@@ -12605,7 +12797,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 2,070/38,486 (5.4%)</t>
+          <t>비영 2,113/39,332 (5.4%)</t>
         </is>
       </c>
     </row>
@@ -12653,7 +12845,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 36,097/38,486 (93.8%)</t>
+          <t>비영 36,921/39,332 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12893,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -12749,7 +12941,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -12936,7 +13128,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -12957,7 +13149,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13275,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13131,7 +13323,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13371,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/243,545) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/255,417) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13419,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 218,402/243,545 (89.7%)</t>
+          <t>비영 192,723/255,417 (75.5%)</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13467,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/243,545) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/255,417) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13492,11 @@
           <t>GA4_DEVICE.DEVICE_TYPE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
@@ -13319,7 +13515,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13563,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 231,012/243,545 (94.9%)</t>
+          <t>비영 240,487/255,417 (94.2%)</t>
         </is>
       </c>
     </row>
@@ -13415,7 +13611,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 196,572/243,545 (80.7%)</t>
+          <t>비영 205,407/255,417 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -13463,7 +13659,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 173,825/243,545 (71.4%)</t>
+          <t>비영 182,977/255,417 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13707,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 21,455/243,545 (8.8%)</t>
+          <t>비영 22,070/255,417 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13755,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 45,823/243,545 (18.8%)</t>
+          <t>비영 47,987/255,417 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -13607,7 +13803,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 12,753/243,545 (5.2%)</t>
+          <t>비영 14,917/255,417 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -13655,7 +13851,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13703,7 +13899,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13751,7 +13947,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13995,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 541/205,059 (0.3%)</t>
+          <t>비영 742/216,085 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -13847,7 +14043,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 893/205,059 (0.4%)</t>
+          <t>비영 1,341/216,085 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -13895,7 +14091,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 782/205,059 (0.4%)</t>
+          <t>비영 1,662/216,085 (0.8%)</t>
         </is>
       </c>
     </row>
@@ -13943,7 +14139,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 84,326/205,059 (41.1%)</t>
+          <t>비영 95,352/216,085 (44.1%)</t>
         </is>
       </c>
     </row>
@@ -13991,7 +14187,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 205,059/205,059 (100%)</t>
+          <t>비영 216,085/216,085 (100%)</t>
         </is>
       </c>
     </row>
@@ -14039,7 +14235,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 5,260/205,059 (2.6%)</t>
+          <t>비영 8,809/216,085 (4.1%)</t>
         </is>
       </c>
     </row>
@@ -14087,7 +14283,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/205,059)</t>
+          <t>전건 NULL (0/216,085)</t>
         </is>
       </c>
     </row>
@@ -14135,7 +14331,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 42,034/205,059 (20.5%)</t>
+          <t>비영 42,034/216,085 (19.5%)</t>
         </is>
       </c>
     </row>
@@ -14183,7 +14379,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 10,978/205,059 (5.4%)</t>
+          <t>비영 18,543/216,085 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -14231,7 +14427,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 2,900/205,059 (1.4%)</t>
+          <t>비영 4,541/216,085 (2.1%)</t>
         </is>
       </c>
     </row>
@@ -14279,7 +14475,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 11,510/205,059 (5.6%)</t>
+          <t>비영 19,462/216,085 (9.0%)</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14523,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 12,569/205,059 (6.1%)</t>
+          <t>비영 21,300/216,085 (9.9%)</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14571,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 3,319/205,059 (1.6%)</t>
+          <t>비영 5,223/216,085 (2.4%)</t>
         </is>
       </c>
     </row>
@@ -14423,7 +14619,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 3,319/205,059 (1.6%)</t>
+          <t>비영 5,223/216,085 (2.4%)</t>
         </is>
       </c>
     </row>
@@ -14471,7 +14667,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 5,260/205,059 (2.6%)</t>
+          <t>비영 8,809/216,085 (4.1%)</t>
         </is>
       </c>
     </row>
@@ -14519,7 +14715,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 37,218/38,486 (96.7%)</t>
+          <t>비영 38,064/39,332 (96.8%)</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14763,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 32,840/38,486 (85.3%)</t>
+          <t>비영 33,621/39,332 (85.5%)</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14811,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 2,070/38,486 (5.4%)</t>
+          <t>비영 2,113/39,332 (5.4%)</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14859,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 33,843/38,486 (87.9%)</t>
+          <t>비영 34,624/39,332 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14907,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 15,203/38,486 (39.5%)</t>
+          <t>비영 15,984/39,332 (40.6%)</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14955,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -14807,7 +15003,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 36,097/38,486 (93.8%)</t>
+          <t>비영 36,921/39,332 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -14855,7 +15051,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -14903,7 +15099,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 36,384/38,486 (94.5%)</t>
+          <t>비영 37,172/39,332 (94.5%)</t>
         </is>
       </c>
     </row>
@@ -14951,7 +15147,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 14,199/38,486 (36.9%)</t>
+          <t>비영 14,980/39,332 (38.1%)</t>
         </is>
       </c>
     </row>
@@ -14999,7 +15195,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 32,739/38,486 (85.1%)</t>
+          <t>비영 32,739/39,332 (83.2%)</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15243,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 35,148/38,486 (91.3%)</t>
+          <t>비영 35,951/39,332 (91.4%)</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15291,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 33,024/38,486 (85.8%)</t>
+          <t>비영 33,805/39,332 (85.9%)</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15339,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 2,170/38,486 (5.6%)</t>
+          <t>비영 2,170/39,332 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -15191,7 +15387,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 237/38,486 (0.6%)</t>
+          <t>비영 239/39,332 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15435,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 37,295/38,486 (96.9%)</t>
+          <t>비영 38,120/39,332 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -15287,7 +15483,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,486)</t>
+          <t>전건 NULL (0/39,332)</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15531,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 2,025/38,486 (5.3%)</t>
+          <t>비영 2,071/39,332 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -15383,7 +15579,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 2,026/38,486 (5.3%)</t>
+          <t>비영 2,072/39,332 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15627,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 13,988/38,486 (36.3%)</t>
+          <t>비영 14,410/39,332 (36.6%)</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15675,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 17,834/38,486 (46.3%)</t>
+          <t>비영 18,345/39,332 (46.6%)</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15801,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 205,059/205,059 (100%)</t>
+          <t>비영 216,085/216,085 (100%)</t>
         </is>
       </c>
     </row>
@@ -15653,7 +15849,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -15701,7 +15897,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -15749,7 +15945,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 231,012/243,545 (94.9%)</t>
+          <t>비영 240,487/255,417 (94.2%)</t>
         </is>
       </c>
     </row>
@@ -15797,7 +15993,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 196,572/243,545 (80.7%)</t>
+          <t>비영 205,407/255,417 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -15845,7 +16041,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 173,825/243,545 (71.4%)</t>
+          <t>비영 182,977/255,417 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -15893,7 +16089,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 45,823/243,545 (18.8%)</t>
+          <t>비영 47,987/255,417 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -15941,7 +16137,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 12,753/243,545 (5.2%)</t>
+          <t>비영 14,917/255,417 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -15989,7 +16185,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 541/205,059 (0.3%)</t>
+          <t>비영 742/216,085 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -16037,7 +16233,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 893/205,059 (0.4%)</t>
+          <t>비영 1,341/216,085 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -16085,7 +16281,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 782/205,059 (0.4%)</t>
+          <t>비영 1,662/216,085 (0.8%)</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16329,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 84,326/205,059 (41.1%)</t>
+          <t>비영 95,352/216,085 (44.1%)</t>
         </is>
       </c>
     </row>
@@ -16181,7 +16377,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 205,059/205,059 (100%)</t>
+          <t>비영 216,085/216,085 (100%)</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16425,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 5,260/205,059 (2.6%)</t>
+          <t>비영 8,809/216,085 (4.1%)</t>
         </is>
       </c>
     </row>
@@ -16277,7 +16473,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전건 NULL (0/205,059)</t>
+          <t>전건 NULL (0/216,085)</t>
         </is>
       </c>
     </row>
@@ -16325,7 +16521,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 42,034/205,059 (20.5%)</t>
+          <t>비영 42,034/216,085 (19.5%)</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16569,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 10,978/205,059 (5.4%)</t>
+          <t>비영 18,543/216,085 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16617,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 2,900/205,059 (1.4%)</t>
+          <t>비영 4,541/216,085 (2.1%)</t>
         </is>
       </c>
     </row>
@@ -16469,7 +16665,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 11,510/205,059 (5.6%)</t>
+          <t>비영 19,462/216,085 (9.0%)</t>
         </is>
       </c>
     </row>
@@ -16517,7 +16713,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 12,569/205,059 (6.1%)</t>
+          <t>비영 21,300/216,085 (9.9%)</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16761,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 3,319/205,059 (1.6%)</t>
+          <t>비영 5,223/216,085 (2.4%)</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16809,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 3,319/205,059 (1.6%)</t>
+          <t>비영 5,223/216,085 (2.4%)</t>
         </is>
       </c>
     </row>
@@ -16661,7 +16857,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 5,260/205,059 (2.6%)</t>
+          <t>비영 8,809/216,085 (4.1%)</t>
         </is>
       </c>
     </row>
@@ -16888,7 +17084,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -16909,7 +17105,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -16957,7 +17153,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 8,715/8,716 (100.0%)</t>
+          <t>비영 9,164/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17005,7 +17201,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 8,712/8,716 (100.0%)</t>
+          <t>비영 9,161/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17030,7 +17226,11 @@
           <t>GA4_DEVICE.DEVICE_TYPE</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
@@ -17175,7 +17375,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17423,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17471,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 231,012/243,545 (94.9%)</t>
+          <t>비영 240,487/255,417 (94.2%)</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17519,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 196,572/243,545 (80.7%)</t>
+          <t>비영 205,407/255,417 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -17367,7 +17567,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 173,825/243,545 (71.4%)</t>
+          <t>비영 182,977/255,417 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17615,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 21,455/243,545 (8.8%)</t>
+          <t>비영 22,070/255,417 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -17463,7 +17663,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 45,823/243,545 (18.8%)</t>
+          <t>비영 47,987/255,417 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -17511,7 +17711,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 12,753/243,545 (5.2%)</t>
+          <t>비영 14,917/255,417 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17759,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -17607,7 +17807,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17855,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -17882,7 +18082,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -17903,7 +18103,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -17930,7 +18130,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -17951,7 +18151,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -17978,7 +18178,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -17999,7 +18199,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18026,7 +18226,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -18047,7 +18247,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18274,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -18095,7 +18295,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18322,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -18143,7 +18343,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 33,892/36,144 (93.8%)</t>
+          <t>비영 33,918/36,164 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -18191,7 +18391,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 8,716/8,716 (100%)</t>
+          <t>비영 9,165/9,165 (100%)</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18439,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 8,715/8,716 (100.0%)</t>
+          <t>비영 9,164/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18287,7 +18487,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 8,715/8,716 (100.0%)</t>
+          <t>비영 9,164/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18335,7 +18535,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>전건 NULL (0/8,716)</t>
+          <t>전건 NULL (0/9,165)</t>
         </is>
       </c>
     </row>
@@ -18383,7 +18583,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 8,712/8,716 (100.0%)</t>
+          <t>비영 9,161/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18431,7 +18631,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 5,112/8,716 (58.7%)</t>
+          <t>비영 5,561/9,165 (60.7%)</t>
         </is>
       </c>
     </row>
@@ -18479,7 +18679,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 NULL (0/8,716)</t>
+          <t>전건 NULL (0/9,165)</t>
         </is>
       </c>
     </row>
@@ -18504,7 +18704,11 @@
           <t>GA4_DEVICE.DEVICE_TYPE</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -18548,7 +18752,11 @@
           <t>GA4_DEVICE.PLATFORM</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
@@ -18693,7 +18901,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 75,996/75,996 (100%)</t>
+          <t>비영 2,964/2,964 (100%)</t>
         </is>
       </c>
     </row>
@@ -18741,7 +18949,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 75,996/75,996 (100%)</t>
+          <t>비영 2,964/2,964 (100%)</t>
         </is>
       </c>
     </row>
@@ -18789,7 +18997,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 75,996/75,996 (100%)</t>
+          <t>비영 2,964/2,964 (100%)</t>
         </is>
       </c>
     </row>
@@ -18837,7 +19045,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 8,066/75,996 (10.6%)</t>
+          <t>비영 424/2,964 (14.3%)</t>
         </is>
       </c>
     </row>
@@ -18885,7 +19093,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 NULL (0/75,996)</t>
+          <t>전건 NULL (0/2,964)</t>
         </is>
       </c>
     </row>
@@ -18933,7 +19141,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 4,899/75,996 (6.4%)</t>
+          <t>비영 662/2,964 (22.3%)</t>
         </is>
       </c>
     </row>
@@ -18981,7 +19189,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 NULL (0/75,996)</t>
+          <t>전건 NULL (0/2,964)</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19237,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 NULL (0/75,996)</t>
+          <t>전건 NULL (0/2,964)</t>
         </is>
       </c>
     </row>
@@ -19077,7 +19285,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 NULL (0/75,996)</t>
+          <t>전건 NULL (0/2,964)</t>
         </is>
       </c>
     </row>
@@ -19317,7 +19525,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 6,318/6,318 (100%)</t>
+          <t>비영 180/180 (100%)</t>
         </is>
       </c>
     </row>
@@ -19365,7 +19573,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 6,317/6,318 (100.0%)</t>
+          <t>비영 179/180 (99.4%)</t>
         </is>
       </c>
     </row>
@@ -19392,7 +19600,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -19413,7 +19621,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19648,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -19461,7 +19669,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19696,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -19509,7 +19717,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -19620,7 +19828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19822,12 +20030,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,134,126) — 설계O·값 미주입</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -19849,7 +20057,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -19865,17 +20073,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,134,126) — 설계O·값 미주입</t>
+          <t>비영 96,679/1,134,126 (8.5%)</t>
         </is>
       </c>
     </row>
@@ -19897,7 +20105,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -19913,17 +20121,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,134,126) — 설계O·값 미주입</t>
+          <t>비영 3,347/1,134,126 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -19945,7 +20153,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -19961,7 +20169,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -19993,7 +20201,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -20009,7 +20217,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -20041,7 +20249,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -20057,17 +20265,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,134,126) — 설계O·값 미주입</t>
+          <t>비영 1,932/1,134,126 (0.2%)</t>
         </is>
       </c>
     </row>
@@ -20089,7 +20297,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -20105,7 +20313,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -20137,7 +20345,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -20153,7 +20361,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -20185,7 +20393,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -20201,7 +20409,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -20233,7 +20441,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -20249,7 +20457,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -20281,7 +20489,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -20297,7 +20505,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -21039,16 +21247,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FULL_DATE</t>
+          <t>PART_EVENT_KIND</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIM_DATE.FULL_DATE</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.DW_SOURCE_TABLE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
@@ -21057,17 +21273,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -21079,16 +21295,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YEAR</t>
+          <t>PART_EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIM_DATE.YEAR</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND_NAME</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.DW_SOURCE_TABLE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -21097,17 +21321,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -21119,12 +21343,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MONTH</t>
+          <t>FULL_DATE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIM_DATE.MONTH</t>
+          <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -21159,12 +21383,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DAY_OF_WEEK</t>
+          <t>YEAR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIM_DATE.DAY_OF_WEEK</t>
+          <t>DIM_DATE.YEAR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -21199,12 +21423,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WEEK_OF_YEAR</t>
+          <t>MONTH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIM_DATE.WEEK_OF_YEAR</t>
+          <t>DIM_DATE.MONTH</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -21239,12 +21463,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IS_HOLIDAY</t>
+          <t>DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DIM_DATE.IS_HOLIDAY</t>
+          <t>DIM_DATE.DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -21262,12 +21486,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21279,24 +21503,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.WEEK_OF_YEAR</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
@@ -21305,7 +21521,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -21315,7 +21531,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21327,24 +21543,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SEX_NM</t>
+          <t>IS_HOLIDAY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX_NM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX_NM</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.IS_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
@@ -21353,17 +21561,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -21375,22 +21583,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MEMBER_GENDER_NAME</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER_NAME</t>
+          <t>DIM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -21423,22 +21631,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MEMBER_AREA_CD</t>
+          <t>SEX_NM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AREA_CD</t>
+          <t>DIM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AREA_CD</t>
+          <t>CRM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -21459,7 +21667,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 7,738,245/7,925,716 (97.6%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21471,12 +21679,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MEMBER_REGION</t>
+          <t>MEMBER_GENDER_NAME</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.REGION</t>
+          <t>DIM_MEMBER.GENDER_NAME</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -21507,7 +21715,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 7,681,020/7,925,716 (96.9%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21519,22 +21727,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_CD</t>
+          <t>MEMBER_AREA_CD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE</t>
+          <t>DIM_MEMBER.AREA_CD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AGE</t>
+          <t>CRM_MEMBER_DEV.AREA_CD</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -21555,7 +21763,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,738,250/7,925,716 (97.6%)</t>
+          <t>비영 7,738,245/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21567,12 +21775,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_BAND</t>
+          <t>MEMBER_REGION</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE_BAND</t>
+          <t>DIM_MEMBER.REGION</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -21603,7 +21811,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,738,250/7,925,716 (97.6%)</t>
+          <t>비영 7,681,020/7,925,716 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -21615,22 +21823,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MBER_STAT_CD</t>
+          <t>MEMBER_AGE_CD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_STAT_CD</t>
+          <t>DIM_MEMBER.AGE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
+          <t>CRM_MEMBER_DEV.AGE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -21651,7 +21859,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 7,749,993/7,925,716 (97.8%)</t>
+          <t>비영 7,738,250/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21663,22 +21871,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MEMBER_STATUS_NAME</t>
+          <t>MEMBER_AGE_BAND</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
+          <t>DIM_MEMBER.AGE_BAND</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -21699,7 +21907,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 7,925,715/7,925,716 (100.0%)</t>
+          <t>비영 7,738,250/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21711,17 +21919,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MBER_DIV_CD</t>
+          <t>MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_DIV_CD</t>
+          <t>DIM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_DIV_CD</t>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -21742,12 +21950,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 7,749,993/7,925,716 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -21759,22 +21967,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MEMBER_TYPE_NAME</t>
+          <t>MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
+          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -21790,12 +21998,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 7,925,715/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21807,22 +22015,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EVENT_BK</t>
+          <t>MBER_DIV_CD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_BK</t>
+          <t>DIM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_KEY</t>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -21843,7 +22051,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 3,787/3,787 (100%)</t>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
         </is>
       </c>
     </row>
@@ -21855,22 +22063,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EVENT_KIND</t>
+          <t>MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_KIND</t>
+          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_SOURCE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -21886,12 +22094,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
         </is>
       </c>
     </row>
@@ -21903,17 +22111,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EVENT_KIND_NAME</t>
+          <t>EVENT_BK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_KIND_NAME</t>
+          <t>DIM_EVENT.EVENT_BK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_SOURCE</t>
+          <t>CRM_EVENT.EVENT_KEY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -21951,17 +22159,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY</t>
+          <t>EVENT_KIND</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY</t>
+          <t>DIM_EVENT.EVENT_KIND</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_CD</t>
+          <t>CRM_EVENT.EVENT_SOURCE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -21999,17 +22207,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY_GROUP</t>
+          <t>EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY_GROUP</t>
+          <t>DIM_EVENT.EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_GROUP</t>
+          <t>CRM_EVENT.EVENT_SOURCE</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -22030,12 +22238,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 3,787/3,787 (100%)</t>
         </is>
       </c>
     </row>
@@ -22047,17 +22255,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY_NAME</t>
+          <t>EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY_NAME</t>
+          <t>DIM_EVENT.EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_NM</t>
+          <t>CRM_EVENT.EVENT_DIV_CD</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -22095,17 +22303,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EVENT_NAME</t>
+          <t>EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_NAME</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_NM</t>
+          <t>CRM_EVENT.EVENT_DIV_GROUP</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -22143,17 +22351,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EVENT_START_DATE</t>
+          <t>EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_START_DATE</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CRM_EVENT.STRT_DE</t>
+          <t>CRM_EVENT.EVENT_DIV_NM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -22179,7 +22387,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 3,785/3,787 (99.9%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -22191,17 +22399,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EVENT_END_DATE</t>
+          <t>EVENT_NAME</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_END_DATE</t>
+          <t>DIM_EVENT.EVENT_NAME</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CRM_EVENT.END_DE</t>
+          <t>CRM_EVENT.EVENT_NM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -22227,7 +22435,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 3,785/3,787 (99.9%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -22239,17 +22447,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EVENT_APPLY_CHANNEL</t>
+          <t>EVENT_START_DATE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DIM_EVENT.APPLY_CHANNEL</t>
+          <t>DIM_EVENT.EVENT_START_DATE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CRM_EVENT.END_DE</t>
+          <t>CRM_EVENT.STRT_DE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -22270,12 +22478,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>전건 NULL (0/3,787)</t>
+          <t>비영 3,785/3,787 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -22287,17 +22495,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EVENT_RECRUIT_HEADCOUNT</t>
+          <t>EVENT_END_DATE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
+          <t>DIM_EVENT.EVENT_END_DATE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
+          <t>CRM_EVENT.END_DE</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -22323,7 +22531,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>비영 3,348/3,787 (88.4%)</t>
+          <t>비영 3,785/3,787 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -22335,22 +22543,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>EVENT_APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_EVENT.APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>CRM_EVENT.END_DE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -22366,12 +22574,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>전건 NULL (0/3,787)</t>
         </is>
       </c>
     </row>
@@ -22383,22 +22591,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>EVENT_RECRUIT_HEADCOUNT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -22419,7 +22627,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 3,348/3,787 (88.4%)</t>
         </is>
       </c>
     </row>
@@ -22431,22 +22639,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -22467,7 +22675,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -22479,22 +22687,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>CAMPAIGN_BRAND</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>DIM_CAMPAIGN.BRAND</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -22510,12 +22718,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -22527,22 +22735,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_NAME</t>
+          <t>CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -22562,6 +22770,102 @@
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>비영 36,164/36,164 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_BK</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>비영 51/51 (100%)</t>
         </is>
@@ -22666,7 +22970,11 @@
           <t>GA4_EVENT.EVENT_DT</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
@@ -22685,7 +22993,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -22710,7 +23018,11 @@
           <t>GA4_EVENT.PAGE_LOCATION</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -22729,7 +23041,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -22754,7 +23066,11 @@
           <t>GA4_EVENT.PAGE_LOCATION</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
@@ -22773,7 +23089,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -22798,7 +23114,11 @@
           <t>GA4_EVENT.EVENT_NAME</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
@@ -22817,7 +23137,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 4,444/68,836 (6.5%)</t>
+          <t>비영 276,949/4,376,339 (6.3%)</t>
         </is>
       </c>
     </row>
@@ -22842,7 +23162,11 @@
           <t>GA4_EVENT.EVENT_NAME</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
@@ -22861,7 +23185,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -22886,7 +23210,11 @@
           <t>GA4_EVENT.EVENT_NAME</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
@@ -22905,7 +23233,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 19,129/68,836 (27.8%)</t>
+          <t>비영 1,179,584/4,376,339 (27.0%)</t>
         </is>
       </c>
     </row>
@@ -22930,7 +23258,11 @@
           <t>GA4_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
@@ -22944,12 +23276,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,338/4,376,339 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -22974,7 +23306,11 @@
           <t>GA4_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
@@ -22993,7 +23329,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 64,450/68,836 (93.6%)</t>
+          <t>비영 4,051,953/4,376,339 (92.6%)</t>
         </is>
       </c>
     </row>
@@ -23018,7 +23354,11 @@
           <t>GA4_EVENT.PERCENT_SCROLLED</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
@@ -23037,7 +23377,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 14,042/68,836 (20.4%)</t>
+          <t>비영 904,700/4,376,339 (20.7%)</t>
         </is>
       </c>
     </row>
@@ -23062,7 +23402,11 @@
           <t>GA4_EVENT.USER_PSEUDO_ID</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
@@ -23081,7 +23425,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 68,507/68,836 (99.5%)</t>
+          <t>비영 2,921,421/4,376,339 (66.8%)</t>
         </is>
       </c>
     </row>
@@ -23106,7 +23450,11 @@
           <t>GA4_EVENT.USER_PSEUDO_ID</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
@@ -23125,7 +23473,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -23150,7 +23498,11 @@
           <t>GA4_EVENT.USER_PSEUDO_ID</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
@@ -23169,7 +23521,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 NULL (0/68,836)</t>
+          <t>전건 NULL (0/4,376,339)</t>
         </is>
       </c>
     </row>
@@ -23196,7 +23548,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>BIGQUERY_REFINED_DATA;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -23217,7 +23569,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 NULL (0/68,836)</t>
+          <t>전건 NULL (0/4,376,339)</t>
         </is>
       </c>
     </row>
@@ -23242,7 +23594,11 @@
           <t>GA4_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
@@ -23261,7 +23617,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 64,450/68,836 (93.6%)</t>
+          <t>비영 4,051,953/4,376,339 (92.6%)</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23642,11 @@
           <t>GA4_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
@@ -23305,7 +23665,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 62,332/68,836 (90.6%)</t>
+          <t>비영 3,973,984/4,376,339 (90.8%)</t>
         </is>
       </c>
     </row>
@@ -23737,7 +24097,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 1,722/1,763,066 (0.1%)</t>
+          <t>비영 70,039/1,763,066 (4.0%)</t>
         </is>
       </c>
     </row>
@@ -23762,7 +24122,11 @@
           <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
@@ -23781,7 +24145,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 4,016/4,017 (100.0%)</t>
+          <t>비영 78,660/78,661 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23806,7 +24170,11 @@
           <t>GA4_EVENT_DIM.EVENT_LABEL</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
@@ -23825,7 +24193,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 4,015/4,017 (100.0%)</t>
+          <t>비영 78,642/78,661 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23850,7 +24218,11 @@
           <t>GA4_EVENT_DIM.EVENT_ACTION</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
@@ -23869,7 +24241,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 4,015/4,017 (100.0%)</t>
+          <t>비영 78,659/78,661 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23894,7 +24266,11 @@
           <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
@@ -23913,7 +24289,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 142/147 (96.6%)</t>
+          <t>비영 672/689 (97.5%)</t>
         </is>
       </c>
     </row>
@@ -23938,7 +24314,11 @@
           <t>GA4_TRAFFIC_SOURCE.UTM_MEDIUM</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -23957,7 +24337,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 140/147 (95.2%)</t>
+          <t>비영 670/689 (97.2%)</t>
         </is>
       </c>
     </row>
@@ -23982,7 +24362,11 @@
           <t>GA4_TRAFFIC_SOURCE.UTM_CONTENT</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
@@ -24001,7 +24385,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 82/147 (55.8%)</t>
+          <t>비영 688/689 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -24026,7 +24410,11 @@
           <t>GA4_TRAFFIC_SOURCE.UTM_TERM</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
@@ -24045,7 +24433,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 81/147 (55.1%)</t>
+          <t>비영 688/689 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -24070,7 +24458,11 @@
           <t>GA4_TRAFFIC_SOURCE.SOURCE_MEDIUM</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
@@ -24089,7 +24481,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 135/147 (91.8%)</t>
+          <t>비영 688/689 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24506,11 @@
           <t>GA4_DEVICE.DEVICE_TYPE</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
@@ -24160,7 +24556,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -24181,7 +24577,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -24208,7 +24604,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -24229,7 +24625,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -24256,7 +24652,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -24277,7 +24673,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -24292,7 +24688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24382,7 +24778,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -24430,7 +24826,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -24478,7 +24874,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -24526,7 +24922,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -24574,7 +24970,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -24622,7 +25018,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -24670,7 +25066,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -24718,7 +25114,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -24766,7 +25162,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -24814,7 +25210,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -24862,7 +25258,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -24910,7 +25306,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -24958,7 +25354,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -25294,7 +25690,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -25390,7 +25786,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -25438,7 +25834,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -25910,7 +26306,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -26006,7 +26402,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -26486,7 +26882,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -26507,7 +26903,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -26534,7 +26930,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -26555,7 +26951,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26582,7 +26978,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -26603,7 +26999,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26630,7 +27026,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -26651,7 +27047,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -26678,7 +27074,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -26699,7 +27095,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26716,7 +27112,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_TYPE</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_CTGR_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -26726,7 +27122,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -26747,7 +27143,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 33,892/36,144 (93.8%)</t>
+          <t>비영 3,580,536/4,633,105 (77.3%)</t>
         </is>
       </c>
     </row>
@@ -26764,7 +27160,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.INFLOW_PATH</t>
+          <t>FACT_MEMBER_EVENT.MBER_INFLOW_PATH_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -26774,7 +27170,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -26795,7 +27191,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 33,915/36,144 (93.8%)</t>
+          <t>비영 3,594,823/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -26807,22 +27203,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>CAMPAIGN_DOMESTIC_OVERSEAS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_TYPE1_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_CAMPAIGN.CMPGN_TYPE1_NM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -26838,12 +27234,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 3,593,246/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -26855,22 +27251,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_NAME</t>
+          <t>CAMPAIGN_BIZ_CASE_TYPE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_TYPE2_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_TYPE2_NM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -26886,12 +27282,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 3,593,246/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -26903,22 +27299,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ORG_CORP</t>
+          <t>CAMPAIGN_MARKETING_CAMPAIGN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DIM_ORG.CORP</t>
+          <t>FACT_MEMBER_EVENT.MKTG_CMPGN_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_CAMPAIGN.MK_CMPGN_NM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -26934,12 +27330,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 2,431,816/4,633,105 (52.5%)</t>
         </is>
       </c>
     </row>
@@ -26951,22 +27347,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ORG_DIVISION</t>
+          <t>CAMPAIGN_CMMN_BRND</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DIM_ORG.DIVISION</t>
+          <t>FACT_MEMBER_EVENT.CMMN_BRND_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_CAMPAIGN.CMMN_BRND_NM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -26982,12 +27378,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 3,594,822/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -26999,22 +27395,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ORG_DEPARTMENT</t>
+          <t>CAMPAIGN_MKTG_UTM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DIM_ORG.DEPARTMENT</t>
+          <t>FACT_MEMBER_EVENT.MKTG_UTM_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_CAMPAIGN.MKTG_UTM_NM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -27030,12 +27426,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>비영 651,493/4,633,105 (14.1%)</t>
         </is>
       </c>
     </row>
@@ -27047,22 +27443,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ORG_TEAM</t>
+          <t>CAMPAIGN_SPNSR_DIV_CD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIM_ORG.TEAM</t>
+          <t>FACT_MEMBER_EVENT.SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_CAMPAIGN.SPNSR_DIV_CD</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -27078,12 +27474,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 3,594,825/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -27095,22 +27491,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>REASON_CODE</t>
+          <t>CAMPAIGN_SPNSR_DIV_NM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_CODE</t>
+          <t>FACT_MEMBER_EVENT.SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_ID</t>
+          <t>CRM_CAMPAIGN.SPNSR_DIV_NM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -27126,12 +27522,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 5,839/5,839 (100%)</t>
+          <t>비영 3,594,825/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -27143,22 +27539,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>REASON_NAME</t>
+          <t>CAMPAIGN_CPR_DIV_CD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_NAME</t>
+          <t>FACT_MEMBER_EVENT.CPR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_CAMPAIGN.CPR_DIV_CD</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -27174,12 +27570,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 5,839/5,839 (100%)</t>
+          <t>비영 3,594,825/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -27191,22 +27587,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>REASON_TYPE</t>
+          <t>CAMPAIGN_CPR_DIV_NM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_TYPE</t>
+          <t>FACT_MEMBER_EVENT.CPR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CRM_CODE.CD_ID</t>
+          <t>CRM_CAMPAIGN.CPR_DIV_NM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -27227,7 +27623,535 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 5,838/5,839 (100.0%)</t>
+          <t>비영 3,594,825/4,633,105 (77.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_BK</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_DIV_NAME</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_DIV_NAME</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>비영 50/51 (98.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_GROUP_NAME</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_GROUP_NAME</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>비영 50/51 (98.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ORG_CORP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DIM_ORG.CORP</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_ID</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>전건 NULL (0/1,315)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ORG_DIVISION</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DIM_ORG.DIVISION</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_ID</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>전건 NULL (0/1,315)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ORG_DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DIM_ORG.DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_NM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>비영 1,315/1,315 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ORG_TEAM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DIM_ORG.TEAM</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_NM</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>전건 NULL (0/1,315)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>REASON_CODE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_CODE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_ID</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>비영 5,854/5,854 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>REASON_NAME</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_NAME</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>비영 5,854/5,854 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CRM_CODE.CD_ID</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>비영 5,853/5,854 (100.0%)</t>
         </is>
       </c>
     </row>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 39,332/39,332 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 240,487/255,417 (94.2%)</t>
+          <t>비영 240,487/255,452 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 22,070/255,417 (8.6%)</t>
+          <t>비영 22,078/255,452 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 38,064/39,332 (96.8%)</t>
+          <t>비영 38,099/39,367 (96.8%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 33,621/39,332 (85.5%)</t>
+          <t>비영 33,621/39,367 (85.4%)</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 2,113/39,332 (5.4%)</t>
+          <t>비영 2,148/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 34,624/39,332 (88.0%)</t>
+          <t>비영 34,624/39,367 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 15,984/39,332 (40.6%)</t>
+          <t>비영 15,984/39,367 (40.6%)</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 39,332/39,332 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 36,921/39,332 (93.9%)</t>
+          <t>비영 36,956/39,367 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 39,332/39,332 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 37,172/39,332 (94.5%)</t>
+          <t>비영 37,172/39,367 (94.4%)</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 14,980/39,332 (38.1%)</t>
+          <t>비영 14,980/39,367 (38.1%)</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 32,739/39,332 (83.2%)</t>
+          <t>비영 32,739/39,367 (83.2%)</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 35,951/39,332 (91.4%)</t>
+          <t>비영 35,951/39,367 (91.3%)</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 33,805/39,332 (85.9%)</t>
+          <t>비영 33,805/39,367 (85.9%)</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 2,170/39,332 (5.5%)</t>
+          <t>비영 2,170/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 239/39,332 (0.6%)</t>
+          <t>비영 239/39,367 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 38,120/39,332 (96.9%)</t>
+          <t>비영 38,155/39,367 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/39,332)</t>
+          <t>전건 NULL (0/39,367)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 2,071/39,332 (5.3%)</t>
+          <t>비영 2,079/39,367 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 2,072/39,332 (5.3%)</t>
+          <t>비영 2,080/39,367 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 14,410/39,332 (36.6%)</t>
+          <t>비영 14,410/39,367 (36.6%)</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 18,345/39,332 (46.6%)</t>
+          <t>비영 18,345/39,367 (46.6%)</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 9,164/9,165 (100.0%)</t>
+          <t>비영 9,166/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 9,161/9,165 (100.0%)</t>
+          <t>비영 9,163/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 5,442/5,442 (100%)</t>
+          <t>비영 5,522/5,522 (100%)</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 5,442/5,442 (100%)</t>
+          <t>비영 5,522/5,522 (100%)</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 5,433/5,442 (99.8%)</t>
+          <t>비영 5,508/5,522 (99.7%)</t>
         </is>
       </c>
     </row>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 5,359/5,442 (98.5%)</t>
+          <t>비영 5,438/5,522 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 5,413/5,442 (99.5%)</t>
+          <t>비영 5,492/5,522 (99.5%)</t>
         </is>
       </c>
     </row>
@@ -12749,7 +12749,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 5,401/5,442 (99.2%)</t>
+          <t>비영 5,480/5,522 (99.2%)</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 2,113/39,332 (5.4%)</t>
+          <t>비영 2,148/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 36,921/39,332 (93.9%)</t>
+          <t>비영 36,956/39,367 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -12893,7 +12893,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 39,332/39,332 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 39,332/39,332 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/255,417) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/255,452) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13419,7 +13419,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 192,723/255,417 (75.5%)</t>
+          <t>비영 192,723/255,452 (75.4%)</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/255,417) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/255,452) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13489,7 +13489,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.DEVICE_TYPE</t>
+          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 240,487/255,417 (94.2%)</t>
+          <t>비영 240,487/255,452 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 205,407/255,417 (80.4%)</t>
+          <t>비영 205,407/255,452 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 182,977/255,417 (71.6%)</t>
+          <t>비영 182,977/255,452 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 22,070/255,417 (8.6%)</t>
+          <t>비영 22,078/255,452 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 47,987/255,417 (18.8%)</t>
+          <t>비영 47,987/255,452 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 14,917/255,417 (5.8%)</t>
+          <t>비영 14,917/255,452 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13969,7 +13969,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.PAGE_TYPE</t>
+          <t>AGENCY_AD_DIGITAL.PAGE_TYPE_NM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_GROUP_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_GRP_NM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.GROUP_DIV</t>
+          <t>AGENCY_AD_DIGITAL.GRP_DIV_NM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CREATIVE_TYPE</t>
+          <t>AGENCY_AD_DIGITAL.MATR_TY_NM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_TYPE_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_TY_NM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.MEDIA_POTENTIAL_CUST_CNT</t>
+          <t>AGENCY_AD_DIGITAL.MEDIA_PTNT_CUST_CNT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CRM_DEV_CNT</t>
+          <t>AGENCY_AD_DIGITAL.CRM_DVLP_CNT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 38,064/39,332 (96.8%)</t>
+          <t>비영 38,099/39,367 (96.8%)</t>
         </is>
       </c>
     </row>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 33,621/39,332 (85.5%)</t>
+          <t>비영 33,621/39,367 (85.4%)</t>
         </is>
       </c>
     </row>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 2,113/39,332 (5.4%)</t>
+          <t>비영 2,148/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 34,624/39,332 (88.0%)</t>
+          <t>비영 34,624/39,367 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -14907,7 +14907,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 15,984/39,332 (40.6%)</t>
+          <t>비영 15,984/39,367 (40.6%)</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 39,332/39,332 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 36,921/39,332 (93.9%)</t>
+          <t>비영 36,956/39,367 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 39,332/39,332 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 37,172/39,332 (94.5%)</t>
+          <t>비영 37,172/39,367 (94.4%)</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 14,980/39,332 (38.1%)</t>
+          <t>비영 14,980/39,367 (38.1%)</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 32,739/39,332 (83.2%)</t>
+          <t>비영 32,739/39,367 (83.2%)</t>
         </is>
       </c>
     </row>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 35,951/39,332 (91.4%)</t>
+          <t>비영 35,951/39,367 (91.3%)</t>
         </is>
       </c>
     </row>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 33,805/39,332 (85.9%)</t>
+          <t>비영 33,805/39,367 (85.9%)</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 2,170/39,332 (5.5%)</t>
+          <t>비영 2,170/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 239/39,332 (0.6%)</t>
+          <t>비영 239/39,367 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 38,120/39,332 (96.9%)</t>
+          <t>비영 38,155/39,367 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>전건 NULL (0/39,332)</t>
+          <t>전건 NULL (0/39,367)</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 2,071/39,332 (5.3%)</t>
+          <t>비영 2,079/39,367 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 2,072/39,332 (5.3%)</t>
+          <t>비영 2,080/39,367 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 14,410/39,332 (36.6%)</t>
+          <t>비영 14,410/39,367 (36.6%)</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 18,345/39,332 (46.6%)</t>
+          <t>비영 18,345/39,367 (46.6%)</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 240,487/255,417 (94.2%)</t>
+          <t>비영 240,487/255,452 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -15993,7 +15993,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 205,407/255,417 (80.4%)</t>
+          <t>비영 205,407/255,452 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 182,977/255,417 (71.6%)</t>
+          <t>비영 182,977/255,452 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 47,987/255,417 (18.8%)</t>
+          <t>비영 47,987/255,452 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -16137,7 +16137,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 14,917/255,417 (5.8%)</t>
+          <t>비영 14,917/255,452 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.PAGE_TYPE</t>
+          <t>AGENCY_AD_DIGITAL.PAGE_TYPE_NM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -16207,7 +16207,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_GROUP_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_GRP_NM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.GROUP_DIV</t>
+          <t>AGENCY_AD_DIGITAL.GRP_DIV_NM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CREATIVE_TYPE</t>
+          <t>AGENCY_AD_DIGITAL.MATR_TY_NM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_TYPE_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_TY_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.MEDIA_POTENTIAL_CUST_CNT</t>
+          <t>AGENCY_AD_DIGITAL.MEDIA_PTNT_CUST_CNT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CRM_DEV_CNT</t>
+          <t>AGENCY_AD_DIGITAL.CRM_DVLP_CNT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 9,164/9,165 (100.0%)</t>
+          <t>비영 9,166/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 9,161/9,165 (100.0%)</t>
+          <t>비영 9,163/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.DEVICE_TYPE</t>
+          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 240,487/255,417 (94.2%)</t>
+          <t>비영 240,487/255,452 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 205,407/255,417 (80.4%)</t>
+          <t>비영 205,407/255,452 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 182,977/255,417 (71.6%)</t>
+          <t>비영 182,977/255,452 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -17615,7 +17615,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 22,070/255,417 (8.6%)</t>
+          <t>비영 22,078/255,452 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17663,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 47,987/255,417 (18.8%)</t>
+          <t>비영 47,987/255,452 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 14,917/255,417 (5.8%)</t>
+          <t>비영 14,917/255,452 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 255,417/255,417 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 9,165/9,165 (100%)</t>
+          <t>비영 9,167/9,167 (100%)</t>
         </is>
       </c>
     </row>
@@ -18439,7 +18439,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 9,164/9,165 (100.0%)</t>
+          <t>비영 9,166/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 9,164/9,165 (100.0%)</t>
+          <t>비영 9,166/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>전건 NULL (0/9,165)</t>
+          <t>전건 NULL (0/9,167)</t>
         </is>
       </c>
     </row>
@@ -18583,7 +18583,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 9,161/9,165 (100.0%)</t>
+          <t>비영 9,163/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18631,7 +18631,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 5,561/9,165 (60.7%)</t>
+          <t>비영 5,563/9,167 (60.7%)</t>
         </is>
       </c>
     </row>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 NULL (0/9,165)</t>
+          <t>전건 NULL (0/9,167)</t>
         </is>
       </c>
     </row>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.DEVICE_TYPE</t>
+          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.PLATFORM</t>
+          <t>BIGQUERY_DEVICE.PLATFORM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18790,7 +18790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 2,964/2,964 (100%)</t>
+          <t>비영 1,332/1,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 2,964/2,964 (100%)</t>
+          <t>비영 1,332/1,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -18997,7 +18997,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 2,964/2,964 (100%)</t>
+          <t>비영 1,332/1,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 424/2,964 (14.3%)</t>
+          <t>비영 274/1,332 (20.6%)</t>
         </is>
       </c>
     </row>
@@ -19057,17 +19057,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLAN_BUDGET_YEAR</t>
+          <t>EXEC_BUDGET_ERP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.PLAN_BUDGET_YEAR</t>
+          <t>FACT_BUDGET.EXEC_BUDGET_ERP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ERP_BUDGET.YEAR_BUDGET_AMT</t>
+          <t>ERP_BUDGET.EXEC_AMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 NULL (0/2,964)</t>
+          <t>비영 344/1,332 (25.8%)</t>
         </is>
       </c>
     </row>
@@ -19105,12 +19105,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EXEC_BUDGET_ERP</t>
+          <t>EXEC_BUDGET_EST</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.EXEC_BUDGET_ERP</t>
+          <t>FACT_BUDGET.EXEC_BUDGET_EST</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19136,12 +19136,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 662/2,964 (22.3%)</t>
+          <t>전건 NULL (0/1,332)</t>
         </is>
       </c>
     </row>
@@ -19153,12 +19153,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EXEC_BUDGET_EST</t>
+          <t>FUNDRAISING_COST</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.EXEC_BUDGET_EST</t>
+          <t>FACT_BUDGET.FUNDRAISING_COST</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19189,7 +19189,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 NULL (0/2,964)</t>
+          <t>전건 NULL (0/1,332)</t>
         </is>
       </c>
     </row>
@@ -19201,17 +19201,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FUNDRAISING_COST</t>
+          <t>AD_COST</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.FUNDRAISING_COST</t>
+          <t>FACT_BUDGET.AD_COST</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ERP_BUDGET.EXEC_AMT</t>
+          <t>ERP_BUDGET</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -19237,7 +19237,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 NULL (0/2,964)</t>
+          <t>전건 NULL (0/1,332)</t>
         </is>
       </c>
     </row>
@@ -19249,22 +19249,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AD_COST</t>
+          <t>ORG_CORP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.AD_COST</t>
+          <t>DIM_ORG.CORP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ERP_BUDGET</t>
+          <t>CRM_ORG.DEPT_ID</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BDGT_ACMSLT_LEDGER</t>
+          <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -19275,7 +19275,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 NULL (0/2,964)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -19297,12 +19297,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORG_CORP</t>
+          <t>ORG_DIVISION</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DIM_ORG.CORP</t>
+          <t>DIM_ORG.DIVISION</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19345,17 +19345,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORG_DIVISION</t>
+          <t>ORG_DEPARTMENT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DIM_ORG.DIVISION</t>
+          <t>DIM_ORG.DEPARTMENT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG.DEPT_NM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -19376,12 +19376,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 1,315/1,315 (100%)</t>
         </is>
       </c>
     </row>
@@ -19393,12 +19393,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORG_DEPARTMENT</t>
+          <t>ORG_TEAM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DIM_ORG.DEPARTMENT</t>
+          <t>DIM_ORG.TEAM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19424,12 +19424,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -19441,22 +19441,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORG_TEAM</t>
+          <t>BUDGET_ITEM_NAME</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DIM_ORG.TEAM</t>
+          <t>DIM_BUDGET_ITEM.BUDGET_ITEM_NAME</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>ERP_BUDGET_ITEM.MOK_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -19472,12 +19472,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 180/180 (100%)</t>
         </is>
       </c>
     </row>
@@ -19489,17 +19489,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BUDGET_ITEM_NAME</t>
+          <t>BUDGET_CATEGORY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DIM_BUDGET_ITEM.BUDGET_ITEM_NAME</t>
+          <t>DIM_BUDGET_ITEM.BUDGET_CATEGORY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ERP_BUDGET_ITEM.MOK_NM</t>
+          <t>ERP_BUDGET_ITEM.INCOME_EXPS_DIV_NM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -19520,12 +19520,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 180/180 (100%)</t>
+          <t>비영 179/180 (99.4%)</t>
         </is>
       </c>
     </row>
@@ -19537,22 +19537,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BUDGET_CATEGORY</t>
+          <t>CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DIM_BUDGET_ITEM.BUDGET_CATEGORY</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ERP_BUDGET_ITEM.INCOME_EXPENSE_DIV</t>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BDGT_ACMSLT_LEDGER</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -19568,12 +19568,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 179/180 (99.4%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -19585,17 +19585,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>CAMPAIGN_BRAND</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_CAMPAIGN.BRAND</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -19616,12 +19616,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 36,164/36,164 (100%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -19633,17 +19633,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -19664,12 +19664,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 34,704/36,164 (96.0%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -19681,22 +19681,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -19717,7 +19717,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 36,164/36,164 (100%)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -19729,17 +19729,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -19764,54 +19764,6 @@
         </is>
       </c>
       <c r="J20" t="inlineStr">
-        <is>
-          <t>비영 51/51 (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>WIDE_BUDGET</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SPONSORSHIP_NAME</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>직접참조</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>컬럼확정</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
         <is>
           <t>비영 51/51 (100%)</t>
         </is>
@@ -19828,7 +19780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20815,17 +20767,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INCREASE_FLAG</t>
+          <t>PART_STATUS_GROUP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.INCREASE_FLAG</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_GROUP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_CD</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_GROUP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -20846,12 +20798,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,134,126)</t>
+          <t>비영 1,122,886/1,134,126 (99.0%)</t>
         </is>
       </c>
     </row>
@@ -20863,17 +20815,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PART_STATUS_GROUP</t>
+          <t>PART_STATUS_NAME</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_GROUP</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_NAME</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_GROUP</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -20899,7 +20851,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,122,886/1,134,126 (99.0%)</t>
+          <t>비영 1,122,884/1,134,126 (99.0%)</t>
         </is>
       </c>
     </row>
@@ -20911,17 +20863,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PART_STATUS_NAME</t>
+          <t>PART_PATH_GROUP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_PATH_GROUP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_GROUP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -20947,7 +20899,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,122,884/1,134,126 (99.0%)</t>
+          <t>비영 1,124,441/1,134,126 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -20959,17 +20911,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PART_PATH_GROUP</t>
+          <t>PART_PATH_NAME</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_PATH_GROUP</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_PATH_NAME</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_GROUP</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_NM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -20995,7 +20947,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,124,441/1,134,126 (99.1%)</t>
+          <t>비영 1,124,439/1,134,126 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -21007,17 +20959,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PART_PATH_NAME</t>
+          <t>PART_CHANNEL_GROUP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_PATH_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_GROUP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_GROUP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -21043,7 +20995,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 1,124,439/1,134,126 (99.1%)</t>
+          <t>비영 981,922/1,134,126 (86.6%)</t>
         </is>
       </c>
     </row>
@@ -21055,17 +21007,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PART_CHANNEL_GROUP</t>
+          <t>PART_CHANNEL_NAME</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_GROUP</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_NAME</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_GROUP</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_NM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -21091,7 +21043,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 981,922/1,134,126 (86.6%)</t>
+          <t>비영 981,920/1,134,126 (86.6%)</t>
         </is>
       </c>
     </row>
@@ -21103,17 +21055,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PART_CHANNEL_NAME</t>
+          <t>PART_EVENT_BK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_BK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.EVENT_KEY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -21134,12 +21086,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 981,920/1,134,126 (86.6%)</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -21151,17 +21103,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PART_EVENT_BK</t>
+          <t>PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.EVENT_BK</t>
+          <t>FACT_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.EVENT_KEY</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -21199,17 +21151,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PARTCPT_SEQ</t>
+          <t>PART_EVENT_KIND</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+          <t>CRM_EVENT_PARTICIPATION.DW_SOURCE_TABLE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -21247,12 +21199,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PART_EVENT_KIND</t>
+          <t>PART_EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND</t>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21295,24 +21247,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PART_EVENT_KIND_NAME</t>
+          <t>FULL_DATE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND_NAME</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CRM_EVENT_PARTICIPATION.DW_SOURCE_TABLE</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
-        </is>
-      </c>
+          <t>DIM_DATE.FULL_DATE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -21321,17 +21265,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 1,134,126/1,134,126 (100%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21343,12 +21287,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FULL_DATE</t>
+          <t>YEAR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIM_DATE.FULL_DATE</t>
+          <t>DIM_DATE.YEAR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -21383,12 +21327,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YEAR</t>
+          <t>MONTH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIM_DATE.YEAR</t>
+          <t>DIM_DATE.MONTH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -21423,12 +21367,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MONTH</t>
+          <t>DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIM_DATE.MONTH</t>
+          <t>DIM_DATE.DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -21463,12 +21407,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DAY_OF_WEEK</t>
+          <t>WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DIM_DATE.DAY_OF_WEEK</t>
+          <t>DIM_DATE.WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -21503,12 +21447,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WEEK_OF_YEAR</t>
+          <t>IS_HOLIDAY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DIM_DATE.WEEK_OF_YEAR</t>
+          <t>DIM_DATE.IS_HOLIDAY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -21526,12 +21470,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -21543,16 +21487,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IS_HOLIDAY</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIM_DATE.IS_HOLIDAY</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+          <t>DIM_MEMBER.SEX</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.SEX</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
@@ -21561,17 +21513,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21583,17 +21535,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>SEX_NM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX</t>
+          <t>DIM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.SEX</t>
+          <t>CRM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -21631,22 +21583,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SEX_NM</t>
+          <t>MEMBER_GENDER_NAME</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX_NM</t>
+          <t>DIM_MEMBER.GENDER_NAME</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.SEX_NM</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -21679,22 +21631,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MEMBER_GENDER_NAME</t>
+          <t>MEMBER_AREA_CD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER_NAME</t>
+          <t>DIM_MEMBER.AREA_CD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER_DEV.AREA_CD</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -21715,7 +21667,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>비영 7,738,245/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21727,22 +21679,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MEMBER_AREA_CD</t>
+          <t>MEMBER_REGION</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AREA_CD</t>
+          <t>DIM_MEMBER.REGION</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AREA_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -21763,7 +21715,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,738,245/7,925,716 (97.6%)</t>
+          <t>비영 7,681,020/7,925,716 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -21775,22 +21727,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MEMBER_REGION</t>
+          <t>MEMBER_AGE_CD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.REGION</t>
+          <t>DIM_MEMBER.AGE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER_DEV.AGE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -21811,7 +21763,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,681,020/7,925,716 (96.9%)</t>
+          <t>비영 7,738,250/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21823,22 +21775,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_CD</t>
+          <t>MEMBER_AGE_BAND</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE</t>
+          <t>DIM_MEMBER.AGE_BAND</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AGE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -21871,22 +21823,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_BAND</t>
+          <t>MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE_BAND</t>
+          <t>DIM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -21907,7 +21859,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 7,738,250/7,925,716 (97.6%)</t>
+          <t>비영 7,749,993/7,925,716 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -21919,17 +21871,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MBER_STAT_CD</t>
+          <t>MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_STAT_CD</t>
+          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -21955,7 +21907,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 7,749,993/7,925,716 (97.8%)</t>
+          <t>비영 7,925,715/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21967,17 +21919,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MEMBER_STATUS_NAME</t>
+          <t>MBER_DIV_CD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
+          <t>DIM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -21998,12 +21950,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 7,925,715/7,925,716 (100.0%)</t>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
         </is>
       </c>
     </row>
@@ -22015,22 +21967,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MBER_DIV_CD</t>
+          <t>MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_DIV_CD</t>
+          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_DIV_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -22063,22 +22015,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MEMBER_TYPE_NAME</t>
+          <t>EVENT_BK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
+          <t>DIM_EVENT.EVENT_BK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_EVENT.EVENT_KEY</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -22099,7 +22051,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 3,787/3,787 (100%)</t>
         </is>
       </c>
     </row>
@@ -22111,17 +22063,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EVENT_BK</t>
+          <t>EVENT_KIND</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_BK</t>
+          <t>DIM_EVENT.EVENT_KIND</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_KEY</t>
+          <t>CRM_EVENT.EVENT_SOURCE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -22142,12 +22094,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 3,787/3,787 (100%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -22159,12 +22111,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EVENT_KIND</t>
+          <t>EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_KIND</t>
+          <t>DIM_EVENT.EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -22190,12 +22142,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 3,787/3,787 (100%)</t>
         </is>
       </c>
     </row>
@@ -22207,17 +22159,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EVENT_KIND_NAME</t>
+          <t>EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_KIND_NAME</t>
+          <t>DIM_EVENT.EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_SOURCE</t>
+          <t>CRM_EVENT.EVENT_DIV_CD</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -22238,12 +22190,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 3,787/3,787 (100%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -22255,17 +22207,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY</t>
+          <t>EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_CD</t>
+          <t>CRM_EVENT.EVENT_DIV_GROUP</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -22303,17 +22255,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY_GROUP</t>
+          <t>EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY_GROUP</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_GROUP</t>
+          <t>CRM_EVENT.EVENT_DIV_NM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -22351,17 +22303,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY_NAME</t>
+          <t>EVENT_NAME</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY_NAME</t>
+          <t>DIM_EVENT.EVENT_NAME</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_NM</t>
+          <t>CRM_EVENT.EVENT_NM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -22399,17 +22351,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EVENT_NAME</t>
+          <t>EVENT_START_DATE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_NAME</t>
+          <t>DIM_EVENT.EVENT_START_DATE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_NM</t>
+          <t>CRM_EVENT.STRT_DE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -22435,7 +22387,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 3,785/3,787 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -22447,17 +22399,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EVENT_START_DATE</t>
+          <t>EVENT_END_DATE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_START_DATE</t>
+          <t>DIM_EVENT.EVENT_END_DATE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CRM_EVENT.STRT_DE</t>
+          <t>CRM_EVENT.END_DE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -22495,12 +22447,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EVENT_END_DATE</t>
+          <t>EVENT_APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_END_DATE</t>
+          <t>DIM_EVENT.APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -22526,12 +22478,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>비영 3,785/3,787 (99.9%)</t>
+          <t>전건 NULL (0/3,787)</t>
         </is>
       </c>
     </row>
@@ -22543,17 +22495,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EVENT_APPLY_CHANNEL</t>
+          <t>EVENT_RECRUIT_HEADCOUNT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DIM_EVENT.APPLY_CHANNEL</t>
+          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CRM_EVENT.END_DE</t>
+          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -22574,12 +22526,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>전건 NULL (0/3,787)</t>
+          <t>비영 3,348/3,787 (88.4%)</t>
         </is>
       </c>
     </row>
@@ -22591,22 +22543,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EVENT_RECRUIT_HEADCOUNT</t>
+          <t>CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -22622,12 +22574,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 3,348/3,787 (88.4%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -22639,17 +22591,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>CAMPAIGN_BRAND</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_CAMPAIGN.BRAND</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -22670,12 +22622,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 36,164/36,164 (100%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -22687,17 +22639,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -22718,12 +22670,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 34,704/36,164 (96.0%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -22735,22 +22687,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -22771,7 +22723,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 36,164/36,164 (100%)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -22783,17 +22735,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -22818,54 +22770,6 @@
         </is>
       </c>
       <c r="J63" t="inlineStr">
-        <is>
-          <t>비영 51/51 (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>WIDE_EVENT_PARTICIPATION</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>SPONSORSHIP_NAME</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>직접참조</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>컬럼확정</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
         <is>
           <t>비영 51/51 (100%)</t>
         </is>
@@ -22967,7 +22871,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -23015,7 +22919,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GA4_EVENT.PAGE_LOCATION</t>
+          <t>BIGQUERY_EVENT.PAGE_LOCATION</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -23063,7 +22967,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.PAGE_LOCATION</t>
+          <t>BIGQUERY_EVENT.PAGE_LOCATION</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -23111,7 +23015,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_NAME</t>
+          <t>BIGQUERY_EVENT.EVENT_NAME</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -23159,7 +23063,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_NAME</t>
+          <t>BIGQUERY_EVENT.EVENT_NAME</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -23207,7 +23111,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_NAME</t>
+          <t>BIGQUERY_EVENT.EVENT_NAME</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -23255,7 +23159,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -23303,7 +23207,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -23351,7 +23255,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GA4_EVENT.PERCENT_SCROLLED</t>
+          <t>BIGQUERY_EVENT.PERCENT_SCROLLED</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -23399,7 +23303,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GA4_EVENT.USER_PSEUDO_ID</t>
+          <t>BIGQUERY_EVENT.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -23447,7 +23351,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GA4_EVENT.USER_PSEUDO_ID</t>
+          <t>BIGQUERY_EVENT.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -23495,7 +23399,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GA4_EVENT.USER_PSEUDO_ID</t>
+          <t>BIGQUERY_EVENT.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -23543,7 +23447,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GA4_EVENT;IDENTITY_MEMBER_XREF</t>
+          <t>BIGQUERY_EVENT;IDENTITY_MEMBER_XREF</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -23591,7 +23495,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -23639,7 +23543,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -24119,7 +24023,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -24167,7 +24071,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_LABEL</t>
+          <t>BIGQUERY_EVENT_DIM.EVENT_LABEL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -24215,7 +24119,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_ACTION</t>
+          <t>BIGQUERY_EVENT_DIM.EVENT_ACTION</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -24263,7 +24167,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -24311,7 +24215,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_MEDIUM</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_MEDIUM</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -24359,7 +24263,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_CONTENT</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_CONTENT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -24407,7 +24311,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_TERM</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_TERM</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -24455,7 +24359,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.SOURCE_MEDIUM</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE.SOURCE_MEDIUM</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -24503,7 +24407,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.DEVICE_TYPE</t>
+          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 39,367/39,367 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 240,487/255,452 (94.1%)</t>
+          <t>비영 240,487/255,417 (94.2%)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 22,078/255,452 (8.6%)</t>
+          <t>비영 22,070/255,417 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 38,099/39,367 (96.8%)</t>
+          <t>비영 38,064/39,332 (96.8%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 33,621/39,367 (85.4%)</t>
+          <t>비영 33,621/39,332 (85.5%)</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 2,148/39,367 (5.5%)</t>
+          <t>비영 2,113/39,332 (5.4%)</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 34,624/39,367 (88.0%)</t>
+          <t>비영 34,624/39,332 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 15,984/39,367 (40.6%)</t>
+          <t>비영 15,984/39,332 (40.6%)</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 39,367/39,367 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 36,956/39,367 (93.9%)</t>
+          <t>비영 36,921/39,332 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 39,367/39,367 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 37,172/39,367 (94.4%)</t>
+          <t>비영 37,172/39,332 (94.5%)</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 14,980/39,367 (38.1%)</t>
+          <t>비영 14,980/39,332 (38.1%)</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 32,739/39,367 (83.2%)</t>
+          <t>비영 32,739/39,332 (83.2%)</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 35,951/39,367 (91.3%)</t>
+          <t>비영 35,951/39,332 (91.4%)</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 33,805/39,367 (85.9%)</t>
+          <t>비영 33,805/39,332 (85.9%)</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 2,170/39,367 (5.5%)</t>
+          <t>비영 2,170/39,332 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 239/39,367 (0.6%)</t>
+          <t>비영 239/39,332 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 38,155/39,367 (96.9%)</t>
+          <t>비영 38,120/39,332 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/39,367)</t>
+          <t>전건 NULL (0/39,332)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 2,079/39,367 (5.3%)</t>
+          <t>비영 2,071/39,332 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 2,080/39,367 (5.3%)</t>
+          <t>비영 2,072/39,332 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 14,410/39,367 (36.6%)</t>
+          <t>비영 14,410/39,332 (36.6%)</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 18,345/39,367 (46.6%)</t>
+          <t>비영 18,345/39,332 (46.6%)</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 9,166/9,167 (100.0%)</t>
+          <t>비영 9,164/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 9,163/9,167 (100.0%)</t>
+          <t>비영 9,161/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 5,522/5,522 (100%)</t>
+          <t>비영 5,442/5,442 (100%)</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 5,522/5,522 (100%)</t>
+          <t>비영 5,442/5,442 (100%)</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 5,508/5,522 (99.7%)</t>
+          <t>비영 5,433/5,442 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 5,438/5,522 (98.5%)</t>
+          <t>비영 5,359/5,442 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 5,492/5,522 (99.5%)</t>
+          <t>비영 5,413/5,442 (99.5%)</t>
         </is>
       </c>
     </row>
@@ -12749,7 +12749,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 5,480/5,522 (99.2%)</t>
+          <t>비영 5,401/5,442 (99.2%)</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 2,148/39,367 (5.5%)</t>
+          <t>비영 2,113/39,332 (5.4%)</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 36,956/39,367 (93.9%)</t>
+          <t>비영 36,921/39,332 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -12893,7 +12893,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 39,367/39,367 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 39,367/39,367 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/255,452) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/255,417) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13419,7 +13419,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 192,723/255,452 (75.4%)</t>
+          <t>비영 192,723/255,417 (75.5%)</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/255,452) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/255,417) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13489,7 +13489,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
+          <t>BIGQUERY_DEVICE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 240,487/255,452 (94.1%)</t>
+          <t>비영 240,487/255,417 (94.2%)</t>
         </is>
       </c>
     </row>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 205,407/255,452 (80.4%)</t>
+          <t>비영 205,407/255,417 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 182,977/255,452 (71.6%)</t>
+          <t>비영 182,977/255,417 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 22,078/255,452 (8.6%)</t>
+          <t>비영 22,070/255,417 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 47,987/255,452 (18.8%)</t>
+          <t>비영 47,987/255,417 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 14,917/255,452 (5.8%)</t>
+          <t>비영 14,917/255,417 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -13969,7 +13969,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.PAGE_TYPE_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_PERF_DK</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_GRP_NM</t>
+          <t>AGENCY_AD_DIGITAL.PAGE_TYPE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.GRP_DIV_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_GROUP_NM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.MATR_TY_NM</t>
+          <t>AGENCY_AD_DIGITAL.GROUP_DIV</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_TY_NM</t>
+          <t>AGENCY_AD_DIGITAL.CREATIVE_TYPE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.MEDIA_PTNT_CUST_CNT</t>
+          <t>AGENCY_AD_DIGITAL.READ_CNT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CRM_DVLP_CNT</t>
+          <t>AGENCY_AD_DIGITAL.MEDIA_POTENTIAL_CUST_CNT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 38,099/39,367 (96.8%)</t>
+          <t>비영 38,064/39,332 (96.8%)</t>
         </is>
       </c>
     </row>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 33,621/39,367 (85.4%)</t>
+          <t>비영 33,621/39,332 (85.5%)</t>
         </is>
       </c>
     </row>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 2,148/39,367 (5.5%)</t>
+          <t>비영 2,113/39,332 (5.4%)</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 34,624/39,367 (88.0%)</t>
+          <t>비영 34,624/39,332 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -14907,7 +14907,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 15,984/39,367 (40.6%)</t>
+          <t>비영 15,984/39,332 (40.6%)</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 39,367/39,367 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 36,956/39,367 (93.9%)</t>
+          <t>비영 36,921/39,332 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 39,367/39,367 (100%)</t>
+          <t>비영 39,332/39,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 37,172/39,367 (94.4%)</t>
+          <t>비영 37,172/39,332 (94.5%)</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 14,980/39,367 (38.1%)</t>
+          <t>비영 14,980/39,332 (38.1%)</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 32,739/39,367 (83.2%)</t>
+          <t>비영 32,739/39,332 (83.2%)</t>
         </is>
       </c>
     </row>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 35,951/39,367 (91.3%)</t>
+          <t>비영 35,951/39,332 (91.4%)</t>
         </is>
       </c>
     </row>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 33,805/39,367 (85.9%)</t>
+          <t>비영 33,805/39,332 (85.9%)</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 2,170/39,367 (5.5%)</t>
+          <t>비영 2,170/39,332 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 239/39,367 (0.6%)</t>
+          <t>비영 239/39,332 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 38,155/39,367 (96.9%)</t>
+          <t>비영 38,120/39,332 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>전건 NULL (0/39,367)</t>
+          <t>전건 NULL (0/39,332)</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 2,079/39,367 (5.3%)</t>
+          <t>비영 2,071/39,332 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 2,080/39,367 (5.3%)</t>
+          <t>비영 2,072/39,332 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 14,410/39,367 (36.6%)</t>
+          <t>비영 14,410/39,332 (36.6%)</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 18,345/39,367 (46.6%)</t>
+          <t>비영 18,345/39,332 (46.6%)</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 240,487/255,452 (94.1%)</t>
+          <t>비영 240,487/255,417 (94.2%)</t>
         </is>
       </c>
     </row>
@@ -15993,7 +15993,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 205,407/255,452 (80.4%)</t>
+          <t>비영 205,407/255,417 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 182,977/255,452 (71.6%)</t>
+          <t>비영 182,977/255,417 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 47,987/255,452 (18.8%)</t>
+          <t>비영 47,987/255,417 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -16137,7 +16137,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 14,917/255,452 (5.8%)</t>
+          <t>비영 14,917/255,417 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.PAGE_TYPE_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_PERF_DK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -16207,7 +16207,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_GRP_NM</t>
+          <t>AGENCY_AD_DIGITAL.PAGE_TYPE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.GRP_DIV_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_GROUP_NM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.MATR_TY_NM</t>
+          <t>AGENCY_AD_DIGITAL.GROUP_DIV</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_TY_NM</t>
+          <t>AGENCY_AD_DIGITAL.CREATIVE_TYPE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.MEDIA_PTNT_CUST_CNT</t>
+          <t>AGENCY_AD_DIGITAL.READ_CNT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CRM_DVLP_CNT</t>
+          <t>AGENCY_AD_DIGITAL.MEDIA_POTENTIAL_CUST_CNT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 9,166/9,167 (100.0%)</t>
+          <t>비영 9,164/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 9,163/9,167 (100.0%)</t>
+          <t>비영 9,161/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
+          <t>BIGQUERY_DEVICE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 240,487/255,452 (94.1%)</t>
+          <t>비영 240,487/255,417 (94.2%)</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 205,407/255,452 (80.4%)</t>
+          <t>비영 205,407/255,417 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 182,977/255,452 (71.6%)</t>
+          <t>비영 182,977/255,417 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -17615,7 +17615,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 22,078/255,452 (8.6%)</t>
+          <t>비영 22,070/255,417 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17663,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 47,987/255,452 (18.8%)</t>
+          <t>비영 47,987/255,417 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 14,917/255,452 (5.8%)</t>
+          <t>비영 14,917/255,417 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 255,452/255,452 (100%)</t>
+          <t>비영 255,417/255,417 (100%)</t>
         </is>
       </c>
     </row>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 9,167/9,167 (100%)</t>
+          <t>비영 9,165/9,165 (100%)</t>
         </is>
       </c>
     </row>
@@ -18439,7 +18439,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 9,166/9,167 (100.0%)</t>
+          <t>비영 9,164/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 9,166/9,167 (100.0%)</t>
+          <t>비영 9,164/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>전건 NULL (0/9,167)</t>
+          <t>전건 NULL (0/9,165)</t>
         </is>
       </c>
     </row>
@@ -18583,7 +18583,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 9,163/9,167 (100.0%)</t>
+          <t>비영 9,161/9,165 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18631,7 +18631,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 5,563/9,167 (60.7%)</t>
+          <t>비영 5,561/9,165 (60.7%)</t>
         </is>
       </c>
     </row>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 NULL (0/9,167)</t>
+          <t>전건 NULL (0/9,165)</t>
         </is>
       </c>
     </row>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
+          <t>BIGQUERY_DEVICE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BIGQUERY_DEVICE.PLATFORM</t>
+          <t>BIGQUERY_DEVICE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18765,7 +18765,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -18790,7 +18790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18901,7 +18901,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 1,332/1,332 (100%)</t>
+          <t>비영 2,964/2,964 (100%)</t>
         </is>
       </c>
     </row>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 1,332/1,332 (100%)</t>
+          <t>비영 2,964/2,964 (100%)</t>
         </is>
       </c>
     </row>
@@ -18997,7 +18997,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 1,332/1,332 (100%)</t>
+          <t>비영 2,964/2,964 (100%)</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 274/1,332 (20.6%)</t>
+          <t>비영 424/2,964 (14.3%)</t>
         </is>
       </c>
     </row>
@@ -19057,17 +19057,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EXEC_BUDGET_ERP</t>
+          <t>PLAN_BUDGET_YEAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.EXEC_BUDGET_ERP</t>
+          <t>FACT_BUDGET.PLAN_BUDGET_YEAR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ERP_BUDGET.EXEC_AMT</t>
+          <t>ERP_BUDGET</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -19078,22 +19078,22 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>직접참조</t>
+          <t>CTE경유·동명대조</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 344/1,332 (25.8%)</t>
+          <t>전건 NULL (0/2,964)</t>
         </is>
       </c>
     </row>
@@ -19105,12 +19105,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EXEC_BUDGET_EST</t>
+          <t>EXEC_BUDGET_ERP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.EXEC_BUDGET_EST</t>
+          <t>FACT_BUDGET.EXEC_BUDGET_ERP</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19136,12 +19136,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,332)</t>
+          <t>비영 662/2,964 (22.3%)</t>
         </is>
       </c>
     </row>
@@ -19153,12 +19153,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FUNDRAISING_COST</t>
+          <t>EXEC_BUDGET_EST</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.FUNDRAISING_COST</t>
+          <t>FACT_BUDGET.EXEC_BUDGET_EST</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19189,7 +19189,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,332)</t>
+          <t>전건 NULL (0/2,964)</t>
         </is>
       </c>
     </row>
@@ -19201,17 +19201,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AD_COST</t>
+          <t>FUNDRAISING_COST</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.AD_COST</t>
+          <t>FACT_BUDGET.FUNDRAISING_COST</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ERP_BUDGET</t>
+          <t>ERP_BUDGET.EXEC_AMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -19237,7 +19237,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,332)</t>
+          <t>전건 NULL (0/2,964)</t>
         </is>
       </c>
     </row>
@@ -19249,22 +19249,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORG_CORP</t>
+          <t>AD_COST</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DIM_ORG.CORP</t>
+          <t>FACT_BUDGET.AD_COST</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>ERP_BUDGET</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -19275,7 +19275,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>전건 NULL (0/2,964)</t>
         </is>
       </c>
     </row>
@@ -19297,12 +19297,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORG_DIVISION</t>
+          <t>ORG_CORP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DIM_ORG.DIVISION</t>
+          <t>DIM_ORG.CORP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19345,17 +19345,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORG_DEPARTMENT</t>
+          <t>ORG_DIVISION</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DIM_ORG.DEPARTMENT</t>
+          <t>DIM_ORG.DIVISION</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_ORG.DEPT_ID</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -19376,12 +19376,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -19393,12 +19393,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORG_TEAM</t>
+          <t>ORG_DEPARTMENT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DIM_ORG.TEAM</t>
+          <t>DIM_ORG.DEPARTMENT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19424,12 +19424,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 1,315/1,315 (100%)</t>
         </is>
       </c>
     </row>
@@ -19441,22 +19441,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BUDGET_ITEM_NAME</t>
+          <t>ORG_TEAM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DIM_BUDGET_ITEM.BUDGET_ITEM_NAME</t>
+          <t>DIM_ORG.TEAM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ERP_BUDGET_ITEM.MOK_NM</t>
+          <t>CRM_ORG.DEPT_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BDGT_ACMSLT_LEDGER</t>
+          <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -19472,12 +19472,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 180/180 (100%)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -19489,17 +19489,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BUDGET_CATEGORY</t>
+          <t>BUDGET_ITEM_NAME</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DIM_BUDGET_ITEM.BUDGET_CATEGORY</t>
+          <t>DIM_BUDGET_ITEM.BUDGET_ITEM_NAME</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ERP_BUDGET_ITEM.INCOME_EXPS_DIV_NM</t>
+          <t>ERP_BUDGET_ITEM.MOK_NM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -19520,12 +19520,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 179/180 (99.4%)</t>
+          <t>비영 180/180 (100%)</t>
         </is>
       </c>
     </row>
@@ -19537,22 +19537,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>BUDGET_CATEGORY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_BUDGET_ITEM.BUDGET_CATEGORY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>ERP_BUDGET_ITEM.MOK_NM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -19568,12 +19568,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 36,164/36,164 (100%)</t>
+          <t>비영 179/180 (99.4%)</t>
         </is>
       </c>
     </row>
@@ -19585,17 +19585,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -19616,12 +19616,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 34,704/36,164 (96.0%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -19633,17 +19633,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>CAMPAIGN_BRAND</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_CAMPAIGN.BRAND</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -19664,12 +19664,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,164/36,164 (100%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -19681,22 +19681,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -19717,7 +19717,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -19729,17 +19729,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_NAME</t>
+          <t>SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -19764,6 +19764,54 @@
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WIDE_BUDGET</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>비영 51/51 (100%)</t>
         </is>
@@ -19780,7 +19828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20767,17 +20815,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PART_STATUS_GROUP</t>
+          <t>INCREASE_FLAG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_GROUP</t>
+          <t>FACT_EVENT_PARTICIPATION.INCREASE_FLAG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_GROUP</t>
+          <t>CRM_EVENT_PARTICIPATION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -20788,22 +20836,22 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>직접참조</t>
+          <t>CTE경유·동명대조</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 1,122,886/1,134,126 (99.0%)</t>
+          <t>전건 NULL (0/1,134,126)</t>
         </is>
       </c>
     </row>
@@ -20815,17 +20863,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PART_STATUS_NAME</t>
+          <t>PART_STATUS_GROUP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_GROUP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_GROUP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -20851,7 +20899,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,122,884/1,134,126 (99.0%)</t>
+          <t>비영 1,122,886/1,134,126 (99.0%)</t>
         </is>
       </c>
     </row>
@@ -20863,17 +20911,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PART_PATH_GROUP</t>
+          <t>PART_STATUS_NAME</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_PATH_GROUP</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_NAME</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_GROUP</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -20899,7 +20947,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,124,441/1,134,126 (99.1%)</t>
+          <t>비영 1,122,884/1,134,126 (99.0%)</t>
         </is>
       </c>
     </row>
@@ -20911,17 +20959,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PART_PATH_NAME</t>
+          <t>PART_PATH_GROUP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_PATH_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_PATH_GROUP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_GROUP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -20947,7 +20995,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,124,439/1,134,126 (99.1%)</t>
+          <t>비영 1,124,441/1,134,126 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -20959,17 +21007,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PART_CHANNEL_GROUP</t>
+          <t>PART_PATH_NAME</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_GROUP</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_PATH_NAME</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_GROUP</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_NM</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -20995,7 +21043,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 981,922/1,134,126 (86.6%)</t>
+          <t>비영 1,124,439/1,134,126 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -21007,17 +21055,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PART_CHANNEL_NAME</t>
+          <t>PART_CHANNEL_GROUP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_GROUP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_GROUP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -21043,7 +21091,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 981,920/1,134,126 (86.6%)</t>
+          <t>비영 981,922/1,134,126 (86.6%)</t>
         </is>
       </c>
     </row>
@@ -21055,17 +21103,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PART_EVENT_BK</t>
+          <t>PART_CHANNEL_NAME</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.EVENT_BK</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_NAME</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.EVENT_KEY</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_NM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -21086,12 +21134,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 1,134,126/1,134,126 (100%)</t>
+          <t>비영 981,920/1,134,126 (86.6%)</t>
         </is>
       </c>
     </row>
@@ -21103,17 +21151,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PARTCPT_SEQ</t>
+          <t>PART_EVENT_BK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_BK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+          <t>CRM_EVENT_PARTICIPATION.EVENT_KEY</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -21151,17 +21199,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PART_EVENT_KIND</t>
+          <t>PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND</t>
+          <t>FACT_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.DW_SOURCE_TABLE</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -21199,12 +21247,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PART_EVENT_KIND_NAME</t>
+          <t>PART_EVENT_KIND</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21247,16 +21295,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FULL_DATE</t>
+          <t>PART_EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIM_DATE.FULL_DATE</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND_NAME</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.DW_SOURCE_TABLE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -21265,17 +21321,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -21287,12 +21343,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YEAR</t>
+          <t>FULL_DATE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIM_DATE.YEAR</t>
+          <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -21327,12 +21383,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MONTH</t>
+          <t>YEAR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIM_DATE.MONTH</t>
+          <t>DIM_DATE.YEAR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -21367,12 +21423,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DAY_OF_WEEK</t>
+          <t>MONTH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIM_DATE.DAY_OF_WEEK</t>
+          <t>DIM_DATE.MONTH</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -21407,12 +21463,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WEEK_OF_YEAR</t>
+          <t>DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DIM_DATE.WEEK_OF_YEAR</t>
+          <t>DIM_DATE.DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -21447,12 +21503,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IS_HOLIDAY</t>
+          <t>WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DIM_DATE.IS_HOLIDAY</t>
+          <t>DIM_DATE.WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -21470,12 +21526,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21487,24 +21543,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>IS_HOLIDAY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.IS_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
@@ -21513,17 +21561,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -21535,17 +21583,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SEX_NM</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX_NM</t>
+          <t>DIM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.SEX_NM</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -21583,22 +21631,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MEMBER_GENDER_NAME</t>
+          <t>SEX_NM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER_NAME</t>
+          <t>DIM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -21631,22 +21679,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MEMBER_AREA_CD</t>
+          <t>MEMBER_GENDER_NAME</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AREA_CD</t>
+          <t>DIM_MEMBER.GENDER_NAME</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AREA_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -21667,7 +21715,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 7,738,245/7,925,716 (97.6%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21679,22 +21727,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MEMBER_REGION</t>
+          <t>MEMBER_AREA_CD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.REGION</t>
+          <t>DIM_MEMBER.AREA_CD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER_DEV.AREA_CD</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -21715,7 +21763,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,681,020/7,925,716 (96.9%)</t>
+          <t>비영 7,738,245/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21727,22 +21775,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_CD</t>
+          <t>MEMBER_REGION</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE</t>
+          <t>DIM_MEMBER.REGION</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AGE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -21763,7 +21811,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,738,250/7,925,716 (97.6%)</t>
+          <t>비영 7,681,020/7,925,716 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -21775,22 +21823,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_BAND</t>
+          <t>MEMBER_AGE_CD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE_BAND</t>
+          <t>DIM_MEMBER.AGE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER_DEV.AGE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -21823,22 +21871,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MBER_STAT_CD</t>
+          <t>MEMBER_AGE_BAND</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_STAT_CD</t>
+          <t>DIM_MEMBER.AGE_BAND</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -21859,7 +21907,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 7,749,993/7,925,716 (97.8%)</t>
+          <t>비영 7,738,250/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21871,17 +21919,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MEMBER_STATUS_NAME</t>
+          <t>MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
+          <t>DIM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -21907,7 +21955,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 7,925,715/7,925,716 (100.0%)</t>
+          <t>비영 7,749,993/7,925,716 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -21919,17 +21967,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MBER_DIV_CD</t>
+          <t>MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_DIV_CD</t>
+          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_DIV_CD</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -21950,12 +21998,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 7,925,715/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21967,22 +22015,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MEMBER_TYPE_NAME</t>
+          <t>MBER_DIV_CD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
+          <t>DIM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -22015,22 +22063,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EVENT_BK</t>
+          <t>MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_BK</t>
+          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_KEY</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -22051,7 +22099,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 3,787/3,787 (100%)</t>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
         </is>
       </c>
     </row>
@@ -22063,17 +22111,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EVENT_KIND</t>
+          <t>EVENT_BK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_KIND</t>
+          <t>DIM_EVENT.EVENT_BK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_SOURCE</t>
+          <t>CRM_EVENT.EVENT_KEY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -22094,12 +22142,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 3,787/3,787 (100%)</t>
         </is>
       </c>
     </row>
@@ -22111,12 +22159,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EVENT_KIND_NAME</t>
+          <t>EVENT_KIND</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_KIND_NAME</t>
+          <t>DIM_EVENT.EVENT_KIND</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -22142,12 +22190,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 3,787/3,787 (100%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -22159,17 +22207,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY</t>
+          <t>EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY</t>
+          <t>DIM_EVENT.EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_CD</t>
+          <t>CRM_EVENT.EVENT_SOURCE</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -22190,12 +22238,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 3,787/3,787 (100%)</t>
         </is>
       </c>
     </row>
@@ -22207,17 +22255,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY_GROUP</t>
+          <t>EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY_GROUP</t>
+          <t>DIM_EVENT.EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_GROUP</t>
+          <t>CRM_EVENT.EVENT_DIV_CD</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -22255,17 +22303,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY_NAME</t>
+          <t>EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY_NAME</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_NM</t>
+          <t>CRM_EVENT.EVENT_DIV_GROUP</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -22303,17 +22351,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EVENT_NAME</t>
+          <t>EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_NAME</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_NM</t>
+          <t>CRM_EVENT.EVENT_DIV_NM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -22351,17 +22399,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EVENT_START_DATE</t>
+          <t>EVENT_NAME</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_START_DATE</t>
+          <t>DIM_EVENT.EVENT_NAME</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CRM_EVENT.STRT_DE</t>
+          <t>CRM_EVENT.EVENT_NM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -22387,7 +22435,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 3,785/3,787 (99.9%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -22399,17 +22447,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EVENT_END_DATE</t>
+          <t>EVENT_START_DATE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_END_DATE</t>
+          <t>DIM_EVENT.EVENT_START_DATE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CRM_EVENT.END_DE</t>
+          <t>CRM_EVENT.STRT_DE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -22447,12 +22495,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EVENT_APPLY_CHANNEL</t>
+          <t>EVENT_END_DATE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DIM_EVENT.APPLY_CHANNEL</t>
+          <t>DIM_EVENT.EVENT_END_DATE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -22478,12 +22526,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>전건 NULL (0/3,787)</t>
+          <t>비영 3,785/3,787 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -22495,17 +22543,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EVENT_RECRUIT_HEADCOUNT</t>
+          <t>EVENT_APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
+          <t>DIM_EVENT.APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
+          <t>CRM_EVENT.END_DE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -22526,12 +22574,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 3,348/3,787 (88.4%)</t>
+          <t>전건 NULL (0/3,787)</t>
         </is>
       </c>
     </row>
@@ -22543,22 +22591,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>EVENT_RECRUIT_HEADCOUNT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -22574,12 +22622,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 36,164/36,164 (100%)</t>
+          <t>비영 3,348/3,787 (88.4%)</t>
         </is>
       </c>
     </row>
@@ -22591,17 +22639,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -22622,12 +22670,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 34,704/36,164 (96.0%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -22639,17 +22687,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>CAMPAIGN_BRAND</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_CAMPAIGN.BRAND</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -22670,12 +22718,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 36,164/36,164 (100%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -22687,22 +22735,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -22723,7 +22771,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -22735,17 +22783,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_NAME</t>
+          <t>SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -22770,6 +22818,54 @@
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>비영 51/51 (100%)</t>
         </is>
@@ -22871,12 +22967,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.EVENT_DT</t>
+          <t>IDENTITY_MEMBER_XREF.MEMBER_DK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -22919,12 +23015,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.PAGE_LOCATION</t>
+          <t>BIGQUERY_EVENT;IDENTITY_MEMBER_XREF</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>BIGQUERY_REFINED_DATA;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -22935,7 +23031,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -22967,12 +23063,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.PAGE_LOCATION</t>
+          <t>BIGQUERY_EVENT;IDENTITY_MEMBER_XREF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>BIGQUERY_REFINED_DATA;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -22983,7 +23079,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -23015,12 +23111,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.EVENT_NAME</t>
+          <t>BIGQUERY_EVENT;IDENTITY_MEMBER_XREF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>BIGQUERY_REFINED_DATA;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -23031,7 +23127,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -23063,12 +23159,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.EVENT_NAME</t>
+          <t>BIGQUERY_EVENT;IDENTITY_MEMBER_XREF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>BIGQUERY_REFINED_DATA;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -23079,7 +23175,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -23111,12 +23207,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.EVENT_NAME</t>
+          <t>BIGQUERY_EVENT;IDENTITY_MEMBER_XREF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>BIGQUERY_REFINED_DATA;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -23127,7 +23223,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -23159,12 +23255,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -23207,12 +23303,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -23255,12 +23351,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.PERCENT_SCROLLED</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -23303,12 +23399,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.USER_PSEUDO_ID</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -23351,12 +23447,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.USER_PSEUDO_ID</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -23399,12 +23495,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.USER_PSEUDO_ID</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -23495,12 +23591,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -23543,12 +23639,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+          <t>IDENTITY_MEMBER_XREF.USER_PSEUDO_ID</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BIGQUERY_REFINED_DATA</t>
+          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -24023,7 +24119,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+          <t>BIGQUERY_EVENT_DIM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -24039,7 +24135,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -24071,7 +24167,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT_DIM.EVENT_LABEL</t>
+          <t>BIGQUERY_EVENT_DIM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -24087,7 +24183,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -24119,7 +24215,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT_DIM.EVENT_ACTION</t>
+          <t>BIGQUERY_EVENT_DIM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -24135,7 +24231,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -24167,7 +24263,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -24183,7 +24279,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -24215,7 +24311,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_MEDIUM</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -24231,7 +24327,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -24263,7 +24359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_CONTENT</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -24279,7 +24375,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -24311,7 +24407,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_TERM</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -24327,7 +24423,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -24359,7 +24455,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BIGQUERY_TRAFFIC_SOURCE.SOURCE_MEDIUM</t>
+          <t>BIGQUERY_TRAFFIC_SOURCE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -24375,7 +24471,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -24407,7 +24503,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
+          <t>BIGQUERY_DEVICE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -24423,7 +24519,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
